--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,6 +887,9722 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126243187</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80948</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>438777</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6783503</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126244085</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4772</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>438809</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6783806</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126243254</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>438790</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6783520</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126242851</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>438926</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6783631</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126243811</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98364</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>438886</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6783805</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126242965</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57649</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>438888</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6783584</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126243055</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>438823</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6783513</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126244046</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98364</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>438887</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6783852</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126243614</v>
+      </c>
+      <c r="B12" t="n">
+        <v>88645</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>510</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>438797</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6783670</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126243724</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91857</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5454</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Hornvaxskinn</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Crustoderma corneum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>438883</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6783662</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126243784</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98364</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>438893</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6783787</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126243933</v>
+      </c>
+      <c r="B15" t="n">
+        <v>82785</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>438928</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6783763</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126243682</v>
+      </c>
+      <c r="B16" t="n">
+        <v>88645</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>510</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>438813</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6783722</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126243075</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79059</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>438799</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6783496</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126244296</v>
+      </c>
+      <c r="B18" t="n">
+        <v>82785</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>438723</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6783752</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126244055</v>
+      </c>
+      <c r="B19" t="n">
+        <v>82785</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>438833</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6783826</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126242913</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>438938</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6783637</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126243527</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91250</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>438826</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6783693</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126243709</v>
+      </c>
+      <c r="B22" t="n">
+        <v>82785</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>438875</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6783718</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126244007</v>
+      </c>
+      <c r="B23" t="n">
+        <v>82785</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>438925</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6783804</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126243757</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79052</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>864</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>438889</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6783762</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126243439</v>
+      </c>
+      <c r="B25" t="n">
+        <v>88645</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>510</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>438740</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6783462</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126243348</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79005</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>185</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>438767</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6783455</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126243738</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79005</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>185</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>438885</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6783710</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126243565</v>
+      </c>
+      <c r="B28" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>438805</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6783685</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126243148</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>438785</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6783487</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126243647</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97221</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>438790</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6783649</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126243342</v>
+      </c>
+      <c r="B31" t="n">
+        <v>82785</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>438767</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6783455</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126244253</v>
+      </c>
+      <c r="B32" t="n">
+        <v>82785</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>438791</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6783795</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126243742</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>438885</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6783710</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126244571</v>
+      </c>
+      <c r="B34" t="n">
+        <v>82785</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>438751</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6783884</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126244328</v>
+      </c>
+      <c r="B35" t="n">
+        <v>82785</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>438584</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6783774</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126243379</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79059</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>438694</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6783458</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126244106</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98364</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>438782</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6783777</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126244026</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98364</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>438902</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6783843</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126243450</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91201</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>438740</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6783462</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126243521</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91201</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>438845</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6783696</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126242981</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>438894</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6783561</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126244589</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98364</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>438824</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6783885</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126243702</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98343</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>438786</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6783704</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126243995</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98364</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>438953</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6783788</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126243519</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57812</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>438845</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6783696</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>126244033</v>
+      </c>
+      <c r="B46" t="n">
+        <v>82785</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>438911</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6783847</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>126243010</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>438852</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6783530</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>126243233</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>438775</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6783504</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>126243370</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79591</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>438714</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6783492</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>126244099</v>
+      </c>
+      <c r="B50" t="n">
+        <v>82785</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>438804</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6783800</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>126244009</v>
+      </c>
+      <c r="B51" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>438925</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6783804</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>126243769</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78336</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>498</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Liten sotlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Acolium karelicum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>438898</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6783784</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>126243332</v>
+      </c>
+      <c r="B53" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>438770</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6783484</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>126242940</v>
+      </c>
+      <c r="B54" t="n">
+        <v>57649</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>438898</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6783622</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>126243499</v>
+      </c>
+      <c r="B55" t="n">
+        <v>82785</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>438858</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6783695</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>126243713</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>438875</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6783718</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>126243617</v>
+      </c>
+      <c r="B57" t="n">
+        <v>91236</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>438797</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6783670</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>126243351</v>
+      </c>
+      <c r="B58" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>438767</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6783455</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>126243986</v>
+      </c>
+      <c r="B59" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>438947</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6783782</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>126244294</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98364</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>438723</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6783752</v>
+      </c>
+      <c r="S60" t="n">
+        <v>5</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>126243980</v>
+      </c>
+      <c r="B61" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>438928</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6783763</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>126243641</v>
+      </c>
+      <c r="B62" t="n">
+        <v>98364</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>438790</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6783649</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>126244052</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79591</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>438821</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6783854</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>126243462</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>438777</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6783527</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>126243492</v>
+      </c>
+      <c r="B65" t="n">
+        <v>56844</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>438871</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6783612</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Den tog ett s.k sandbad i sandblottan efter en rofyllda.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>126243823</v>
+      </c>
+      <c r="B66" t="n">
+        <v>82785</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>438911</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6783821</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>126244312</v>
+      </c>
+      <c r="B67" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>438654</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6783741</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>126243259</v>
+      </c>
+      <c r="B68" t="n">
+        <v>91201</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>438790</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6783520</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>126242798</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57649</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>438938</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6783650</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Mycket hackspår i den ca 160 åriga naturskogen</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>126242918</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79005</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>185</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>438917</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6783626</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>126244077</v>
+      </c>
+      <c r="B71" t="n">
+        <v>98364</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>438852</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6783837</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>126243314</v>
+      </c>
+      <c r="B72" t="n">
+        <v>91823</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1179</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Gräddticka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Perenniporia subacida</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Peck) Donk</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>438816</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6783530</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>126243042</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79052</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>864</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>438848</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6783520</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>126244274</v>
+      </c>
+      <c r="B74" t="n">
+        <v>82785</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>438776</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6783788</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>126243459</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79005</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>185</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>438777</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6783527</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>126244337</v>
+      </c>
+      <c r="B76" t="n">
+        <v>98261</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>438574</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6783811</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>126243070</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79005</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>185</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>438799</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6783496</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>126243991</v>
+      </c>
+      <c r="B78" t="n">
+        <v>91254</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>438953</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6783776</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>126243586</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57649</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>438805</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6783685</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>126243208</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57649</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>438777</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6783503</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>126243363</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79591</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>438739</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6783474</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>126243816</v>
+      </c>
+      <c r="B82" t="n">
+        <v>98261</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>438886</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6783805</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>126243505</v>
+      </c>
+      <c r="B83" t="n">
+        <v>80111</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>438858</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6783695</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>126243220</v>
+      </c>
+      <c r="B84" t="n">
+        <v>91201</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>438775</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6783504</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>126243452</v>
+      </c>
+      <c r="B85" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>438740</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6783462</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>126243191</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79059</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>438777</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6783503</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>126243732</v>
+      </c>
+      <c r="B87" t="n">
+        <v>57649</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>438882</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6783685</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>126243676</v>
+      </c>
+      <c r="B88" t="n">
+        <v>98364</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>438813</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6783722</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>126243608</v>
+      </c>
+      <c r="B89" t="n">
+        <v>91594</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>438797</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6783670</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>126243143</v>
+      </c>
+      <c r="B90" t="n">
+        <v>56844</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>438785</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6783487</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>En hona och 5 kycklingar</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>126249487</v>
+      </c>
+      <c r="B91" t="n">
+        <v>98364</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Räklitt, Hållberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>438890</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6783610</v>
+      </c>
+      <c r="S91" t="n">
+        <v>50</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>21:07</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>126244082</v>
+      </c>
+      <c r="B92" t="n">
+        <v>5176</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>438809</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6783806</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>126243447</v>
+      </c>
+      <c r="B93" t="n">
+        <v>82785</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>438740</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6783462</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>126243415</v>
+      </c>
+      <c r="B94" t="n">
+        <v>57649</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>438722</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6783470</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>126243503</v>
+      </c>
+      <c r="B95" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>438858</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6783695</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>126243973</v>
+      </c>
+      <c r="B96" t="n">
+        <v>88645</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>510</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>438928</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6783763</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>126243395</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79562</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>438682</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6783454</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>126244320</v>
+      </c>
+      <c r="B98" t="n">
+        <v>98261</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>438606</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6783759</v>
+      </c>
+      <c r="S98" t="n">
+        <v>5</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -3929,32 +3929,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126244571</v>
+        <v>126243379</v>
       </c>
       <c r="B34" t="n">
-        <v>82785</v>
+        <v>79059</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>6450</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438751</v>
+        <v>438694</v>
       </c>
       <c r="R34" t="n">
-        <v>6783884</v>
+        <v>6783458</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4030,37 +4030,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126244328</v>
+        <v>126244106</v>
       </c>
       <c r="B35" t="n">
-        <v>82785</v>
+        <v>98364</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4068,10 +4069,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>438584</v>
+        <v>438782</v>
       </c>
       <c r="R35" t="n">
-        <v>6783774</v>
+        <v>6783777</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4098,12 +4099,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4131,32 +4132,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126243379</v>
+        <v>126244571</v>
       </c>
       <c r="B36" t="n">
-        <v>79059</v>
+        <v>82785</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4169,10 +4170,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>438694</v>
+        <v>438751</v>
       </c>
       <c r="R36" t="n">
-        <v>6783458</v>
+        <v>6783884</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4199,12 +4200,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4232,38 +4233,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126244106</v>
+        <v>126244328</v>
       </c>
       <c r="B37" t="n">
-        <v>98364</v>
+        <v>82785</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>438782</v>
+        <v>438584</v>
       </c>
       <c r="R37" t="n">
-        <v>6783777</v>
+        <v>6783774</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4301,12 +4301,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -6277,10 +6277,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126243617</v>
+        <v>126243980</v>
       </c>
       <c r="B57" t="n">
-        <v>91236</v>
+        <v>78973</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6288,21 +6288,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>438797</v>
+        <v>438928</v>
       </c>
       <c r="R57" t="n">
-        <v>6783670</v>
+        <v>6783763</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6378,37 +6378,42 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126243351</v>
+        <v>126243641</v>
       </c>
       <c r="B58" t="n">
-        <v>78973</v>
+        <v>98364</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6416,10 +6421,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>438767</v>
+        <v>438790</v>
       </c>
       <c r="R58" t="n">
-        <v>6783455</v>
+        <v>6783649</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6479,10 +6484,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126243986</v>
+        <v>126243617</v>
       </c>
       <c r="B59" t="n">
-        <v>78973</v>
+        <v>91236</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6490,21 +6495,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6517,10 +6522,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>438947</v>
+        <v>438797</v>
       </c>
       <c r="R59" t="n">
-        <v>6783782</v>
+        <v>6783670</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6580,38 +6585,37 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126244294</v>
+        <v>126244052</v>
       </c>
       <c r="B60" t="n">
-        <v>98364</v>
+        <v>79591</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6619,10 +6623,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>438723</v>
+        <v>438821</v>
       </c>
       <c r="R60" t="n">
-        <v>6783752</v>
+        <v>6783854</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6649,12 +6653,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6682,7 +6686,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126243980</v>
+        <v>126243462</v>
       </c>
       <c r="B61" t="n">
         <v>78973</v>
@@ -6720,10 +6724,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>438928</v>
+        <v>438777</v>
       </c>
       <c r="R61" t="n">
-        <v>6783763</v>
+        <v>6783527</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6783,10 +6787,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126243641</v>
+        <v>126243492</v>
       </c>
       <c r="B62" t="n">
-        <v>98364</v>
+        <v>56844</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6794,31 +6798,35 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -6826,10 +6834,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>438790</v>
+        <v>438871</v>
       </c>
       <c r="R62" t="n">
-        <v>6783649</v>
+        <v>6783612</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6864,13 +6872,17 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Den tog ett s.k sandbad i sandblottan efter en rofyllda.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6889,10 +6901,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126244052</v>
+        <v>126243351</v>
       </c>
       <c r="B63" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6900,21 +6912,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6927,10 +6939,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>438821</v>
+        <v>438767</v>
       </c>
       <c r="R63" t="n">
-        <v>6783854</v>
+        <v>6783455</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6990,7 +7002,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126243462</v>
+        <v>126243986</v>
       </c>
       <c r="B64" t="n">
         <v>78973</v>
@@ -7028,10 +7040,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>438777</v>
+        <v>438947</v>
       </c>
       <c r="R64" t="n">
-        <v>6783527</v>
+        <v>6783782</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7091,10 +7103,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126243492</v>
+        <v>126244294</v>
       </c>
       <c r="B65" t="n">
-        <v>56844</v>
+        <v>98364</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7102,35 +7114,27 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7138,10 +7142,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>438871</v>
+        <v>438723</v>
       </c>
       <c r="R65" t="n">
-        <v>6783612</v>
+        <v>6783752</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7168,17 +7172,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Den tog ett s.k sandbad i sandblottan efter en rofyllda.</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7187,6 +7186,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7306,54 +7306,37 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126244312</v>
+        <v>126243259</v>
       </c>
       <c r="B67" t="n">
-        <v>56835</v>
+        <v>91201</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7361,10 +7344,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>438654</v>
+        <v>438790</v>
       </c>
       <c r="R67" t="n">
-        <v>6783741</v>
+        <v>6783520</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7391,12 +7374,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7405,6 +7388,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7423,37 +7407,42 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126243259</v>
+        <v>126242798</v>
       </c>
       <c r="B68" t="n">
-        <v>91201</v>
+        <v>57649</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7461,10 +7450,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>438790</v>
+        <v>438938</v>
       </c>
       <c r="R68" t="n">
-        <v>6783520</v>
+        <v>6783650</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7499,13 +7488,17 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Mycket hackspår i den ca 160 åriga naturskogen</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7524,10 +7517,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126242798</v>
+        <v>126242918</v>
       </c>
       <c r="B69" t="n">
-        <v>57649</v>
+        <v>79005</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7535,31 +7528,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7567,10 +7555,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>438938</v>
+        <v>438917</v>
       </c>
       <c r="R69" t="n">
-        <v>6783650</v>
+        <v>6783626</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7605,17 +7593,13 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Mycket hackspår i den ca 160 åriga naturskogen</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7634,37 +7618,38 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126242918</v>
+        <v>126244077</v>
       </c>
       <c r="B70" t="n">
-        <v>79005</v>
+        <v>98364</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>185</v>
+        <v>221952</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7672,10 +7657,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>438917</v>
+        <v>438852</v>
       </c>
       <c r="R70" t="n">
-        <v>6783626</v>
+        <v>6783837</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7735,38 +7720,54 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126244077</v>
+        <v>126244312</v>
       </c>
       <c r="B71" t="n">
-        <v>98364</v>
+        <v>56835</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>102612</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7774,10 +7775,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>438852</v>
+        <v>438654</v>
       </c>
       <c r="R71" t="n">
-        <v>6783837</v>
+        <v>6783741</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7804,12 +7805,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7818,7 +7819,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -9891,10 +9891,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126244082</v>
+        <v>126244320</v>
       </c>
       <c r="B92" t="n">
-        <v>5176</v>
+        <v>98261</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9902,28 +9902,27 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100526</v>
+        <v>223591</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -9931,10 +9930,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>438809</v>
+        <v>438606</v>
       </c>
       <c r="R92" t="n">
-        <v>6783806</v>
+        <v>6783759</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9961,12 +9960,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9994,37 +9993,39 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126243447</v>
+        <v>126244082</v>
       </c>
       <c r="B93" t="n">
-        <v>82785</v>
+        <v>5176</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1312</v>
+        <v>100526</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10032,10 +10033,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>438740</v>
+        <v>438809</v>
       </c>
       <c r="R93" t="n">
-        <v>6783462</v>
+        <v>6783806</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10095,10 +10096,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126243415</v>
+        <v>126243447</v>
       </c>
       <c r="B94" t="n">
-        <v>57649</v>
+        <v>82785</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10106,31 +10107,26 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10138,10 +10134,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>438722</v>
+        <v>438740</v>
       </c>
       <c r="R94" t="n">
-        <v>6783470</v>
+        <v>6783462</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10182,6 +10178,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10200,10 +10197,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126243503</v>
+        <v>126243415</v>
       </c>
       <c r="B95" t="n">
-        <v>78973</v>
+        <v>57649</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10211,26 +10208,31 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10238,10 +10240,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>438858</v>
+        <v>438722</v>
       </c>
       <c r="R95" t="n">
-        <v>6783695</v>
+        <v>6783470</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10282,7 +10284,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10301,10 +10302,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126243973</v>
+        <v>126243503</v>
       </c>
       <c r="B96" t="n">
-        <v>88645</v>
+        <v>78973</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10312,21 +10313,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10339,10 +10340,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>438928</v>
+        <v>438858</v>
       </c>
       <c r="R96" t="n">
-        <v>6783763</v>
+        <v>6783695</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10402,10 +10403,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126243395</v>
+        <v>126243973</v>
       </c>
       <c r="B97" t="n">
-        <v>79562</v>
+        <v>88645</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10413,21 +10414,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229821</v>
+        <v>510</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10440,10 +10441,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>438682</v>
+        <v>438928</v>
       </c>
       <c r="R97" t="n">
-        <v>6783454</v>
+        <v>6783763</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10503,38 +10504,37 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126244320</v>
+        <v>126243395</v>
       </c>
       <c r="B98" t="n">
-        <v>98261</v>
+        <v>79562</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>223591</v>
+        <v>229821</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -10542,10 +10542,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>438606</v>
+        <v>438682</v>
       </c>
       <c r="R98" t="n">
-        <v>6783759</v>
+        <v>6783454</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10572,12 +10572,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD98" t="b">

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -990,39 +990,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126244085</v>
+        <v>126242965</v>
       </c>
       <c r="B5" t="n">
-        <v>4772</v>
+        <v>57649</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1030,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438809</v>
+        <v>438888</v>
       </c>
       <c r="R5" t="n">
-        <v>6783806</v>
+        <v>6783584</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1074,7 +1077,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1093,37 +1095,39 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126243254</v>
+        <v>126244085</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>4772</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1131,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438790</v>
+        <v>438809</v>
       </c>
       <c r="R6" t="n">
-        <v>6783520</v>
+        <v>6783806</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1194,7 +1198,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126242851</v>
+        <v>126243254</v>
       </c>
       <c r="B7" t="n">
         <v>78973</v>
@@ -1232,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438926</v>
+        <v>438790</v>
       </c>
       <c r="R7" t="n">
-        <v>6783631</v>
+        <v>6783520</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1295,38 +1299,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126243811</v>
+        <v>126242851</v>
       </c>
       <c r="B8" t="n">
-        <v>98364</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1334,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438886</v>
+        <v>438926</v>
       </c>
       <c r="R8" t="n">
-        <v>6783805</v>
+        <v>6783631</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,10 +1400,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126242965</v>
+        <v>126243055</v>
       </c>
       <c r="B9" t="n">
-        <v>57649</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1408,31 +1411,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1440,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438888</v>
+        <v>438823</v>
       </c>
       <c r="R9" t="n">
-        <v>6783584</v>
+        <v>6783513</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1484,6 +1482,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1502,37 +1501,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126243055</v>
+        <v>126243811</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>98366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438823</v>
+        <v>438886</v>
       </c>
       <c r="R10" t="n">
-        <v>6783513</v>
+        <v>6783805</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1606,7 +1606,7 @@
         <v>126244046</v>
       </c>
       <c r="B11" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>126243614</v>
       </c>
       <c r="B12" t="n">
-        <v>88645</v>
+        <v>88647</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126243724</v>
+        <v>126243933</v>
       </c>
       <c r="B13" t="n">
-        <v>91857</v>
+        <v>82785</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1817,21 +1817,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5454</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438883</v>
+        <v>438928</v>
       </c>
       <c r="R13" t="n">
-        <v>6783662</v>
+        <v>6783763</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1907,38 +1907,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126243784</v>
+        <v>126243682</v>
       </c>
       <c r="B14" t="n">
-        <v>98364</v>
+        <v>88647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1946,10 +1945,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438893</v>
+        <v>438813</v>
       </c>
       <c r="R14" t="n">
-        <v>6783787</v>
+        <v>6783722</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2009,10 +2008,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126243933</v>
+        <v>126243724</v>
       </c>
       <c r="B15" t="n">
-        <v>82785</v>
+        <v>91859</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2020,21 +2019,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>5454</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2047,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438928</v>
+        <v>438883</v>
       </c>
       <c r="R15" t="n">
-        <v>6783763</v>
+        <v>6783662</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2110,37 +2109,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126243682</v>
+        <v>126243784</v>
       </c>
       <c r="B16" t="n">
-        <v>88645</v>
+        <v>98366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438813</v>
+        <v>438893</v>
       </c>
       <c r="R16" t="n">
-        <v>6783722</v>
+        <v>6783787</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2211,32 +2211,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126243075</v>
+        <v>126244296</v>
       </c>
       <c r="B17" t="n">
-        <v>79059</v>
+        <v>82785</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438799</v>
+        <v>438723</v>
       </c>
       <c r="R17" t="n">
-        <v>6783496</v>
+        <v>6783752</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2279,12 +2279,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2312,7 +2312,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126244296</v>
+        <v>126244055</v>
       </c>
       <c r="B18" t="n">
         <v>82785</v>
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438723</v>
+        <v>438833</v>
       </c>
       <c r="R18" t="n">
-        <v>6783752</v>
+        <v>6783826</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2380,12 +2380,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2413,7 +2413,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126244055</v>
+        <v>126243709</v>
       </c>
       <c r="B19" t="n">
         <v>82785</v>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438833</v>
+        <v>438875</v>
       </c>
       <c r="R19" t="n">
-        <v>6783826</v>
+        <v>6783718</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2514,10 +2514,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126242913</v>
+        <v>126244007</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>82785</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2525,21 +2525,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438938</v>
+        <v>438925</v>
       </c>
       <c r="R20" t="n">
-        <v>6783637</v>
+        <v>6783804</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126243527</v>
+        <v>126243757</v>
       </c>
       <c r="B21" t="n">
-        <v>91250</v>
+        <v>79052</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438826</v>
+        <v>438889</v>
       </c>
       <c r="R21" t="n">
-        <v>6783693</v>
+        <v>6783762</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2716,10 +2716,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126243709</v>
+        <v>126243527</v>
       </c>
       <c r="B22" t="n">
-        <v>82785</v>
+        <v>91252</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2727,21 +2727,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438875</v>
+        <v>438826</v>
       </c>
       <c r="R22" t="n">
-        <v>6783718</v>
+        <v>6783693</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126244007</v>
+        <v>126242913</v>
       </c>
       <c r="B23" t="n">
-        <v>82785</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2828,21 +2828,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>438925</v>
+        <v>438938</v>
       </c>
       <c r="R23" t="n">
-        <v>6783804</v>
+        <v>6783637</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2918,32 +2918,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126243757</v>
+        <v>126243075</v>
       </c>
       <c r="B24" t="n">
-        <v>79052</v>
+        <v>79059</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>864</v>
+        <v>6450</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>438889</v>
+        <v>438799</v>
       </c>
       <c r="R24" t="n">
-        <v>6783762</v>
+        <v>6783496</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3022,7 +3022,7 @@
         <v>126243439</v>
       </c>
       <c r="B25" t="n">
-        <v>88645</v>
+        <v>88647</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126243348</v>
+        <v>126243565</v>
       </c>
       <c r="B26" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3131,21 +3131,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>438767</v>
+        <v>438805</v>
       </c>
       <c r="R26" t="n">
-        <v>6783455</v>
+        <v>6783685</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3221,10 +3221,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126243738</v>
+        <v>126243148</v>
       </c>
       <c r="B27" t="n">
-        <v>79005</v>
+        <v>78973</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3232,21 +3232,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438885</v>
+        <v>438785</v>
       </c>
       <c r="R27" t="n">
-        <v>6783710</v>
+        <v>6783487</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3322,7 +3322,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126243565</v>
+        <v>126243742</v>
       </c>
       <c r="B28" t="n">
         <v>78973</v>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438805</v>
+        <v>438885</v>
       </c>
       <c r="R28" t="n">
-        <v>6783685</v>
+        <v>6783710</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3423,10 +3423,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126243148</v>
+        <v>126243342</v>
       </c>
       <c r="B29" t="n">
-        <v>78973</v>
+        <v>82785</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3434,21 +3434,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438785</v>
+        <v>438767</v>
       </c>
       <c r="R29" t="n">
-        <v>6783487</v>
+        <v>6783455</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3524,38 +3524,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126243647</v>
+        <v>126244253</v>
       </c>
       <c r="B30" t="n">
-        <v>97221</v>
+        <v>82785</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3563,10 +3562,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438790</v>
+        <v>438791</v>
       </c>
       <c r="R30" t="n">
-        <v>6783649</v>
+        <v>6783795</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3626,10 +3625,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126243342</v>
+        <v>126243348</v>
       </c>
       <c r="B31" t="n">
-        <v>82785</v>
+        <v>79005</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3637,21 +3636,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3727,10 +3726,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126244253</v>
+        <v>126243738</v>
       </c>
       <c r="B32" t="n">
-        <v>82785</v>
+        <v>79005</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3738,21 +3737,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3765,10 +3764,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438791</v>
+        <v>438885</v>
       </c>
       <c r="R32" t="n">
-        <v>6783795</v>
+        <v>6783710</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3828,37 +3827,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126243742</v>
+        <v>126243647</v>
       </c>
       <c r="B33" t="n">
-        <v>78973</v>
+        <v>97223</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>438885</v>
+        <v>438790</v>
       </c>
       <c r="R33" t="n">
-        <v>6783710</v>
+        <v>6783649</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3929,32 +3929,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126243379</v>
+        <v>126244571</v>
       </c>
       <c r="B34" t="n">
-        <v>79059</v>
+        <v>82785</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438694</v>
+        <v>438751</v>
       </c>
       <c r="R34" t="n">
-        <v>6783458</v>
+        <v>6783884</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4030,38 +4030,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126244106</v>
+        <v>126244328</v>
       </c>
       <c r="B35" t="n">
-        <v>98364</v>
+        <v>82785</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4069,10 +4068,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>438782</v>
+        <v>438584</v>
       </c>
       <c r="R35" t="n">
-        <v>6783777</v>
+        <v>6783774</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4099,12 +4098,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4132,32 +4131,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126244571</v>
+        <v>126243379</v>
       </c>
       <c r="B36" t="n">
-        <v>82785</v>
+        <v>79059</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>6450</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4170,10 +4169,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>438751</v>
+        <v>438694</v>
       </c>
       <c r="R36" t="n">
-        <v>6783884</v>
+        <v>6783458</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4200,12 +4199,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4233,37 +4232,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126244328</v>
+        <v>126244106</v>
       </c>
       <c r="B37" t="n">
-        <v>82785</v>
+        <v>98366</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>438584</v>
+        <v>438782</v>
       </c>
       <c r="R37" t="n">
-        <v>6783774</v>
+        <v>6783777</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4301,12 +4301,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4334,10 +4334,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126244026</v>
+        <v>126243450</v>
       </c>
       <c r="B38" t="n">
-        <v>98364</v>
+        <v>91203</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4345,27 +4345,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4373,10 +4372,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>438902</v>
+        <v>438740</v>
       </c>
       <c r="R38" t="n">
-        <v>6783843</v>
+        <v>6783462</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4436,10 +4435,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126243450</v>
+        <v>126243521</v>
       </c>
       <c r="B39" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4474,10 +4473,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>438740</v>
+        <v>438845</v>
       </c>
       <c r="R39" t="n">
-        <v>6783462</v>
+        <v>6783696</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4537,32 +4536,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126243521</v>
+        <v>126242981</v>
       </c>
       <c r="B40" t="n">
-        <v>91201</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4575,10 +4574,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>438845</v>
+        <v>438894</v>
       </c>
       <c r="R40" t="n">
-        <v>6783696</v>
+        <v>6783561</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4638,37 +4637,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126242981</v>
+        <v>126244026</v>
       </c>
       <c r="B41" t="n">
-        <v>78973</v>
+        <v>98366</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>438894</v>
+        <v>438902</v>
       </c>
       <c r="R41" t="n">
-        <v>6783561</v>
+        <v>6783843</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4739,35 +4739,39 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126244589</v>
+        <v>126243702</v>
       </c>
       <c r="B42" t="n">
-        <v>98364</v>
+        <v>98345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -4778,10 +4782,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>438824</v>
+        <v>438786</v>
       </c>
       <c r="R42" t="n">
-        <v>6783885</v>
+        <v>6783704</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4808,12 +4812,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4841,39 +4845,35 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126243702</v>
+        <v>126244589</v>
       </c>
       <c r="B43" t="n">
-        <v>98343</v>
+        <v>98366</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
@@ -4884,10 +4884,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>438786</v>
+        <v>438824</v>
       </c>
       <c r="R43" t="n">
-        <v>6783704</v>
+        <v>6783885</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4914,12 +4914,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4950,7 +4950,7 @@
         <v>126243995</v>
       </c>
       <c r="B44" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5667,10 +5667,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126244009</v>
+        <v>126243499</v>
       </c>
       <c r="B51" t="n">
-        <v>78973</v>
+        <v>82785</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5678,21 +5678,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>438925</v>
+        <v>438858</v>
       </c>
       <c r="R51" t="n">
-        <v>6783804</v>
+        <v>6783695</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5869,10 +5869,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126243332</v>
+        <v>126242940</v>
       </c>
       <c r="B53" t="n">
-        <v>78973</v>
+        <v>57649</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5880,26 +5880,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -5907,10 +5912,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>438770</v>
+        <v>438898</v>
       </c>
       <c r="R53" t="n">
-        <v>6783484</v>
+        <v>6783622</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5951,7 +5956,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5970,10 +5974,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126242940</v>
+        <v>126244009</v>
       </c>
       <c r="B54" t="n">
-        <v>57649</v>
+        <v>78973</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5981,31 +5985,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6013,10 +6012,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>438898</v>
+        <v>438925</v>
       </c>
       <c r="R54" t="n">
-        <v>6783622</v>
+        <v>6783804</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6057,6 +6056,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6075,10 +6075,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126243499</v>
+        <v>126243332</v>
       </c>
       <c r="B55" t="n">
-        <v>82785</v>
+        <v>78973</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6086,21 +6086,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6113,10 +6113,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>438858</v>
+        <v>438770</v>
       </c>
       <c r="R55" t="n">
-        <v>6783695</v>
+        <v>6783484</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6378,42 +6378,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126243641</v>
+        <v>126243462</v>
       </c>
       <c r="B58" t="n">
-        <v>98364</v>
+        <v>78973</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6421,10 +6416,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>438790</v>
+        <v>438777</v>
       </c>
       <c r="R58" t="n">
-        <v>6783649</v>
+        <v>6783527</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6484,10 +6479,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126243617</v>
+        <v>126243351</v>
       </c>
       <c r="B59" t="n">
-        <v>91236</v>
+        <v>78973</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6495,21 +6490,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6522,10 +6517,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>438797</v>
+        <v>438767</v>
       </c>
       <c r="R59" t="n">
-        <v>6783670</v>
+        <v>6783455</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6585,10 +6580,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126244052</v>
+        <v>126243986</v>
       </c>
       <c r="B60" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6596,21 +6591,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6623,10 +6618,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>438821</v>
+        <v>438947</v>
       </c>
       <c r="R60" t="n">
-        <v>6783854</v>
+        <v>6783782</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6686,10 +6681,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126243462</v>
+        <v>126243823</v>
       </c>
       <c r="B61" t="n">
-        <v>78973</v>
+        <v>82785</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6697,21 +6692,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6724,10 +6719,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>438777</v>
+        <v>438911</v>
       </c>
       <c r="R61" t="n">
-        <v>6783527</v>
+        <v>6783821</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6787,46 +6782,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126243492</v>
+        <v>126244052</v>
       </c>
       <c r="B62" t="n">
-        <v>56844</v>
+        <v>79591</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -6834,10 +6820,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>438871</v>
+        <v>438821</v>
       </c>
       <c r="R62" t="n">
-        <v>6783612</v>
+        <v>6783854</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6872,17 +6858,13 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Den tog ett s.k sandbad i sandblottan efter en rofyllda.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -6901,37 +6883,46 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126243351</v>
+        <v>126243492</v>
       </c>
       <c r="B63" t="n">
-        <v>78973</v>
+        <v>56844</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6939,10 +6930,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>438767</v>
+        <v>438871</v>
       </c>
       <c r="R63" t="n">
-        <v>6783455</v>
+        <v>6783612</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6977,13 +6968,17 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Den tog ett s.k sandbad i sandblottan efter en rofyllda.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7002,10 +6997,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126243986</v>
+        <v>126243617</v>
       </c>
       <c r="B64" t="n">
-        <v>78973</v>
+        <v>91238</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7013,21 +7008,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7040,10 +7035,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>438947</v>
+        <v>438797</v>
       </c>
       <c r="R64" t="n">
-        <v>6783782</v>
+        <v>6783670</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7103,10 +7098,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126244294</v>
+        <v>126243641</v>
       </c>
       <c r="B65" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7131,7 +7126,11 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
@@ -7142,10 +7141,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>438723</v>
+        <v>438790</v>
       </c>
       <c r="R65" t="n">
-        <v>6783752</v>
+        <v>6783649</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7172,12 +7171,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7205,37 +7204,38 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126243823</v>
+        <v>126244294</v>
       </c>
       <c r="B66" t="n">
-        <v>82785</v>
+        <v>98366</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>438911</v>
+        <v>438723</v>
       </c>
       <c r="R66" t="n">
-        <v>6783821</v>
+        <v>6783752</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7273,12 +7273,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7309,7 +7309,7 @@
         <v>126243259</v>
       </c>
       <c r="B67" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7407,10 +7407,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126242798</v>
+        <v>126244312</v>
       </c>
       <c r="B68" t="n">
-        <v>57649</v>
+        <v>56835</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7418,16 +7418,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7435,12 +7435,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -7450,10 +7462,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>438938</v>
+        <v>438654</v>
       </c>
       <c r="R68" t="n">
-        <v>6783650</v>
+        <v>6783741</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7480,17 +7492,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Mycket hackspår i den ca 160 åriga naturskogen</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7618,38 +7625,42 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126244077</v>
+        <v>126242798</v>
       </c>
       <c r="B70" t="n">
-        <v>98364</v>
+        <v>57649</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7657,10 +7668,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>438852</v>
+        <v>438938</v>
       </c>
       <c r="R70" t="n">
-        <v>6783837</v>
+        <v>6783650</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7695,13 +7706,17 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Mycket hackspår i den ca 160 åriga naturskogen</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7720,54 +7735,38 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126244312</v>
+        <v>126244077</v>
       </c>
       <c r="B71" t="n">
-        <v>56835</v>
+        <v>98366</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7775,10 +7774,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>438654</v>
+        <v>438852</v>
       </c>
       <c r="R71" t="n">
-        <v>6783741</v>
+        <v>6783837</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7805,12 +7804,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7819,6 +7818,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7837,37 +7837,38 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126243314</v>
+        <v>126244337</v>
       </c>
       <c r="B72" t="n">
-        <v>91823</v>
+        <v>98263</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1179</v>
+        <v>223591</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7875,10 +7876,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>438816</v>
+        <v>438574</v>
       </c>
       <c r="R72" t="n">
-        <v>6783530</v>
+        <v>6783811</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7905,12 +7906,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7938,10 +7939,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126243042</v>
+        <v>126244274</v>
       </c>
       <c r="B73" t="n">
-        <v>79052</v>
+        <v>82785</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7949,21 +7950,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7976,10 +7977,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>438848</v>
+        <v>438776</v>
       </c>
       <c r="R73" t="n">
-        <v>6783520</v>
+        <v>6783788</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8039,10 +8040,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126244274</v>
+        <v>126243042</v>
       </c>
       <c r="B74" t="n">
-        <v>82785</v>
+        <v>79052</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8050,21 +8051,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8077,10 +8078,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>438776</v>
+        <v>438848</v>
       </c>
       <c r="R74" t="n">
-        <v>6783788</v>
+        <v>6783520</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8140,32 +8141,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126243459</v>
+        <v>126243314</v>
       </c>
       <c r="B75" t="n">
-        <v>79005</v>
+        <v>91825</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>1179</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8178,10 +8179,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>438777</v>
+        <v>438816</v>
       </c>
       <c r="R75" t="n">
-        <v>6783527</v>
+        <v>6783530</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8241,38 +8242,37 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126244337</v>
+        <v>126243459</v>
       </c>
       <c r="B76" t="n">
-        <v>98261</v>
+        <v>79005</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>223591</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>438574</v>
+        <v>438777</v>
       </c>
       <c r="R76" t="n">
-        <v>6783811</v>
+        <v>6783527</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8310,12 +8310,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8447,7 +8447,7 @@
         <v>126243991</v>
       </c>
       <c r="B78" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8545,10 +8545,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126243586</v>
+        <v>126243363</v>
       </c>
       <c r="B79" t="n">
-        <v>57649</v>
+        <v>79591</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8556,31 +8556,26 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8588,10 +8583,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>438805</v>
+        <v>438739</v>
       </c>
       <c r="R79" t="n">
-        <v>6783685</v>
+        <v>6783474</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8632,6 +8627,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8755,10 +8751,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126243363</v>
+        <v>126243586</v>
       </c>
       <c r="B81" t="n">
-        <v>79591</v>
+        <v>57649</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8766,26 +8762,31 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8793,10 +8794,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>438739</v>
+        <v>438805</v>
       </c>
       <c r="R81" t="n">
-        <v>6783474</v>
+        <v>6783685</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8837,7 +8838,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8856,38 +8856,42 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126243816</v>
+        <v>126243732</v>
       </c>
       <c r="B82" t="n">
-        <v>98261</v>
+        <v>57649</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>223591</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -8895,10 +8899,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>438886</v>
+        <v>438882</v>
       </c>
       <c r="R82" t="n">
-        <v>6783805</v>
+        <v>6783685</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8939,7 +8943,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8958,32 +8961,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126243505</v>
+        <v>126243608</v>
       </c>
       <c r="B83" t="n">
-        <v>80111</v>
+        <v>91596</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6463</v>
+        <v>2062</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8996,10 +8999,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>438858</v>
+        <v>438797</v>
       </c>
       <c r="R83" t="n">
-        <v>6783695</v>
+        <v>6783670</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9062,7 +9065,7 @@
         <v>126243220</v>
       </c>
       <c r="B84" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9261,10 +9264,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126243191</v>
+        <v>126243505</v>
       </c>
       <c r="B86" t="n">
-        <v>79059</v>
+        <v>80111</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9272,21 +9275,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6450</v>
+        <v>6463</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9299,10 +9302,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>438777</v>
+        <v>438858</v>
       </c>
       <c r="R86" t="n">
-        <v>6783503</v>
+        <v>6783695</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9362,42 +9365,37 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126243732</v>
+        <v>126243191</v>
       </c>
       <c r="B87" t="n">
-        <v>57649</v>
+        <v>79059</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>6450</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9405,10 +9403,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>438882</v>
+        <v>438777</v>
       </c>
       <c r="R87" t="n">
-        <v>6783685</v>
+        <v>6783503</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9449,6 +9447,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9470,7 +9469,7 @@
         <v>126243676</v>
       </c>
       <c r="B88" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9573,37 +9572,38 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126243608</v>
+        <v>126243816</v>
       </c>
       <c r="B89" t="n">
-        <v>91594</v>
+        <v>98263</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2062</v>
+        <v>223591</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9611,10 +9611,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>438797</v>
+        <v>438886</v>
       </c>
       <c r="R89" t="n">
-        <v>6783670</v>
+        <v>6783805</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9787,7 +9787,7 @@
         <v>126249487</v>
       </c>
       <c r="B91" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9891,38 +9891,37 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126244320</v>
+        <v>126243503</v>
       </c>
       <c r="B92" t="n">
-        <v>98261</v>
+        <v>78973</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>223591</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -9930,10 +9929,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>438606</v>
+        <v>438858</v>
       </c>
       <c r="R92" t="n">
-        <v>6783759</v>
+        <v>6783695</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9960,12 +9959,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9993,39 +9992,42 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126244082</v>
+        <v>126243415</v>
       </c>
       <c r="B93" t="n">
-        <v>5176</v>
+        <v>57649</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10033,10 +10035,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>438809</v>
+        <v>438722</v>
       </c>
       <c r="R93" t="n">
-        <v>6783806</v>
+        <v>6783470</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10077,7 +10079,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10096,37 +10097,39 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126243447</v>
+        <v>126244082</v>
       </c>
       <c r="B94" t="n">
-        <v>82785</v>
+        <v>5176</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1312</v>
+        <v>100526</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10134,10 +10137,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>438740</v>
+        <v>438809</v>
       </c>
       <c r="R94" t="n">
-        <v>6783462</v>
+        <v>6783806</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10197,10 +10200,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126243415</v>
+        <v>126243447</v>
       </c>
       <c r="B95" t="n">
-        <v>57649</v>
+        <v>82785</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10208,31 +10211,26 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10240,10 +10238,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>438722</v>
+        <v>438740</v>
       </c>
       <c r="R95" t="n">
-        <v>6783470</v>
+        <v>6783462</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10284,6 +10282,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10302,37 +10301,38 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126243503</v>
+        <v>126244320</v>
       </c>
       <c r="B96" t="n">
-        <v>78973</v>
+        <v>98263</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>223591</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10340,10 +10340,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>438858</v>
+        <v>438606</v>
       </c>
       <c r="R96" t="n">
-        <v>6783695</v>
+        <v>6783759</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10370,12 +10370,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10406,7 +10406,7 @@
         <v>126243973</v>
       </c>
       <c r="B97" t="n">
-        <v>88645</v>
+        <v>88647</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -1806,37 +1806,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126243933</v>
+        <v>126243784</v>
       </c>
       <c r="B13" t="n">
-        <v>82785</v>
+        <v>98366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1844,10 +1845,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438928</v>
+        <v>438893</v>
       </c>
       <c r="R13" t="n">
-        <v>6783763</v>
+        <v>6783787</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1907,10 +1908,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126243682</v>
+        <v>126243933</v>
       </c>
       <c r="B14" t="n">
-        <v>88647</v>
+        <v>82785</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1918,21 +1919,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1945,10 +1946,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438813</v>
+        <v>438928</v>
       </c>
       <c r="R14" t="n">
-        <v>6783722</v>
+        <v>6783763</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2008,10 +2009,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126243724</v>
+        <v>126243682</v>
       </c>
       <c r="B15" t="n">
-        <v>91859</v>
+        <v>88647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2019,21 +2020,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5454</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438883</v>
+        <v>438813</v>
       </c>
       <c r="R15" t="n">
-        <v>6783662</v>
+        <v>6783722</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2109,38 +2110,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126243784</v>
+        <v>126243724</v>
       </c>
       <c r="B16" t="n">
-        <v>98366</v>
+        <v>91859</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>5454</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438893</v>
+        <v>438883</v>
       </c>
       <c r="R16" t="n">
-        <v>6783787</v>
+        <v>6783662</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -4739,39 +4739,35 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126243702</v>
+        <v>126244589</v>
       </c>
       <c r="B42" t="n">
-        <v>98345</v>
+        <v>98366</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -4782,10 +4778,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>438786</v>
+        <v>438824</v>
       </c>
       <c r="R42" t="n">
-        <v>6783704</v>
+        <v>6783885</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4812,12 +4808,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4845,7 +4841,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126244589</v>
+        <v>126243995</v>
       </c>
       <c r="B43" t="n">
         <v>98366</v>
@@ -4884,10 +4880,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>438824</v>
+        <v>438953</v>
       </c>
       <c r="R43" t="n">
-        <v>6783885</v>
+        <v>6783788</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4914,12 +4910,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4947,35 +4943,39 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126243995</v>
+        <v>126243702</v>
       </c>
       <c r="B44" t="n">
-        <v>98366</v>
+        <v>98345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>438953</v>
+        <v>438786</v>
       </c>
       <c r="R44" t="n">
-        <v>6783788</v>
+        <v>6783704</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5263,10 +5263,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126243010</v>
+        <v>126243370</v>
       </c>
       <c r="B47" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5274,21 +5274,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>438852</v>
+        <v>438714</v>
       </c>
       <c r="R47" t="n">
-        <v>6783530</v>
+        <v>6783492</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5364,10 +5364,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126243233</v>
+        <v>126244099</v>
       </c>
       <c r="B48" t="n">
-        <v>78973</v>
+        <v>82785</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5375,21 +5375,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5402,10 +5402,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>438775</v>
+        <v>438804</v>
       </c>
       <c r="R48" t="n">
-        <v>6783504</v>
+        <v>6783800</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5465,10 +5465,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126243370</v>
+        <v>126243010</v>
       </c>
       <c r="B49" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5476,21 +5476,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>438714</v>
+        <v>438852</v>
       </c>
       <c r="R49" t="n">
-        <v>6783492</v>
+        <v>6783530</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5566,10 +5566,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126244099</v>
+        <v>126243233</v>
       </c>
       <c r="B50" t="n">
-        <v>82785</v>
+        <v>78973</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5577,21 +5577,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>438804</v>
+        <v>438775</v>
       </c>
       <c r="R50" t="n">
-        <v>6783800</v>
+        <v>6783504</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5667,10 +5667,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126243499</v>
+        <v>126244009</v>
       </c>
       <c r="B51" t="n">
-        <v>82785</v>
+        <v>78973</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5678,21 +5678,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>438858</v>
+        <v>438925</v>
       </c>
       <c r="R51" t="n">
-        <v>6783695</v>
+        <v>6783804</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5768,32 +5768,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126243769</v>
+        <v>126243332</v>
       </c>
       <c r="B52" t="n">
-        <v>78336</v>
+        <v>78973</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>438898</v>
+        <v>438770</v>
       </c>
       <c r="R52" t="n">
-        <v>6783784</v>
+        <v>6783484</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5869,10 +5869,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126242940</v>
+        <v>126243713</v>
       </c>
       <c r="B53" t="n">
-        <v>57649</v>
+        <v>78973</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5880,31 +5880,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -5912,10 +5907,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>438898</v>
+        <v>438875</v>
       </c>
       <c r="R53" t="n">
-        <v>6783622</v>
+        <v>6783718</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5956,6 +5951,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5974,10 +5970,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126244009</v>
+        <v>126243499</v>
       </c>
       <c r="B54" t="n">
-        <v>78973</v>
+        <v>82785</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5985,21 +5981,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6012,10 +6008,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>438925</v>
+        <v>438858</v>
       </c>
       <c r="R54" t="n">
-        <v>6783804</v>
+        <v>6783695</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6075,32 +6071,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126243332</v>
+        <v>126243769</v>
       </c>
       <c r="B55" t="n">
-        <v>78973</v>
+        <v>78336</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6113,10 +6109,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>438770</v>
+        <v>438898</v>
       </c>
       <c r="R55" t="n">
-        <v>6783484</v>
+        <v>6783784</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6176,10 +6172,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126243713</v>
+        <v>126242940</v>
       </c>
       <c r="B56" t="n">
-        <v>78973</v>
+        <v>57649</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6187,26 +6183,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6214,10 +6215,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>438875</v>
+        <v>438898</v>
       </c>
       <c r="R56" t="n">
-        <v>6783718</v>
+        <v>6783622</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6258,7 +6259,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6277,10 +6277,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126243980</v>
+        <v>126244052</v>
       </c>
       <c r="B57" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6288,21 +6288,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>438928</v>
+        <v>438821</v>
       </c>
       <c r="R57" t="n">
-        <v>6783763</v>
+        <v>6783854</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6378,37 +6378,46 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126243462</v>
+        <v>126243492</v>
       </c>
       <c r="B58" t="n">
-        <v>78973</v>
+        <v>56844</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6416,10 +6425,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>438777</v>
+        <v>438871</v>
       </c>
       <c r="R58" t="n">
-        <v>6783527</v>
+        <v>6783612</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6454,13 +6463,17 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Den tog ett s.k sandbad i sandblottan efter en rofyllda.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6479,10 +6492,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126243351</v>
+        <v>126243823</v>
       </c>
       <c r="B59" t="n">
-        <v>78973</v>
+        <v>82785</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6490,21 +6503,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6517,10 +6530,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>438767</v>
+        <v>438911</v>
       </c>
       <c r="R59" t="n">
-        <v>6783455</v>
+        <v>6783821</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6580,10 +6593,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126243986</v>
+        <v>126243617</v>
       </c>
       <c r="B60" t="n">
-        <v>78973</v>
+        <v>91238</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6591,21 +6604,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6618,10 +6631,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>438947</v>
+        <v>438797</v>
       </c>
       <c r="R60" t="n">
-        <v>6783782</v>
+        <v>6783670</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6681,10 +6694,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126243823</v>
+        <v>126243980</v>
       </c>
       <c r="B61" t="n">
-        <v>82785</v>
+        <v>78973</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6692,21 +6705,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6719,10 +6732,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>438911</v>
+        <v>438928</v>
       </c>
       <c r="R61" t="n">
-        <v>6783821</v>
+        <v>6783763</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6782,10 +6795,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126244052</v>
+        <v>126243462</v>
       </c>
       <c r="B62" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6793,21 +6806,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6820,10 +6833,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>438821</v>
+        <v>438777</v>
       </c>
       <c r="R62" t="n">
-        <v>6783854</v>
+        <v>6783527</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6883,46 +6896,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126243492</v>
+        <v>126243351</v>
       </c>
       <c r="B63" t="n">
-        <v>56844</v>
+        <v>78973</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6930,10 +6934,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>438871</v>
+        <v>438767</v>
       </c>
       <c r="R63" t="n">
-        <v>6783612</v>
+        <v>6783455</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6968,17 +6972,13 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Den tog ett s.k sandbad i sandblottan efter en rofyllda.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6997,10 +6997,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126243617</v>
+        <v>126243986</v>
       </c>
       <c r="B64" t="n">
-        <v>91238</v>
+        <v>78973</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7008,21 +7008,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7035,10 +7035,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>438797</v>
+        <v>438947</v>
       </c>
       <c r="R64" t="n">
-        <v>6783670</v>
+        <v>6783782</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7306,10 +7306,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126243259</v>
+        <v>126244077</v>
       </c>
       <c r="B67" t="n">
-        <v>91203</v>
+        <v>98366</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7317,26 +7317,27 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7344,10 +7345,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>438790</v>
+        <v>438852</v>
       </c>
       <c r="R67" t="n">
-        <v>6783520</v>
+        <v>6783837</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7407,10 +7408,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126244312</v>
+        <v>126242918</v>
       </c>
       <c r="B68" t="n">
-        <v>56835</v>
+        <v>79005</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7418,43 +7419,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102612</v>
+        <v>185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7462,10 +7446,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>438654</v>
+        <v>438917</v>
       </c>
       <c r="R68" t="n">
-        <v>6783741</v>
+        <v>6783626</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7492,12 +7476,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7506,6 +7490,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7524,10 +7509,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126242918</v>
+        <v>126242798</v>
       </c>
       <c r="B69" t="n">
-        <v>79005</v>
+        <v>57649</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7535,26 +7520,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7562,10 +7552,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>438917</v>
+        <v>438938</v>
       </c>
       <c r="R69" t="n">
-        <v>6783626</v>
+        <v>6783650</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7600,13 +7590,17 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Mycket hackspår i den ca 160 åriga naturskogen</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7625,42 +7619,37 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126242798</v>
+        <v>126243259</v>
       </c>
       <c r="B70" t="n">
-        <v>57649</v>
+        <v>91203</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7668,10 +7657,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>438938</v>
+        <v>438790</v>
       </c>
       <c r="R70" t="n">
-        <v>6783650</v>
+        <v>6783520</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7706,17 +7695,13 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Mycket hackspår i den ca 160 åriga naturskogen</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7735,38 +7720,54 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126244077</v>
+        <v>126244312</v>
       </c>
       <c r="B71" t="n">
-        <v>98366</v>
+        <v>56835</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>102612</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7774,10 +7775,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>438852</v>
+        <v>438654</v>
       </c>
       <c r="R71" t="n">
-        <v>6783837</v>
+        <v>6783741</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7804,12 +7805,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7818,7 +7819,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8444,10 +8444,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126243991</v>
+        <v>126243208</v>
       </c>
       <c r="B78" t="n">
-        <v>91256</v>
+        <v>57649</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8455,26 +8455,31 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8482,10 +8487,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>438953</v>
+        <v>438777</v>
       </c>
       <c r="R78" t="n">
-        <v>6783776</v>
+        <v>6783503</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8526,7 +8531,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8545,10 +8549,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126243363</v>
+        <v>126243586</v>
       </c>
       <c r="B79" t="n">
-        <v>79591</v>
+        <v>57649</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8556,26 +8560,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8583,10 +8592,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>438739</v>
+        <v>438805</v>
       </c>
       <c r="R79" t="n">
-        <v>6783474</v>
+        <v>6783685</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8627,7 +8636,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8646,10 +8654,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126243208</v>
+        <v>126243991</v>
       </c>
       <c r="B80" t="n">
-        <v>57649</v>
+        <v>91256</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8657,31 +8665,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -8689,10 +8692,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438777</v>
+        <v>438953</v>
       </c>
       <c r="R80" t="n">
-        <v>6783503</v>
+        <v>6783776</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8733,6 +8736,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8751,10 +8755,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126243586</v>
+        <v>126243363</v>
       </c>
       <c r="B81" t="n">
-        <v>57649</v>
+        <v>79591</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8762,31 +8766,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8794,10 +8793,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>438805</v>
+        <v>438739</v>
       </c>
       <c r="R81" t="n">
-        <v>6783685</v>
+        <v>6783474</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8838,6 +8837,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126223492</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>126243187</v>
       </c>
       <c r="B4" t="n">
-        <v>80948</v>
+        <v>80952</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,42 +990,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126242965</v>
+        <v>126243811</v>
       </c>
       <c r="B5" t="n">
-        <v>57649</v>
+        <v>98370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1033,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438888</v>
+        <v>438886</v>
       </c>
       <c r="R5" t="n">
-        <v>6783584</v>
+        <v>6783805</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1077,6 +1073,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1095,39 +1092,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126244085</v>
+        <v>126243254</v>
       </c>
       <c r="B6" t="n">
-        <v>4772</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1135,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438809</v>
+        <v>438790</v>
       </c>
       <c r="R6" t="n">
-        <v>6783806</v>
+        <v>6783520</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126243254</v>
+        <v>126242851</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1236,10 +1231,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438790</v>
+        <v>438926</v>
       </c>
       <c r="R7" t="n">
-        <v>6783520</v>
+        <v>6783631</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1299,10 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126242851</v>
+        <v>126243055</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438926</v>
+        <v>438823</v>
       </c>
       <c r="R8" t="n">
-        <v>6783631</v>
+        <v>6783513</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1400,10 +1395,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126243055</v>
+        <v>126242965</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>57653</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1411,26 +1406,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438823</v>
+        <v>438888</v>
       </c>
       <c r="R9" t="n">
-        <v>6783513</v>
+        <v>6783584</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1482,7 +1482,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1501,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126243811</v>
+        <v>126244085</v>
       </c>
       <c r="B10" t="n">
-        <v>98366</v>
+        <v>4772</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1512,27 +1511,28 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>100299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1540,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438886</v>
+        <v>438809</v>
       </c>
       <c r="R10" t="n">
-        <v>6783805</v>
+        <v>6783806</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1606,7 +1606,7 @@
         <v>126244046</v>
       </c>
       <c r="B11" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>126243614</v>
       </c>
       <c r="B12" t="n">
-        <v>88647</v>
+        <v>88651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,38 +1806,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126243784</v>
+        <v>126243682</v>
       </c>
       <c r="B13" t="n">
-        <v>98366</v>
+        <v>88651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1845,10 +1844,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438893</v>
+        <v>438813</v>
       </c>
       <c r="R13" t="n">
-        <v>6783787</v>
+        <v>6783722</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1911,7 +1910,7 @@
         <v>126243933</v>
       </c>
       <c r="B14" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,37 +2008,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126243682</v>
+        <v>126243784</v>
       </c>
       <c r="B15" t="n">
-        <v>88647</v>
+        <v>98370</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438813</v>
+        <v>438893</v>
       </c>
       <c r="R15" t="n">
-        <v>6783722</v>
+        <v>6783787</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2113,7 +2113,7 @@
         <v>126243724</v>
       </c>
       <c r="B16" t="n">
-        <v>91859</v>
+        <v>91863</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>126244296</v>
       </c>
       <c r="B17" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>126244055</v>
       </c>
       <c r="B18" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>126243709</v>
       </c>
       <c r="B19" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>126244007</v>
       </c>
       <c r="B20" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126243757</v>
+        <v>126243527</v>
       </c>
       <c r="B21" t="n">
-        <v>79052</v>
+        <v>91256</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438889</v>
+        <v>438826</v>
       </c>
       <c r="R21" t="n">
-        <v>6783762</v>
+        <v>6783693</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2716,32 +2716,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126243527</v>
+        <v>126243075</v>
       </c>
       <c r="B22" t="n">
-        <v>91252</v>
+        <v>79063</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1204</v>
+        <v>6450</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438826</v>
+        <v>438799</v>
       </c>
       <c r="R22" t="n">
-        <v>6783693</v>
+        <v>6783496</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2820,7 +2820,7 @@
         <v>126242913</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2918,32 +2918,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126243075</v>
+        <v>126243757</v>
       </c>
       <c r="B24" t="n">
-        <v>79059</v>
+        <v>79056</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6450</v>
+        <v>864</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>438799</v>
+        <v>438889</v>
       </c>
       <c r="R24" t="n">
-        <v>6783496</v>
+        <v>6783762</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3022,7 +3022,7 @@
         <v>126243439</v>
       </c>
       <c r="B25" t="n">
-        <v>88647</v>
+        <v>88651</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>126243565</v>
       </c>
       <c r="B26" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3224,7 +3224,7 @@
         <v>126243148</v>
       </c>
       <c r="B27" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         <v>126243742</v>
       </c>
       <c r="B28" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3423,10 +3423,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126243342</v>
+        <v>126243348</v>
       </c>
       <c r="B29" t="n">
-        <v>82785</v>
+        <v>79009</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3434,21 +3434,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3524,10 +3524,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126244253</v>
+        <v>126243738</v>
       </c>
       <c r="B30" t="n">
-        <v>82785</v>
+        <v>79009</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3535,21 +3535,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3562,10 +3562,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438791</v>
+        <v>438885</v>
       </c>
       <c r="R30" t="n">
-        <v>6783795</v>
+        <v>6783710</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3625,10 +3625,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126243348</v>
+        <v>126243342</v>
       </c>
       <c r="B31" t="n">
-        <v>79005</v>
+        <v>82789</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3636,21 +3636,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3726,10 +3726,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126243738</v>
+        <v>126244253</v>
       </c>
       <c r="B32" t="n">
-        <v>79005</v>
+        <v>82789</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3737,21 +3737,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3764,10 +3764,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438885</v>
+        <v>438791</v>
       </c>
       <c r="R32" t="n">
-        <v>6783710</v>
+        <v>6783795</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3830,7 +3830,7 @@
         <v>126243647</v>
       </c>
       <c r="B33" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3929,37 +3929,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126244571</v>
+        <v>126244106</v>
       </c>
       <c r="B34" t="n">
-        <v>82785</v>
+        <v>98370</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3967,10 +3968,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438751</v>
+        <v>438782</v>
       </c>
       <c r="R34" t="n">
-        <v>6783884</v>
+        <v>6783777</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3997,12 +3998,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4030,10 +4031,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126244328</v>
+        <v>126244571</v>
       </c>
       <c r="B35" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4068,10 +4069,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>438584</v>
+        <v>438751</v>
       </c>
       <c r="R35" t="n">
-        <v>6783774</v>
+        <v>6783884</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4131,32 +4132,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126243379</v>
+        <v>126244328</v>
       </c>
       <c r="B36" t="n">
-        <v>79059</v>
+        <v>82789</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4169,10 +4170,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>438694</v>
+        <v>438584</v>
       </c>
       <c r="R36" t="n">
-        <v>6783458</v>
+        <v>6783774</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4199,12 +4200,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4232,10 +4233,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126244106</v>
+        <v>126243379</v>
       </c>
       <c r="B37" t="n">
-        <v>98366</v>
+        <v>79063</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4243,27 +4244,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221952</v>
+        <v>6450</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>438782</v>
+        <v>438694</v>
       </c>
       <c r="R37" t="n">
-        <v>6783777</v>
+        <v>6783458</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4334,10 +4334,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126243450</v>
+        <v>126244026</v>
       </c>
       <c r="B38" t="n">
-        <v>91203</v>
+        <v>98370</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4345,26 +4345,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4372,10 +4373,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>438740</v>
+        <v>438902</v>
       </c>
       <c r="R38" t="n">
-        <v>6783462</v>
+        <v>6783843</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4435,10 +4436,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126243521</v>
+        <v>126243450</v>
       </c>
       <c r="B39" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4473,10 +4474,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>438845</v>
+        <v>438740</v>
       </c>
       <c r="R39" t="n">
-        <v>6783696</v>
+        <v>6783462</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4536,32 +4537,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126242981</v>
+        <v>126243521</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>91207</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4574,10 +4575,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>438894</v>
+        <v>438845</v>
       </c>
       <c r="R40" t="n">
-        <v>6783561</v>
+        <v>6783696</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4637,38 +4638,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126244026</v>
+        <v>126242981</v>
       </c>
       <c r="B41" t="n">
-        <v>98366</v>
+        <v>78977</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>438902</v>
+        <v>438894</v>
       </c>
       <c r="R41" t="n">
-        <v>6783843</v>
+        <v>6783561</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4739,35 +4739,39 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126244589</v>
+        <v>126243702</v>
       </c>
       <c r="B42" t="n">
-        <v>98366</v>
+        <v>98349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -4778,10 +4782,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>438824</v>
+        <v>438786</v>
       </c>
       <c r="R42" t="n">
-        <v>6783885</v>
+        <v>6783704</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4808,12 +4812,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4841,10 +4845,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126243995</v>
+        <v>126244589</v>
       </c>
       <c r="B43" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4880,10 +4884,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>438953</v>
+        <v>438824</v>
       </c>
       <c r="R43" t="n">
-        <v>6783788</v>
+        <v>6783885</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4910,12 +4914,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4943,39 +4947,35 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126243702</v>
+        <v>126243995</v>
       </c>
       <c r="B44" t="n">
-        <v>98345</v>
+        <v>98370</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>438786</v>
+        <v>438953</v>
       </c>
       <c r="R44" t="n">
-        <v>6783704</v>
+        <v>6783788</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5052,7 +5052,7 @@
         <v>126243519</v>
       </c>
       <c r="B45" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>126244033</v>
       </c>
       <c r="B46" t="n">
-        <v>82785</v>
+        <v>82789</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5263,10 +5263,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126243370</v>
+        <v>126244099</v>
       </c>
       <c r="B47" t="n">
-        <v>79591</v>
+        <v>82789</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5274,21 +5274,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>438714</v>
+        <v>438804</v>
       </c>
       <c r="R47" t="n">
-        <v>6783492</v>
+        <v>6783800</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5364,10 +5364,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126244099</v>
+        <v>126243010</v>
       </c>
       <c r="B48" t="n">
-        <v>82785</v>
+        <v>78977</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5375,21 +5375,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5402,10 +5402,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>438804</v>
+        <v>438852</v>
       </c>
       <c r="R48" t="n">
-        <v>6783800</v>
+        <v>6783530</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5465,10 +5465,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126243010</v>
+        <v>126243233</v>
       </c>
       <c r="B49" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>438852</v>
+        <v>438775</v>
       </c>
       <c r="R49" t="n">
-        <v>6783530</v>
+        <v>6783504</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5566,10 +5566,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126243233</v>
+        <v>126243370</v>
       </c>
       <c r="B50" t="n">
-        <v>78973</v>
+        <v>79595</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5577,21 +5577,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>438775</v>
+        <v>438714</v>
       </c>
       <c r="R50" t="n">
-        <v>6783504</v>
+        <v>6783492</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5667,32 +5667,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126244009</v>
+        <v>126243769</v>
       </c>
       <c r="B51" t="n">
-        <v>78973</v>
+        <v>78340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>438925</v>
+        <v>438898</v>
       </c>
       <c r="R51" t="n">
-        <v>6783804</v>
+        <v>6783784</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5768,10 +5768,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126243332</v>
+        <v>126243499</v>
       </c>
       <c r="B52" t="n">
-        <v>78973</v>
+        <v>82789</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5779,21 +5779,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>438770</v>
+        <v>438858</v>
       </c>
       <c r="R52" t="n">
-        <v>6783484</v>
+        <v>6783695</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5869,10 +5869,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126243713</v>
+        <v>126244009</v>
       </c>
       <c r="B53" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5907,10 +5907,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>438875</v>
+        <v>438925</v>
       </c>
       <c r="R53" t="n">
-        <v>6783718</v>
+        <v>6783804</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5970,10 +5970,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126243499</v>
+        <v>126243332</v>
       </c>
       <c r="B54" t="n">
-        <v>82785</v>
+        <v>78977</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5981,21 +5981,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>438858</v>
+        <v>438770</v>
       </c>
       <c r="R54" t="n">
-        <v>6783695</v>
+        <v>6783484</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6071,32 +6071,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126243769</v>
+        <v>126243713</v>
       </c>
       <c r="B55" t="n">
-        <v>78336</v>
+        <v>78977</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6109,10 +6109,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>438898</v>
+        <v>438875</v>
       </c>
       <c r="R55" t="n">
-        <v>6783784</v>
+        <v>6783718</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6175,7 +6175,7 @@
         <v>126242940</v>
       </c>
       <c r="B56" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6277,10 +6277,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126244052</v>
+        <v>126243823</v>
       </c>
       <c r="B57" t="n">
-        <v>79591</v>
+        <v>82789</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6288,21 +6288,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>438821</v>
+        <v>438911</v>
       </c>
       <c r="R57" t="n">
-        <v>6783854</v>
+        <v>6783821</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6378,46 +6378,37 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126243492</v>
+        <v>126243980</v>
       </c>
       <c r="B58" t="n">
-        <v>56844</v>
+        <v>78977</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6425,10 +6416,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>438871</v>
+        <v>438928</v>
       </c>
       <c r="R58" t="n">
-        <v>6783612</v>
+        <v>6783763</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6463,17 +6454,13 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Den tog ett s.k sandbad i sandblottan efter en rofyllda.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6492,10 +6479,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126243823</v>
+        <v>126244052</v>
       </c>
       <c r="B59" t="n">
-        <v>82785</v>
+        <v>79595</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6503,21 +6490,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6530,10 +6517,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>438911</v>
+        <v>438821</v>
       </c>
       <c r="R59" t="n">
-        <v>6783821</v>
+        <v>6783854</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6593,10 +6580,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126243617</v>
+        <v>126243462</v>
       </c>
       <c r="B60" t="n">
-        <v>91238</v>
+        <v>78977</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6604,21 +6591,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6631,10 +6618,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>438797</v>
+        <v>438777</v>
       </c>
       <c r="R60" t="n">
-        <v>6783670</v>
+        <v>6783527</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6694,10 +6681,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126243980</v>
+        <v>126243351</v>
       </c>
       <c r="B61" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6732,10 +6719,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>438928</v>
+        <v>438767</v>
       </c>
       <c r="R61" t="n">
-        <v>6783763</v>
+        <v>6783455</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6795,10 +6782,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126243462</v>
+        <v>126243986</v>
       </c>
       <c r="B62" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6833,10 +6820,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>438777</v>
+        <v>438947</v>
       </c>
       <c r="R62" t="n">
-        <v>6783527</v>
+        <v>6783782</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6896,10 +6883,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126243351</v>
+        <v>126243617</v>
       </c>
       <c r="B63" t="n">
-        <v>78973</v>
+        <v>91242</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6907,21 +6894,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6934,10 +6921,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>438767</v>
+        <v>438797</v>
       </c>
       <c r="R63" t="n">
-        <v>6783455</v>
+        <v>6783670</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6997,37 +6984,46 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126243986</v>
+        <v>126243492</v>
       </c>
       <c r="B64" t="n">
-        <v>78973</v>
+        <v>56848</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7035,10 +7031,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>438947</v>
+        <v>438871</v>
       </c>
       <c r="R64" t="n">
-        <v>6783782</v>
+        <v>6783612</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7073,13 +7069,17 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Den tog ett s.k sandbad i sandblottan efter en rofyllda.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7101,7 +7101,7 @@
         <v>126243641</v>
       </c>
       <c r="B65" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>126244294</v>
       </c>
       <c r="B66" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7306,38 +7306,37 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126244077</v>
+        <v>126242918</v>
       </c>
       <c r="B67" t="n">
-        <v>98366</v>
+        <v>79009</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221952</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7345,10 +7344,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>438852</v>
+        <v>438917</v>
       </c>
       <c r="R67" t="n">
-        <v>6783837</v>
+        <v>6783626</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7408,32 +7407,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126242918</v>
+        <v>126243259</v>
       </c>
       <c r="B68" t="n">
-        <v>79005</v>
+        <v>91207</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7446,10 +7445,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>438917</v>
+        <v>438790</v>
       </c>
       <c r="R68" t="n">
-        <v>6783626</v>
+        <v>6783520</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7512,7 +7511,7 @@
         <v>126242798</v>
       </c>
       <c r="B69" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7619,37 +7618,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126243259</v>
+        <v>126244312</v>
       </c>
       <c r="B70" t="n">
-        <v>91203</v>
+        <v>56839</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7657,10 +7673,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>438790</v>
+        <v>438654</v>
       </c>
       <c r="R70" t="n">
-        <v>6783520</v>
+        <v>6783741</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7687,12 +7703,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7701,7 +7717,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7720,54 +7735,38 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126244312</v>
+        <v>126244077</v>
       </c>
       <c r="B71" t="n">
-        <v>56835</v>
+        <v>98370</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7775,10 +7774,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>438654</v>
+        <v>438852</v>
       </c>
       <c r="R71" t="n">
-        <v>6783741</v>
+        <v>6783837</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7805,12 +7804,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7819,6 +7818,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7837,38 +7837,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126244337</v>
+        <v>126243459</v>
       </c>
       <c r="B72" t="n">
-        <v>98263</v>
+        <v>79009</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>223591</v>
+        <v>185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7876,10 +7875,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>438574</v>
+        <v>438777</v>
       </c>
       <c r="R72" t="n">
-        <v>6783811</v>
+        <v>6783527</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7906,12 +7905,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7939,32 +7938,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126244274</v>
+        <v>126243314</v>
       </c>
       <c r="B73" t="n">
-        <v>82785</v>
+        <v>91829</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1312</v>
+        <v>1179</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7977,10 +7976,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>438776</v>
+        <v>438816</v>
       </c>
       <c r="R73" t="n">
-        <v>6783788</v>
+        <v>6783530</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8043,7 +8042,7 @@
         <v>126243042</v>
       </c>
       <c r="B74" t="n">
-        <v>79052</v>
+        <v>79056</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8141,32 +8140,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126243314</v>
+        <v>126244274</v>
       </c>
       <c r="B75" t="n">
-        <v>91825</v>
+        <v>82789</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1179</v>
+        <v>1312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8179,10 +8178,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>438816</v>
+        <v>438776</v>
       </c>
       <c r="R75" t="n">
-        <v>6783530</v>
+        <v>6783788</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8242,37 +8241,38 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126243459</v>
+        <v>126244337</v>
       </c>
       <c r="B76" t="n">
-        <v>79005</v>
+        <v>98267</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>223591</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>438777</v>
+        <v>438574</v>
       </c>
       <c r="R76" t="n">
-        <v>6783527</v>
+        <v>6783811</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8310,12 +8310,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8346,7 +8346,7 @@
         <v>126243070</v>
       </c>
       <c r="B77" t="n">
-        <v>79005</v>
+        <v>79009</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8444,10 +8444,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126243208</v>
+        <v>126243991</v>
       </c>
       <c r="B78" t="n">
-        <v>57649</v>
+        <v>91260</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8455,31 +8455,26 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8487,10 +8482,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>438777</v>
+        <v>438953</v>
       </c>
       <c r="R78" t="n">
-        <v>6783503</v>
+        <v>6783776</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8531,6 +8526,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8552,7 +8548,7 @@
         <v>126243586</v>
       </c>
       <c r="B79" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8654,10 +8650,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126243991</v>
+        <v>126243208</v>
       </c>
       <c r="B80" t="n">
-        <v>91256</v>
+        <v>57653</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8665,26 +8661,31 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -8692,10 +8693,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438953</v>
+        <v>438777</v>
       </c>
       <c r="R80" t="n">
-        <v>6783776</v>
+        <v>6783503</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8736,7 +8737,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8758,7 +8758,7 @@
         <v>126243363</v>
       </c>
       <c r="B81" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8856,42 +8856,37 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126243732</v>
+        <v>126243608</v>
       </c>
       <c r="B82" t="n">
-        <v>57649</v>
+        <v>91600</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -8899,10 +8894,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>438882</v>
+        <v>438797</v>
       </c>
       <c r="R82" t="n">
-        <v>6783685</v>
+        <v>6783670</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8943,6 +8938,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8961,32 +8957,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126243608</v>
+        <v>126243220</v>
       </c>
       <c r="B83" t="n">
-        <v>91596</v>
+        <v>91207</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8999,10 +8995,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>438797</v>
+        <v>438775</v>
       </c>
       <c r="R83" t="n">
-        <v>6783670</v>
+        <v>6783504</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9062,10 +9058,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126243220</v>
+        <v>126243505</v>
       </c>
       <c r="B84" t="n">
-        <v>91203</v>
+        <v>80115</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9073,21 +9069,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9100,10 +9096,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>438775</v>
+        <v>438858</v>
       </c>
       <c r="R84" t="n">
-        <v>6783504</v>
+        <v>6783695</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9166,7 +9162,7 @@
         <v>126243452</v>
       </c>
       <c r="B85" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9264,37 +9260,42 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126243505</v>
+        <v>126243732</v>
       </c>
       <c r="B86" t="n">
-        <v>80111</v>
+        <v>57653</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9302,10 +9303,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>438858</v>
+        <v>438882</v>
       </c>
       <c r="R86" t="n">
-        <v>6783695</v>
+        <v>6783685</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9346,7 +9347,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9365,10 +9365,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126243191</v>
+        <v>126243676</v>
       </c>
       <c r="B87" t="n">
-        <v>79059</v>
+        <v>98370</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9376,26 +9376,31 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6450</v>
+        <v>221952</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9403,10 +9408,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>438777</v>
+        <v>438813</v>
       </c>
       <c r="R87" t="n">
-        <v>6783503</v>
+        <v>6783722</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9466,10 +9471,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126243676</v>
+        <v>126243816</v>
       </c>
       <c r="B88" t="n">
-        <v>98366</v>
+        <v>98267</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9477,28 +9482,24 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221952</v>
+        <v>223591</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
@@ -9509,10 +9510,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>438813</v>
+        <v>438886</v>
       </c>
       <c r="R88" t="n">
-        <v>6783722</v>
+        <v>6783805</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9572,10 +9573,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126243816</v>
+        <v>126243191</v>
       </c>
       <c r="B89" t="n">
-        <v>98263</v>
+        <v>79063</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9583,27 +9584,26 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>223591</v>
+        <v>6450</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9611,10 +9611,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>438886</v>
+        <v>438777</v>
       </c>
       <c r="R89" t="n">
-        <v>6783805</v>
+        <v>6783503</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9677,7 +9677,7 @@
         <v>126243143</v>
       </c>
       <c r="B90" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>126249487</v>
       </c>
       <c r="B91" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9891,37 +9891,39 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126243503</v>
+        <v>126244082</v>
       </c>
       <c r="B92" t="n">
-        <v>78973</v>
+        <v>5176</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -9929,10 +9931,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>438858</v>
+        <v>438809</v>
       </c>
       <c r="R92" t="n">
-        <v>6783695</v>
+        <v>6783806</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9992,10 +9994,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126243415</v>
+        <v>126243973</v>
       </c>
       <c r="B93" t="n">
-        <v>57649</v>
+        <v>88651</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10003,31 +10005,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10035,10 +10032,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>438722</v>
+        <v>438928</v>
       </c>
       <c r="R93" t="n">
-        <v>6783470</v>
+        <v>6783763</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10079,6 +10076,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10097,39 +10095,37 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126244082</v>
+        <v>126243447</v>
       </c>
       <c r="B94" t="n">
-        <v>5176</v>
+        <v>82789</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100526</v>
+        <v>1312</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10137,10 +10133,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>438809</v>
+        <v>438740</v>
       </c>
       <c r="R94" t="n">
-        <v>6783806</v>
+        <v>6783462</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10200,10 +10196,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126243447</v>
+        <v>126243503</v>
       </c>
       <c r="B95" t="n">
-        <v>82785</v>
+        <v>78977</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10211,21 +10207,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10238,10 +10234,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>438740</v>
+        <v>438858</v>
       </c>
       <c r="R95" t="n">
-        <v>6783462</v>
+        <v>6783695</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10301,38 +10297,42 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126244320</v>
+        <v>126243415</v>
       </c>
       <c r="B96" t="n">
-        <v>98263</v>
+        <v>57653</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>223591</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10340,10 +10340,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>438606</v>
+        <v>438722</v>
       </c>
       <c r="R96" t="n">
-        <v>6783759</v>
+        <v>6783470</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10370,12 +10370,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10384,7 +10384,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10403,37 +10402,38 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126243973</v>
+        <v>126244320</v>
       </c>
       <c r="B97" t="n">
-        <v>88647</v>
+        <v>98267</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>510</v>
+        <v>223591</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -10441,10 +10441,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>438928</v>
+        <v>438606</v>
       </c>
       <c r="R97" t="n">
-        <v>6783763</v>
+        <v>6783759</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10471,12 +10471,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10507,7 +10507,7 @@
         <v>126243395</v>
       </c>
       <c r="B98" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -2008,38 +2008,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126243784</v>
+        <v>126243724</v>
       </c>
       <c r="B15" t="n">
-        <v>98370</v>
+        <v>91863</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>5454</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2047,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438893</v>
+        <v>438883</v>
       </c>
       <c r="R15" t="n">
-        <v>6783787</v>
+        <v>6783662</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2110,37 +2109,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126243724</v>
+        <v>126243784</v>
       </c>
       <c r="B16" t="n">
-        <v>91863</v>
+        <v>98370</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5454</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438883</v>
+        <v>438893</v>
       </c>
       <c r="R16" t="n">
-        <v>6783662</v>
+        <v>6783787</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -3929,38 +3929,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126244106</v>
+        <v>126244571</v>
       </c>
       <c r="B34" t="n">
-        <v>98370</v>
+        <v>82789</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3968,10 +3967,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438782</v>
+        <v>438751</v>
       </c>
       <c r="R34" t="n">
-        <v>6783777</v>
+        <v>6783884</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3998,12 +3997,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4031,7 +4030,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126244571</v>
+        <v>126244328</v>
       </c>
       <c r="B35" t="n">
         <v>82789</v>
@@ -4069,10 +4068,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>438751</v>
+        <v>438584</v>
       </c>
       <c r="R35" t="n">
-        <v>6783884</v>
+        <v>6783774</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4132,32 +4131,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126244328</v>
+        <v>126243379</v>
       </c>
       <c r="B36" t="n">
-        <v>82789</v>
+        <v>79063</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>6450</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4170,10 +4169,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>438584</v>
+        <v>438694</v>
       </c>
       <c r="R36" t="n">
-        <v>6783774</v>
+        <v>6783458</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4200,12 +4199,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4233,10 +4232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126243379</v>
+        <v>126244106</v>
       </c>
       <c r="B37" t="n">
-        <v>79063</v>
+        <v>98370</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4244,26 +4243,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6450</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>438694</v>
+        <v>438782</v>
       </c>
       <c r="R37" t="n">
-        <v>6783458</v>
+        <v>6783777</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -7306,32 +7306,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126242918</v>
+        <v>126243259</v>
       </c>
       <c r="B67" t="n">
-        <v>79009</v>
+        <v>91207</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7344,10 +7344,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>438917</v>
+        <v>438790</v>
       </c>
       <c r="R67" t="n">
-        <v>6783626</v>
+        <v>6783520</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7407,37 +7407,54 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126243259</v>
+        <v>126244312</v>
       </c>
       <c r="B68" t="n">
-        <v>91207</v>
+        <v>56839</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7445,10 +7462,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>438790</v>
+        <v>438654</v>
       </c>
       <c r="R68" t="n">
-        <v>6783520</v>
+        <v>6783741</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7475,12 +7492,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7489,7 +7506,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7508,10 +7524,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126242798</v>
+        <v>126242918</v>
       </c>
       <c r="B69" t="n">
-        <v>57653</v>
+        <v>79009</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7519,31 +7535,26 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7551,10 +7562,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>438938</v>
+        <v>438917</v>
       </c>
       <c r="R69" t="n">
-        <v>6783650</v>
+        <v>6783626</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7589,17 +7600,13 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Mycket hackspår i den ca 160 åriga naturskogen</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7618,10 +7625,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126244312</v>
+        <v>126242798</v>
       </c>
       <c r="B70" t="n">
-        <v>56839</v>
+        <v>57653</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7629,16 +7636,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7646,24 +7653,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -7673,10 +7668,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>438654</v>
+        <v>438938</v>
       </c>
       <c r="R70" t="n">
-        <v>6783741</v>
+        <v>6783650</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7703,12 +7698,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Mycket hackspår i den ca 160 åriga naturskogen</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8545,10 +8545,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126243586</v>
+        <v>126243363</v>
       </c>
       <c r="B79" t="n">
-        <v>57653</v>
+        <v>79595</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8556,31 +8556,26 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8588,10 +8583,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>438805</v>
+        <v>438739</v>
       </c>
       <c r="R79" t="n">
-        <v>6783685</v>
+        <v>6783474</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8632,6 +8627,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8650,7 +8646,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126243208</v>
+        <v>126243586</v>
       </c>
       <c r="B80" t="n">
         <v>57653</v>
@@ -8693,10 +8689,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438777</v>
+        <v>438805</v>
       </c>
       <c r="R80" t="n">
-        <v>6783503</v>
+        <v>6783685</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8755,10 +8751,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126243363</v>
+        <v>126243208</v>
       </c>
       <c r="B81" t="n">
-        <v>79595</v>
+        <v>57653</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8766,26 +8762,31 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8793,10 +8794,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>438739</v>
+        <v>438777</v>
       </c>
       <c r="R81" t="n">
-        <v>6783474</v>
+        <v>6783503</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8837,7 +8838,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9674,10 +9674,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126243143</v>
+        <v>126249487</v>
       </c>
       <c r="B90" t="n">
-        <v>56848</v>
+        <v>98370</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9685,45 +9685,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Hålberg-Räklitt, Dlr</t>
+          <t>Räklitt, Hållberg, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>438785</v>
+        <v>438890</v>
       </c>
       <c r="R90" t="n">
-        <v>6783487</v>
+        <v>6783610</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9747,17 +9739,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>21:07</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>En hona och 5 kycklingar</t>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>21:07</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9772,22 +9769,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126249487</v>
+        <v>126243143</v>
       </c>
       <c r="B91" t="n">
-        <v>98370</v>
+        <v>56848</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9795,37 +9792,45 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Räklitt, Hållberg, Dlr</t>
+          <t>Hålberg-Räklitt, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>438890</v>
+        <v>438785</v>
       </c>
       <c r="R91" t="n">
-        <v>6783610</v>
+        <v>6783487</v>
       </c>
       <c r="S91" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9849,22 +9854,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>21:07</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>21:07</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>En hona och 5 kycklingar</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9879,12 +9879,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -990,38 +990,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126243811</v>
+        <v>126242965</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>57653</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1029,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438886</v>
+        <v>438888</v>
       </c>
       <c r="R5" t="n">
-        <v>6783805</v>
+        <v>6783584</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1073,7 +1077,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1092,37 +1095,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126243254</v>
+        <v>126243811</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1130,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438790</v>
+        <v>438886</v>
       </c>
       <c r="R6" t="n">
-        <v>6783520</v>
+        <v>6783805</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1294,7 +1298,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126243055</v>
+        <v>126243254</v>
       </c>
       <c r="B8" t="n">
         <v>78977</v>
@@ -1332,10 +1336,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438823</v>
+        <v>438790</v>
       </c>
       <c r="R8" t="n">
-        <v>6783513</v>
+        <v>6783520</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1395,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126242965</v>
+        <v>126243055</v>
       </c>
       <c r="B9" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1406,31 +1410,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1438,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438888</v>
+        <v>438823</v>
       </c>
       <c r="R9" t="n">
-        <v>6783584</v>
+        <v>6783513</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1482,6 +1481,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>126244046</v>
       </c>
       <c r="B11" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126243682</v>
+        <v>126243933</v>
       </c>
       <c r="B13" t="n">
-        <v>88651</v>
+        <v>82789</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1817,21 +1817,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1844,10 +1844,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438813</v>
+        <v>438928</v>
       </c>
       <c r="R13" t="n">
-        <v>6783722</v>
+        <v>6783763</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126243933</v>
+        <v>126243682</v>
       </c>
       <c r="B14" t="n">
-        <v>82789</v>
+        <v>88651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1945,10 +1945,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438928</v>
+        <v>438813</v>
       </c>
       <c r="R14" t="n">
-        <v>6783763</v>
+        <v>6783722</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2112,7 +2112,7 @@
         <v>126243784</v>
       </c>
       <c r="B16" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2211,10 +2211,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126244296</v>
+        <v>126242913</v>
       </c>
       <c r="B17" t="n">
-        <v>82789</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2222,21 +2222,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438723</v>
+        <v>438938</v>
       </c>
       <c r="R17" t="n">
-        <v>6783752</v>
+        <v>6783637</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2279,12 +2279,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2312,32 +2312,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126244055</v>
+        <v>126243075</v>
       </c>
       <c r="B18" t="n">
-        <v>82789</v>
+        <v>79063</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6450</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438833</v>
+        <v>438799</v>
       </c>
       <c r="R18" t="n">
-        <v>6783826</v>
+        <v>6783496</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2413,7 +2413,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126243709</v>
+        <v>126244296</v>
       </c>
       <c r="B19" t="n">
         <v>82789</v>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438875</v>
+        <v>438723</v>
       </c>
       <c r="R19" t="n">
-        <v>6783718</v>
+        <v>6783752</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2514,7 +2514,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126244007</v>
+        <v>126244055</v>
       </c>
       <c r="B20" t="n">
         <v>82789</v>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438925</v>
+        <v>438833</v>
       </c>
       <c r="R20" t="n">
-        <v>6783804</v>
+        <v>6783826</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126243527</v>
+        <v>126243709</v>
       </c>
       <c r="B21" t="n">
-        <v>91256</v>
+        <v>82789</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438826</v>
+        <v>438875</v>
       </c>
       <c r="R21" t="n">
-        <v>6783693</v>
+        <v>6783718</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2716,32 +2716,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126243075</v>
+        <v>126244007</v>
       </c>
       <c r="B22" t="n">
-        <v>79063</v>
+        <v>82789</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438799</v>
+        <v>438925</v>
       </c>
       <c r="R22" t="n">
-        <v>6783496</v>
+        <v>6783804</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126242913</v>
+        <v>126243527</v>
       </c>
       <c r="B23" t="n">
-        <v>78977</v>
+        <v>91256</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2828,21 +2828,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>438938</v>
+        <v>438826</v>
       </c>
       <c r="R23" t="n">
-        <v>6783637</v>
+        <v>6783693</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126243565</v>
+        <v>126243148</v>
       </c>
       <c r="B26" t="n">
         <v>78977</v>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>438805</v>
+        <v>438785</v>
       </c>
       <c r="R26" t="n">
-        <v>6783685</v>
+        <v>6783487</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3221,7 +3221,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126243148</v>
+        <v>126243742</v>
       </c>
       <c r="B27" t="n">
         <v>78977</v>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438785</v>
+        <v>438885</v>
       </c>
       <c r="R27" t="n">
-        <v>6783487</v>
+        <v>6783710</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3322,10 +3322,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126243742</v>
+        <v>126243738</v>
       </c>
       <c r="B28" t="n">
-        <v>78977</v>
+        <v>79009</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3333,21 +3333,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3423,37 +3423,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126243348</v>
+        <v>126243647</v>
       </c>
       <c r="B29" t="n">
-        <v>79009</v>
+        <v>97230</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3461,10 +3462,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438767</v>
+        <v>438790</v>
       </c>
       <c r="R29" t="n">
-        <v>6783455</v>
+        <v>6783649</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3524,10 +3525,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126243738</v>
+        <v>126243342</v>
       </c>
       <c r="B30" t="n">
-        <v>79009</v>
+        <v>82789</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3535,21 +3536,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3562,10 +3563,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438885</v>
+        <v>438767</v>
       </c>
       <c r="R30" t="n">
-        <v>6783710</v>
+        <v>6783455</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3625,7 +3626,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126243342</v>
+        <v>126244253</v>
       </c>
       <c r="B31" t="n">
         <v>82789</v>
@@ -3663,10 +3664,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438767</v>
+        <v>438791</v>
       </c>
       <c r="R31" t="n">
-        <v>6783455</v>
+        <v>6783795</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3726,10 +3727,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126244253</v>
+        <v>126243348</v>
       </c>
       <c r="B32" t="n">
-        <v>82789</v>
+        <v>79009</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3737,21 +3738,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3764,10 +3765,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438791</v>
+        <v>438767</v>
       </c>
       <c r="R32" t="n">
-        <v>6783795</v>
+        <v>6783455</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3827,38 +3828,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126243647</v>
+        <v>126243565</v>
       </c>
       <c r="B33" t="n">
-        <v>97227</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>438790</v>
+        <v>438805</v>
       </c>
       <c r="R33" t="n">
-        <v>6783649</v>
+        <v>6783685</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4235,7 +4235,7 @@
         <v>126244106</v>
       </c>
       <c r="B37" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4334,10 +4334,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126244026</v>
+        <v>126243450</v>
       </c>
       <c r="B38" t="n">
-        <v>98370</v>
+        <v>91207</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4345,27 +4345,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4373,10 +4372,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>438902</v>
+        <v>438740</v>
       </c>
       <c r="R38" t="n">
-        <v>6783843</v>
+        <v>6783462</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4436,7 +4435,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126243450</v>
+        <v>126243521</v>
       </c>
       <c r="B39" t="n">
         <v>91207</v>
@@ -4474,10 +4473,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>438740</v>
+        <v>438845</v>
       </c>
       <c r="R39" t="n">
-        <v>6783462</v>
+        <v>6783696</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4537,32 +4536,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126243521</v>
+        <v>126242981</v>
       </c>
       <c r="B40" t="n">
-        <v>91207</v>
+        <v>78977</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4575,10 +4574,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>438845</v>
+        <v>438894</v>
       </c>
       <c r="R40" t="n">
-        <v>6783696</v>
+        <v>6783561</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4638,37 +4637,38 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126242981</v>
+        <v>126244026</v>
       </c>
       <c r="B41" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>438894</v>
+        <v>438902</v>
       </c>
       <c r="R41" t="n">
-        <v>6783561</v>
+        <v>6783843</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4742,7 +4742,7 @@
         <v>126243702</v>
       </c>
       <c r="B42" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4848,7 +4848,7 @@
         <v>126244589</v>
       </c>
       <c r="B43" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>126243995</v>
       </c>
       <c r="B44" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5049,10 +5049,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126243519</v>
+        <v>126244033</v>
       </c>
       <c r="B45" t="n">
-        <v>57816</v>
+        <v>82789</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5060,39 +5060,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5100,10 +5087,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>438845</v>
+        <v>438911</v>
       </c>
       <c r="R45" t="n">
-        <v>6783696</v>
+        <v>6783847</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5144,6 +5131,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5162,10 +5150,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126244033</v>
+        <v>126243519</v>
       </c>
       <c r="B46" t="n">
-        <v>82789</v>
+        <v>57816</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5173,26 +5161,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5200,10 +5201,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>438911</v>
+        <v>438845</v>
       </c>
       <c r="R46" t="n">
-        <v>6783847</v>
+        <v>6783696</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5244,7 +5245,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5768,10 +5768,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126243499</v>
+        <v>126242940</v>
       </c>
       <c r="B52" t="n">
-        <v>82789</v>
+        <v>57653</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5779,26 +5779,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -5806,10 +5811,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>438858</v>
+        <v>438898</v>
       </c>
       <c r="R52" t="n">
-        <v>6783695</v>
+        <v>6783622</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5850,7 +5855,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5869,10 +5873,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126244009</v>
+        <v>126243499</v>
       </c>
       <c r="B53" t="n">
-        <v>78977</v>
+        <v>82789</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5880,21 +5884,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5907,10 +5911,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>438925</v>
+        <v>438858</v>
       </c>
       <c r="R53" t="n">
-        <v>6783804</v>
+        <v>6783695</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5970,7 +5974,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126243332</v>
+        <v>126243713</v>
       </c>
       <c r="B54" t="n">
         <v>78977</v>
@@ -6008,10 +6012,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>438770</v>
+        <v>438875</v>
       </c>
       <c r="R54" t="n">
-        <v>6783484</v>
+        <v>6783718</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6071,7 +6075,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126243713</v>
+        <v>126244009</v>
       </c>
       <c r="B55" t="n">
         <v>78977</v>
@@ -6109,10 +6113,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>438875</v>
+        <v>438925</v>
       </c>
       <c r="R55" t="n">
-        <v>6783718</v>
+        <v>6783804</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6172,10 +6176,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126242940</v>
+        <v>126243332</v>
       </c>
       <c r="B56" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6183,31 +6187,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6215,10 +6214,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>438898</v>
+        <v>438770</v>
       </c>
       <c r="R56" t="n">
-        <v>6783622</v>
+        <v>6783484</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6259,6 +6258,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6277,10 +6277,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126243823</v>
+        <v>126243980</v>
       </c>
       <c r="B57" t="n">
-        <v>82789</v>
+        <v>78977</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6288,21 +6288,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>438911</v>
+        <v>438928</v>
       </c>
       <c r="R57" t="n">
-        <v>6783821</v>
+        <v>6783763</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6378,7 +6378,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126243980</v>
+        <v>126243462</v>
       </c>
       <c r="B58" t="n">
         <v>78977</v>
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>438928</v>
+        <v>438777</v>
       </c>
       <c r="R58" t="n">
-        <v>6783763</v>
+        <v>6783527</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6479,10 +6479,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126244052</v>
+        <v>126243986</v>
       </c>
       <c r="B59" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6490,21 +6490,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6517,10 +6517,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>438821</v>
+        <v>438947</v>
       </c>
       <c r="R59" t="n">
-        <v>6783854</v>
+        <v>6783782</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6580,10 +6580,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126243462</v>
+        <v>126244052</v>
       </c>
       <c r="B60" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6591,21 +6591,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>438777</v>
+        <v>438821</v>
       </c>
       <c r="R60" t="n">
-        <v>6783527</v>
+        <v>6783854</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6782,37 +6782,38 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126243986</v>
+        <v>126244294</v>
       </c>
       <c r="B62" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -6820,10 +6821,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>438947</v>
+        <v>438723</v>
       </c>
       <c r="R62" t="n">
-        <v>6783782</v>
+        <v>6783752</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6850,12 +6851,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6883,37 +6884,42 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126243617</v>
+        <v>126243641</v>
       </c>
       <c r="B63" t="n">
-        <v>91242</v>
+        <v>98373</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6921,10 +6927,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>438797</v>
+        <v>438790</v>
       </c>
       <c r="R63" t="n">
-        <v>6783670</v>
+        <v>6783649</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6984,46 +6990,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126243492</v>
+        <v>126243823</v>
       </c>
       <c r="B64" t="n">
-        <v>56848</v>
+        <v>82789</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7031,10 +7028,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>438871</v>
+        <v>438911</v>
       </c>
       <c r="R64" t="n">
-        <v>6783612</v>
+        <v>6783821</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7069,17 +7066,13 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Den tog ett s.k sandbad i sandblottan efter en rofyllda.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7098,42 +7091,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126243641</v>
+        <v>126243617</v>
       </c>
       <c r="B65" t="n">
-        <v>98370</v>
+        <v>91242</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7141,10 +7129,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>438790</v>
+        <v>438797</v>
       </c>
       <c r="R65" t="n">
-        <v>6783649</v>
+        <v>6783670</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7204,10 +7192,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126244294</v>
+        <v>126243492</v>
       </c>
       <c r="B66" t="n">
-        <v>98370</v>
+        <v>56848</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7215,27 +7203,35 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7243,10 +7239,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>438723</v>
+        <v>438871</v>
       </c>
       <c r="R66" t="n">
-        <v>6783752</v>
+        <v>6783612</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7273,12 +7269,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Den tog ett s.k sandbad i sandblottan efter en rofyllda.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7287,7 +7288,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7306,32 +7306,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126243259</v>
+        <v>126242918</v>
       </c>
       <c r="B67" t="n">
-        <v>91207</v>
+        <v>79009</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7344,10 +7344,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>438790</v>
+        <v>438917</v>
       </c>
       <c r="R67" t="n">
-        <v>6783520</v>
+        <v>6783626</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7407,54 +7407,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126244312</v>
+        <v>126244077</v>
       </c>
       <c r="B68" t="n">
-        <v>56839</v>
+        <v>98373</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7462,10 +7446,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>438654</v>
+        <v>438852</v>
       </c>
       <c r="R68" t="n">
-        <v>6783741</v>
+        <v>6783837</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7492,12 +7476,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7506,6 +7490,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7524,32 +7509,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126242918</v>
+        <v>126243259</v>
       </c>
       <c r="B69" t="n">
-        <v>79009</v>
+        <v>91207</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7562,10 +7547,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>438917</v>
+        <v>438790</v>
       </c>
       <c r="R69" t="n">
-        <v>6783626</v>
+        <v>6783520</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7735,38 +7720,54 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126244077</v>
+        <v>126244312</v>
       </c>
       <c r="B71" t="n">
-        <v>98370</v>
+        <v>56839</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>102612</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7774,10 +7775,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>438852</v>
+        <v>438654</v>
       </c>
       <c r="R71" t="n">
-        <v>6783837</v>
+        <v>6783741</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7804,12 +7805,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7818,7 +7819,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7837,32 +7837,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126243459</v>
+        <v>126243314</v>
       </c>
       <c r="B72" t="n">
-        <v>79009</v>
+        <v>91829</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>185</v>
+        <v>1179</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>438777</v>
+        <v>438816</v>
       </c>
       <c r="R72" t="n">
-        <v>6783527</v>
+        <v>6783530</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7938,32 +7938,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126243314</v>
+        <v>126243042</v>
       </c>
       <c r="B73" t="n">
-        <v>91829</v>
+        <v>79056</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1179</v>
+        <v>864</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7976,10 +7976,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>438816</v>
+        <v>438848</v>
       </c>
       <c r="R73" t="n">
-        <v>6783530</v>
+        <v>6783520</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8039,37 +8039,38 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126243042</v>
+        <v>126244337</v>
       </c>
       <c r="B74" t="n">
-        <v>79056</v>
+        <v>98270</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>864</v>
+        <v>223591</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8077,10 +8078,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>438848</v>
+        <v>438574</v>
       </c>
       <c r="R74" t="n">
-        <v>6783520</v>
+        <v>6783811</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8107,12 +8108,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8241,38 +8242,37 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126244337</v>
+        <v>126243459</v>
       </c>
       <c r="B76" t="n">
-        <v>98267</v>
+        <v>79009</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>223591</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>438574</v>
+        <v>438777</v>
       </c>
       <c r="R76" t="n">
-        <v>6783811</v>
+        <v>6783527</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8310,12 +8310,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8343,10 +8343,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126243070</v>
+        <v>126243991</v>
       </c>
       <c r="B77" t="n">
-        <v>79009</v>
+        <v>91260</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8354,21 +8354,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>185</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8381,10 +8381,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>438799</v>
+        <v>438953</v>
       </c>
       <c r="R77" t="n">
-        <v>6783496</v>
+        <v>6783776</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8444,10 +8444,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126243991</v>
+        <v>126243586</v>
       </c>
       <c r="B78" t="n">
-        <v>91260</v>
+        <v>57653</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8455,26 +8455,31 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8482,10 +8487,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>438953</v>
+        <v>438805</v>
       </c>
       <c r="R78" t="n">
-        <v>6783776</v>
+        <v>6783685</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8526,7 +8531,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8545,10 +8549,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126243363</v>
+        <v>126243208</v>
       </c>
       <c r="B79" t="n">
-        <v>79595</v>
+        <v>57653</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8556,26 +8560,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8583,10 +8592,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>438739</v>
+        <v>438777</v>
       </c>
       <c r="R79" t="n">
-        <v>6783474</v>
+        <v>6783503</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8627,7 +8636,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8646,10 +8654,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126243586</v>
+        <v>126243070</v>
       </c>
       <c r="B80" t="n">
-        <v>57653</v>
+        <v>79009</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8657,31 +8665,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -8689,10 +8692,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438805</v>
+        <v>438799</v>
       </c>
       <c r="R80" t="n">
-        <v>6783685</v>
+        <v>6783496</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8733,6 +8736,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8751,10 +8755,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126243208</v>
+        <v>126243363</v>
       </c>
       <c r="B81" t="n">
-        <v>57653</v>
+        <v>79595</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8762,31 +8766,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8794,10 +8793,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>438777</v>
+        <v>438739</v>
       </c>
       <c r="R81" t="n">
-        <v>6783503</v>
+        <v>6783474</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8838,6 +8837,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8856,32 +8856,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126243608</v>
+        <v>126243505</v>
       </c>
       <c r="B82" t="n">
-        <v>91600</v>
+        <v>80115</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2062</v>
+        <v>6463</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8894,10 +8894,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>438797</v>
+        <v>438858</v>
       </c>
       <c r="R82" t="n">
-        <v>6783670</v>
+        <v>6783695</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8957,10 +8957,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126243220</v>
+        <v>126243191</v>
       </c>
       <c r="B83" t="n">
-        <v>91207</v>
+        <v>79063</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8968,21 +8968,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>6450</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8995,10 +8995,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>438775</v>
+        <v>438777</v>
       </c>
       <c r="R83" t="n">
-        <v>6783504</v>
+        <v>6783503</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9058,37 +9058,42 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126243505</v>
+        <v>126243732</v>
       </c>
       <c r="B84" t="n">
-        <v>80115</v>
+        <v>57653</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9096,10 +9101,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>438858</v>
+        <v>438882</v>
       </c>
       <c r="R84" t="n">
-        <v>6783695</v>
+        <v>6783685</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9140,7 +9145,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9159,37 +9163,42 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126243452</v>
+        <v>126243676</v>
       </c>
       <c r="B85" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -9197,10 +9206,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>438740</v>
+        <v>438813</v>
       </c>
       <c r="R85" t="n">
-        <v>6783462</v>
+        <v>6783722</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9260,42 +9269,38 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126243732</v>
+        <v>126243816</v>
       </c>
       <c r="B86" t="n">
-        <v>57653</v>
+        <v>98270</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>223591</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9303,10 +9308,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>438882</v>
+        <v>438886</v>
       </c>
       <c r="R86" t="n">
-        <v>6783685</v>
+        <v>6783805</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9347,6 +9352,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9365,42 +9371,37 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126243676</v>
+        <v>126243608</v>
       </c>
       <c r="B87" t="n">
-        <v>98370</v>
+        <v>91600</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221952</v>
+        <v>2062</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9408,10 +9409,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>438813</v>
+        <v>438797</v>
       </c>
       <c r="R87" t="n">
-        <v>6783722</v>
+        <v>6783670</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9471,10 +9472,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126243816</v>
+        <v>126243220</v>
       </c>
       <c r="B88" t="n">
-        <v>98267</v>
+        <v>91207</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9482,27 +9483,26 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>223591</v>
+        <v>5447</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -9510,10 +9510,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>438886</v>
+        <v>438775</v>
       </c>
       <c r="R88" t="n">
-        <v>6783805</v>
+        <v>6783504</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9573,32 +9573,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126243191</v>
+        <v>126243452</v>
       </c>
       <c r="B89" t="n">
-        <v>79063</v>
+        <v>78977</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9611,10 +9611,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>438777</v>
+        <v>438740</v>
       </c>
       <c r="R89" t="n">
-        <v>6783503</v>
+        <v>6783462</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9674,10 +9674,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126249487</v>
+        <v>126243143</v>
       </c>
       <c r="B90" t="n">
-        <v>98370</v>
+        <v>56848</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9685,37 +9685,45 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Räklitt, Hållberg, Dlr</t>
+          <t>Hålberg-Räklitt, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>438890</v>
+        <v>438785</v>
       </c>
       <c r="R90" t="n">
-        <v>6783610</v>
+        <v>6783487</v>
       </c>
       <c r="S90" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9739,22 +9747,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>21:07</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>21:07</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>En hona och 5 kycklingar</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9769,22 +9772,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126243143</v>
+        <v>126249487</v>
       </c>
       <c r="B91" t="n">
-        <v>56848</v>
+        <v>98373</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9792,45 +9795,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Hålberg-Räklitt, Dlr</t>
+          <t>Räklitt, Hållberg, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>438785</v>
+        <v>438890</v>
       </c>
       <c r="R91" t="n">
-        <v>6783487</v>
+        <v>6783610</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9854,17 +9849,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>21:07</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>En hona och 5 kycklingar</t>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>21:07</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9879,51 +9879,49 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126244082</v>
+        <v>126243503</v>
       </c>
       <c r="B92" t="n">
-        <v>5176</v>
+        <v>78977</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -9931,10 +9929,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>438809</v>
+        <v>438858</v>
       </c>
       <c r="R92" t="n">
-        <v>6783806</v>
+        <v>6783695</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9994,10 +9992,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126243973</v>
+        <v>126243415</v>
       </c>
       <c r="B93" t="n">
-        <v>88651</v>
+        <v>57653</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10005,26 +10003,31 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10032,10 +10035,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>438928</v>
+        <v>438722</v>
       </c>
       <c r="R93" t="n">
-        <v>6783763</v>
+        <v>6783470</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10076,7 +10079,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10095,37 +10097,39 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126243447</v>
+        <v>126244082</v>
       </c>
       <c r="B94" t="n">
-        <v>82789</v>
+        <v>5176</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1312</v>
+        <v>100526</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10133,10 +10137,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>438740</v>
+        <v>438809</v>
       </c>
       <c r="R94" t="n">
-        <v>6783462</v>
+        <v>6783806</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10196,37 +10200,38 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126243503</v>
+        <v>126244320</v>
       </c>
       <c r="B95" t="n">
-        <v>78977</v>
+        <v>98270</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>223591</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10234,10 +10239,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>438858</v>
+        <v>438606</v>
       </c>
       <c r="R95" t="n">
-        <v>6783695</v>
+        <v>6783759</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10264,12 +10269,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10297,10 +10302,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126243415</v>
+        <v>126243395</v>
       </c>
       <c r="B96" t="n">
-        <v>57653</v>
+        <v>79566</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10308,31 +10313,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10340,10 +10340,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>438722</v>
+        <v>438682</v>
       </c>
       <c r="R96" t="n">
-        <v>6783470</v>
+        <v>6783454</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10384,6 +10384,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10402,38 +10403,37 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126244320</v>
+        <v>126243447</v>
       </c>
       <c r="B97" t="n">
-        <v>98267</v>
+        <v>82789</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>223591</v>
+        <v>1312</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -10441,10 +10441,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>438606</v>
+        <v>438740</v>
       </c>
       <c r="R97" t="n">
-        <v>6783759</v>
+        <v>6783462</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10471,12 +10471,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10504,10 +10504,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126243395</v>
+        <v>126243973</v>
       </c>
       <c r="B98" t="n">
-        <v>79566</v>
+        <v>88651</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10515,21 +10515,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>510</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10542,10 +10542,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>438682</v>
+        <v>438928</v>
       </c>
       <c r="R98" t="n">
-        <v>6783454</v>
+        <v>6783763</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -3120,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126243148</v>
+        <v>126243342</v>
       </c>
       <c r="B26" t="n">
-        <v>78977</v>
+        <v>82789</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3131,21 +3131,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>438785</v>
+        <v>438767</v>
       </c>
       <c r="R26" t="n">
-        <v>6783487</v>
+        <v>6783455</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3221,10 +3221,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126243742</v>
+        <v>126244253</v>
       </c>
       <c r="B27" t="n">
-        <v>78977</v>
+        <v>82789</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3232,21 +3232,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438885</v>
+        <v>438791</v>
       </c>
       <c r="R27" t="n">
-        <v>6783710</v>
+        <v>6783795</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3322,7 +3322,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126243738</v>
+        <v>126243348</v>
       </c>
       <c r="B28" t="n">
         <v>79009</v>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438885</v>
+        <v>438767</v>
       </c>
       <c r="R28" t="n">
-        <v>6783710</v>
+        <v>6783455</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3423,38 +3423,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126243647</v>
+        <v>126243738</v>
       </c>
       <c r="B29" t="n">
-        <v>97230</v>
+        <v>79009</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3462,10 +3461,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438790</v>
+        <v>438885</v>
       </c>
       <c r="R29" t="n">
-        <v>6783649</v>
+        <v>6783710</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3525,10 +3524,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126243342</v>
+        <v>126243565</v>
       </c>
       <c r="B30" t="n">
-        <v>82789</v>
+        <v>78977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3536,21 +3535,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3563,10 +3562,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438767</v>
+        <v>438805</v>
       </c>
       <c r="R30" t="n">
-        <v>6783455</v>
+        <v>6783685</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3626,10 +3625,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126244253</v>
+        <v>126243148</v>
       </c>
       <c r="B31" t="n">
-        <v>82789</v>
+        <v>78977</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3637,21 +3636,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3664,10 +3663,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438791</v>
+        <v>438785</v>
       </c>
       <c r="R31" t="n">
-        <v>6783795</v>
+        <v>6783487</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3727,10 +3726,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126243348</v>
+        <v>126243742</v>
       </c>
       <c r="B32" t="n">
-        <v>79009</v>
+        <v>78977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3738,21 +3737,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3765,10 +3764,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438767</v>
+        <v>438885</v>
       </c>
       <c r="R32" t="n">
-        <v>6783455</v>
+        <v>6783710</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3828,37 +3827,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126243565</v>
+        <v>126243647</v>
       </c>
       <c r="B33" t="n">
-        <v>78977</v>
+        <v>97230</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>438805</v>
+        <v>438790</v>
       </c>
       <c r="R33" t="n">
-        <v>6783685</v>
+        <v>6783649</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4334,32 +4334,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126243450</v>
+        <v>126242981</v>
       </c>
       <c r="B38" t="n">
-        <v>91207</v>
+        <v>78977</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>438740</v>
+        <v>438894</v>
       </c>
       <c r="R38" t="n">
-        <v>6783462</v>
+        <v>6783561</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4435,10 +4435,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126243521</v>
+        <v>126244026</v>
       </c>
       <c r="B39" t="n">
-        <v>91207</v>
+        <v>98373</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4446,26 +4446,27 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4473,10 +4474,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>438845</v>
+        <v>438902</v>
       </c>
       <c r="R39" t="n">
-        <v>6783696</v>
+        <v>6783843</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4536,32 +4537,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126242981</v>
+        <v>126243450</v>
       </c>
       <c r="B40" t="n">
-        <v>78977</v>
+        <v>91207</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4574,10 +4575,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>438894</v>
+        <v>438740</v>
       </c>
       <c r="R40" t="n">
-        <v>6783561</v>
+        <v>6783462</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4637,10 +4638,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126244026</v>
+        <v>126243521</v>
       </c>
       <c r="B41" t="n">
-        <v>98373</v>
+        <v>91207</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4648,27 +4649,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>438902</v>
+        <v>438845</v>
       </c>
       <c r="R41" t="n">
-        <v>6783843</v>
+        <v>6783696</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5667,32 +5667,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126243769</v>
+        <v>126244009</v>
       </c>
       <c r="B51" t="n">
-        <v>78340</v>
+        <v>78977</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>438898</v>
+        <v>438925</v>
       </c>
       <c r="R51" t="n">
-        <v>6783784</v>
+        <v>6783804</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5768,10 +5768,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126242940</v>
+        <v>126243332</v>
       </c>
       <c r="B52" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5779,31 +5779,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -5811,10 +5806,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>438898</v>
+        <v>438770</v>
       </c>
       <c r="R52" t="n">
-        <v>6783622</v>
+        <v>6783484</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5855,6 +5850,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5974,32 +5970,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126243713</v>
+        <v>126243769</v>
       </c>
       <c r="B54" t="n">
-        <v>78977</v>
+        <v>78340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6012,10 +6008,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>438875</v>
+        <v>438898</v>
       </c>
       <c r="R54" t="n">
-        <v>6783718</v>
+        <v>6783784</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6075,7 +6071,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126244009</v>
+        <v>126243713</v>
       </c>
       <c r="B55" t="n">
         <v>78977</v>
@@ -6113,10 +6109,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>438925</v>
+        <v>438875</v>
       </c>
       <c r="R55" t="n">
-        <v>6783804</v>
+        <v>6783718</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6176,10 +6172,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126243332</v>
+        <v>126242940</v>
       </c>
       <c r="B56" t="n">
-        <v>78977</v>
+        <v>57653</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6187,26 +6183,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6214,10 +6215,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>438770</v>
+        <v>438898</v>
       </c>
       <c r="R56" t="n">
-        <v>6783484</v>
+        <v>6783622</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6258,7 +6259,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7306,32 +7306,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126242918</v>
+        <v>126243259</v>
       </c>
       <c r="B67" t="n">
-        <v>79009</v>
+        <v>91207</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7344,10 +7344,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>438917</v>
+        <v>438790</v>
       </c>
       <c r="R67" t="n">
-        <v>6783626</v>
+        <v>6783520</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7407,38 +7407,42 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126244077</v>
+        <v>126242798</v>
       </c>
       <c r="B68" t="n">
-        <v>98373</v>
+        <v>57653</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7446,10 +7450,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>438852</v>
+        <v>438938</v>
       </c>
       <c r="R68" t="n">
-        <v>6783837</v>
+        <v>6783650</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7484,13 +7488,17 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Mycket hackspår i den ca 160 åriga naturskogen</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7509,32 +7517,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126243259</v>
+        <v>126242918</v>
       </c>
       <c r="B69" t="n">
-        <v>91207</v>
+        <v>79009</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7547,10 +7555,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>438790</v>
+        <v>438917</v>
       </c>
       <c r="R69" t="n">
-        <v>6783520</v>
+        <v>6783626</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7610,10 +7618,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126242798</v>
+        <v>126244312</v>
       </c>
       <c r="B70" t="n">
-        <v>57653</v>
+        <v>56839</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7621,16 +7629,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7638,12 +7646,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -7653,10 +7673,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>438938</v>
+        <v>438654</v>
       </c>
       <c r="R70" t="n">
-        <v>6783650</v>
+        <v>6783741</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7683,17 +7703,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Mycket hackspår i den ca 160 åriga naturskogen</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7720,54 +7735,38 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126244312</v>
+        <v>126244077</v>
       </c>
       <c r="B71" t="n">
-        <v>56839</v>
+        <v>98373</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102612</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7775,10 +7774,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>438654</v>
+        <v>438852</v>
       </c>
       <c r="R71" t="n">
-        <v>6783741</v>
+        <v>6783837</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7805,12 +7804,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7819,6 +7818,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7837,32 +7837,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126243314</v>
+        <v>126244274</v>
       </c>
       <c r="B72" t="n">
-        <v>91829</v>
+        <v>82789</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1179</v>
+        <v>1312</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>438816</v>
+        <v>438776</v>
       </c>
       <c r="R72" t="n">
-        <v>6783530</v>
+        <v>6783788</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7938,37 +7938,38 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126243042</v>
+        <v>126244337</v>
       </c>
       <c r="B73" t="n">
-        <v>79056</v>
+        <v>98270</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>864</v>
+        <v>223591</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -7976,10 +7977,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>438848</v>
+        <v>438574</v>
       </c>
       <c r="R73" t="n">
-        <v>6783520</v>
+        <v>6783811</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8006,12 +8007,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8039,38 +8040,37 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126244337</v>
+        <v>126243314</v>
       </c>
       <c r="B74" t="n">
-        <v>98270</v>
+        <v>91829</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>223591</v>
+        <v>1179</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>438574</v>
+        <v>438816</v>
       </c>
       <c r="R74" t="n">
-        <v>6783811</v>
+        <v>6783530</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8108,12 +8108,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8141,10 +8141,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126244274</v>
+        <v>126243042</v>
       </c>
       <c r="B75" t="n">
-        <v>82789</v>
+        <v>79056</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8152,21 +8152,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8179,10 +8179,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>438776</v>
+        <v>438848</v>
       </c>
       <c r="R75" t="n">
-        <v>6783788</v>
+        <v>6783520</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8343,10 +8343,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126243991</v>
+        <v>126243070</v>
       </c>
       <c r="B77" t="n">
-        <v>91260</v>
+        <v>79009</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8354,21 +8354,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8381,10 +8381,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>438953</v>
+        <v>438799</v>
       </c>
       <c r="R77" t="n">
-        <v>6783776</v>
+        <v>6783496</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8444,10 +8444,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126243586</v>
+        <v>126243991</v>
       </c>
       <c r="B78" t="n">
-        <v>57653</v>
+        <v>91260</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8455,31 +8455,26 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8487,10 +8482,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>438805</v>
+        <v>438953</v>
       </c>
       <c r="R78" t="n">
-        <v>6783685</v>
+        <v>6783776</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8531,6 +8526,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8549,7 +8545,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126243208</v>
+        <v>126243586</v>
       </c>
       <c r="B79" t="n">
         <v>57653</v>
@@ -8592,10 +8588,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>438777</v>
+        <v>438805</v>
       </c>
       <c r="R79" t="n">
-        <v>6783503</v>
+        <v>6783685</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8654,10 +8650,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126243070</v>
+        <v>126243208</v>
       </c>
       <c r="B80" t="n">
-        <v>79009</v>
+        <v>57653</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8665,26 +8661,31 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>185</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -8692,10 +8693,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438799</v>
+        <v>438777</v>
       </c>
       <c r="R80" t="n">
-        <v>6783496</v>
+        <v>6783503</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8736,7 +8737,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8856,32 +8856,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126243505</v>
+        <v>126243608</v>
       </c>
       <c r="B82" t="n">
-        <v>80115</v>
+        <v>91600</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6463</v>
+        <v>2062</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8894,10 +8894,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>438858</v>
+        <v>438797</v>
       </c>
       <c r="R82" t="n">
-        <v>6783695</v>
+        <v>6783670</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8957,10 +8957,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126243191</v>
+        <v>126243220</v>
       </c>
       <c r="B83" t="n">
-        <v>79063</v>
+        <v>91207</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8968,21 +8968,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6450</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8995,10 +8995,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>438777</v>
+        <v>438775</v>
       </c>
       <c r="R83" t="n">
-        <v>6783503</v>
+        <v>6783504</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9058,10 +9058,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126243732</v>
+        <v>126243452</v>
       </c>
       <c r="B84" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9069,31 +9069,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9101,10 +9096,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>438882</v>
+        <v>438740</v>
       </c>
       <c r="R84" t="n">
-        <v>6783685</v>
+        <v>6783462</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9145,6 +9140,7 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9163,10 +9159,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126243676</v>
+        <v>126243505</v>
       </c>
       <c r="B85" t="n">
-        <v>98373</v>
+        <v>80115</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9174,31 +9170,26 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -9206,10 +9197,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>438813</v>
+        <v>438858</v>
       </c>
       <c r="R85" t="n">
-        <v>6783722</v>
+        <v>6783695</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9269,10 +9260,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126243816</v>
+        <v>126243191</v>
       </c>
       <c r="B86" t="n">
-        <v>98270</v>
+        <v>79063</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9280,27 +9271,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>223591</v>
+        <v>6450</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9308,10 +9298,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>438886</v>
+        <v>438777</v>
       </c>
       <c r="R86" t="n">
-        <v>6783805</v>
+        <v>6783503</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9371,37 +9361,42 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126243608</v>
+        <v>126243732</v>
       </c>
       <c r="B87" t="n">
-        <v>91600</v>
+        <v>57653</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2062</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9409,10 +9404,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>438797</v>
+        <v>438882</v>
       </c>
       <c r="R87" t="n">
-        <v>6783670</v>
+        <v>6783685</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9453,7 +9448,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9472,10 +9466,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126243220</v>
+        <v>126243816</v>
       </c>
       <c r="B88" t="n">
-        <v>91207</v>
+        <v>98270</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9483,26 +9477,27 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5447</v>
+        <v>223591</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -9510,10 +9505,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>438775</v>
+        <v>438886</v>
       </c>
       <c r="R88" t="n">
-        <v>6783504</v>
+        <v>6783805</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9573,37 +9568,42 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126243452</v>
+        <v>126243676</v>
       </c>
       <c r="B89" t="n">
-        <v>78977</v>
+        <v>98373</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9611,10 +9611,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>438740</v>
+        <v>438813</v>
       </c>
       <c r="R89" t="n">
-        <v>6783462</v>
+        <v>6783722</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -889,37 +889,39 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126243187</v>
+        <v>126244085</v>
       </c>
       <c r="B4" t="n">
-        <v>80952</v>
+        <v>4772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>100299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -927,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438777</v>
+        <v>438809</v>
       </c>
       <c r="R4" t="n">
-        <v>6783503</v>
+        <v>6783806</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -990,42 +992,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126242965</v>
+        <v>126243811</v>
       </c>
       <c r="B5" t="n">
-        <v>57653</v>
+        <v>98373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1033,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438888</v>
+        <v>438886</v>
       </c>
       <c r="R5" t="n">
-        <v>6783584</v>
+        <v>6783805</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1077,6 +1075,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1095,38 +1094,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126243811</v>
+        <v>126243187</v>
       </c>
       <c r="B6" t="n">
-        <v>98373</v>
+        <v>80952</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>1049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1134,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438886</v>
+        <v>438777</v>
       </c>
       <c r="R6" t="n">
-        <v>6783805</v>
+        <v>6783503</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1197,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126242851</v>
+        <v>126243254</v>
       </c>
       <c r="B7" t="n">
         <v>78977</v>
@@ -1235,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438926</v>
+        <v>438790</v>
       </c>
       <c r="R7" t="n">
-        <v>6783631</v>
+        <v>6783520</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1298,7 +1296,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126243254</v>
+        <v>126242851</v>
       </c>
       <c r="B8" t="n">
         <v>78977</v>
@@ -1336,10 +1334,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438790</v>
+        <v>438926</v>
       </c>
       <c r="R8" t="n">
-        <v>6783520</v>
+        <v>6783631</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1500,39 +1498,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126244085</v>
+        <v>126242965</v>
       </c>
       <c r="B10" t="n">
-        <v>4772</v>
+        <v>57653</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1540,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438809</v>
+        <v>438888</v>
       </c>
       <c r="R10" t="n">
-        <v>6783806</v>
+        <v>6783584</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1584,7 +1585,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -2211,10 +2211,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126242913</v>
+        <v>126244296</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>82789</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2222,21 +2222,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438938</v>
+        <v>438723</v>
       </c>
       <c r="R17" t="n">
-        <v>6783637</v>
+        <v>6783752</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2279,12 +2279,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2312,32 +2312,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126243075</v>
+        <v>126244055</v>
       </c>
       <c r="B18" t="n">
-        <v>79063</v>
+        <v>82789</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438799</v>
+        <v>438833</v>
       </c>
       <c r="R18" t="n">
-        <v>6783496</v>
+        <v>6783826</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2413,7 +2413,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126244296</v>
+        <v>126243709</v>
       </c>
       <c r="B19" t="n">
         <v>82789</v>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438723</v>
+        <v>438875</v>
       </c>
       <c r="R19" t="n">
-        <v>6783752</v>
+        <v>6783718</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2481,12 +2481,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2514,7 +2514,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126244055</v>
+        <v>126244007</v>
       </c>
       <c r="B20" t="n">
         <v>82789</v>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438833</v>
+        <v>438925</v>
       </c>
       <c r="R20" t="n">
-        <v>6783826</v>
+        <v>6783804</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126243709</v>
+        <v>126243757</v>
       </c>
       <c r="B21" t="n">
-        <v>82789</v>
+        <v>79056</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438875</v>
+        <v>438889</v>
       </c>
       <c r="R21" t="n">
-        <v>6783718</v>
+        <v>6783762</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2716,32 +2716,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126244007</v>
+        <v>126243075</v>
       </c>
       <c r="B22" t="n">
-        <v>82789</v>
+        <v>79063</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6450</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438925</v>
+        <v>438799</v>
       </c>
       <c r="R22" t="n">
-        <v>6783804</v>
+        <v>6783496</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126243527</v>
+        <v>126242913</v>
       </c>
       <c r="B23" t="n">
-        <v>91256</v>
+        <v>78977</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2828,21 +2828,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>438826</v>
+        <v>438938</v>
       </c>
       <c r="R23" t="n">
-        <v>6783693</v>
+        <v>6783637</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126243757</v>
+        <v>126243527</v>
       </c>
       <c r="B24" t="n">
-        <v>79056</v>
+        <v>91256</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2929,21 +2929,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>864</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>438889</v>
+        <v>438826</v>
       </c>
       <c r="R24" t="n">
-        <v>6783762</v>
+        <v>6783693</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126243342</v>
+        <v>126243565</v>
       </c>
       <c r="B26" t="n">
-        <v>82789</v>
+        <v>78977</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3131,21 +3131,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>438767</v>
+        <v>438805</v>
       </c>
       <c r="R26" t="n">
-        <v>6783455</v>
+        <v>6783685</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3221,10 +3221,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126244253</v>
+        <v>126243148</v>
       </c>
       <c r="B27" t="n">
-        <v>82789</v>
+        <v>78977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3232,21 +3232,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438791</v>
+        <v>438785</v>
       </c>
       <c r="R27" t="n">
-        <v>6783795</v>
+        <v>6783487</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3524,10 +3524,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126243565</v>
+        <v>126243342</v>
       </c>
       <c r="B30" t="n">
-        <v>78977</v>
+        <v>82789</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3535,21 +3535,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3562,10 +3562,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438805</v>
+        <v>438767</v>
       </c>
       <c r="R30" t="n">
-        <v>6783685</v>
+        <v>6783455</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3625,10 +3625,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126243148</v>
+        <v>126244253</v>
       </c>
       <c r="B31" t="n">
-        <v>78977</v>
+        <v>82789</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3636,21 +3636,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438785</v>
+        <v>438791</v>
       </c>
       <c r="R31" t="n">
-        <v>6783487</v>
+        <v>6783795</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3929,37 +3929,38 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126244571</v>
+        <v>126244106</v>
       </c>
       <c r="B34" t="n">
-        <v>82789</v>
+        <v>98373</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3967,10 +3968,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438751</v>
+        <v>438782</v>
       </c>
       <c r="R34" t="n">
-        <v>6783884</v>
+        <v>6783777</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3997,12 +3998,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4030,7 +4031,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126244328</v>
+        <v>126244571</v>
       </c>
       <c r="B35" t="n">
         <v>82789</v>
@@ -4068,10 +4069,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>438584</v>
+        <v>438751</v>
       </c>
       <c r="R35" t="n">
-        <v>6783774</v>
+        <v>6783884</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4131,32 +4132,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126243379</v>
+        <v>126244328</v>
       </c>
       <c r="B36" t="n">
-        <v>79063</v>
+        <v>82789</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4169,10 +4170,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>438694</v>
+        <v>438584</v>
       </c>
       <c r="R36" t="n">
-        <v>6783458</v>
+        <v>6783774</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4199,12 +4200,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4232,10 +4233,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126244106</v>
+        <v>126243379</v>
       </c>
       <c r="B37" t="n">
-        <v>98373</v>
+        <v>79063</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4243,27 +4244,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221952</v>
+        <v>6450</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>438782</v>
+        <v>438694</v>
       </c>
       <c r="R37" t="n">
-        <v>6783777</v>
+        <v>6783458</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4334,32 +4334,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126242981</v>
+        <v>126243450</v>
       </c>
       <c r="B38" t="n">
-        <v>78977</v>
+        <v>91207</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>438894</v>
+        <v>438740</v>
       </c>
       <c r="R38" t="n">
-        <v>6783561</v>
+        <v>6783462</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4435,10 +4435,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126244026</v>
+        <v>126243521</v>
       </c>
       <c r="B39" t="n">
-        <v>98373</v>
+        <v>91207</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4446,27 +4446,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4474,10 +4473,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>438902</v>
+        <v>438845</v>
       </c>
       <c r="R39" t="n">
-        <v>6783843</v>
+        <v>6783696</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4537,32 +4536,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126243450</v>
+        <v>126242981</v>
       </c>
       <c r="B40" t="n">
-        <v>91207</v>
+        <v>78977</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4575,10 +4574,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>438740</v>
+        <v>438894</v>
       </c>
       <c r="R40" t="n">
-        <v>6783462</v>
+        <v>6783561</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4638,10 +4637,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126243521</v>
+        <v>126244026</v>
       </c>
       <c r="B41" t="n">
-        <v>91207</v>
+        <v>98373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4649,26 +4648,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>438845</v>
+        <v>438902</v>
       </c>
       <c r="R41" t="n">
-        <v>6783696</v>
+        <v>6783843</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5667,10 +5667,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126244009</v>
+        <v>126242940</v>
       </c>
       <c r="B51" t="n">
-        <v>78977</v>
+        <v>57653</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5678,26 +5678,31 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5705,10 +5710,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>438925</v>
+        <v>438898</v>
       </c>
       <c r="R51" t="n">
-        <v>6783804</v>
+        <v>6783622</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5749,7 +5754,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5768,32 +5772,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126243332</v>
+        <v>126243769</v>
       </c>
       <c r="B52" t="n">
-        <v>78977</v>
+        <v>78340</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>498</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5806,10 +5810,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>438770</v>
+        <v>438898</v>
       </c>
       <c r="R52" t="n">
-        <v>6783484</v>
+        <v>6783784</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5970,32 +5974,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126243769</v>
+        <v>126244009</v>
       </c>
       <c r="B54" t="n">
-        <v>78340</v>
+        <v>78977</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>498</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6008,10 +6012,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>438898</v>
+        <v>438925</v>
       </c>
       <c r="R54" t="n">
-        <v>6783784</v>
+        <v>6783804</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6071,7 +6075,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126243713</v>
+        <v>126243332</v>
       </c>
       <c r="B55" t="n">
         <v>78977</v>
@@ -6109,10 +6113,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>438875</v>
+        <v>438770</v>
       </c>
       <c r="R55" t="n">
-        <v>6783718</v>
+        <v>6783484</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6172,10 +6176,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126242940</v>
+        <v>126243713</v>
       </c>
       <c r="B56" t="n">
-        <v>57653</v>
+        <v>78977</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6183,31 +6187,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6215,10 +6214,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>438898</v>
+        <v>438875</v>
       </c>
       <c r="R56" t="n">
-        <v>6783622</v>
+        <v>6783718</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6259,6 +6258,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6277,10 +6277,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126243980</v>
+        <v>126243617</v>
       </c>
       <c r="B57" t="n">
-        <v>78977</v>
+        <v>91242</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6288,21 +6288,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6315,10 +6315,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>438928</v>
+        <v>438797</v>
       </c>
       <c r="R57" t="n">
-        <v>6783763</v>
+        <v>6783670</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6378,10 +6378,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126243462</v>
+        <v>126243823</v>
       </c>
       <c r="B58" t="n">
-        <v>78977</v>
+        <v>82789</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6389,21 +6389,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>438777</v>
+        <v>438911</v>
       </c>
       <c r="R58" t="n">
-        <v>6783527</v>
+        <v>6783821</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6479,7 +6479,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126243986</v>
+        <v>126243980</v>
       </c>
       <c r="B59" t="n">
         <v>78977</v>
@@ -6517,10 +6517,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>438947</v>
+        <v>438928</v>
       </c>
       <c r="R59" t="n">
-        <v>6783782</v>
+        <v>6783763</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6681,7 +6681,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126243351</v>
+        <v>126243462</v>
       </c>
       <c r="B61" t="n">
         <v>78977</v>
@@ -6719,10 +6719,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>438767</v>
+        <v>438777</v>
       </c>
       <c r="R61" t="n">
-        <v>6783455</v>
+        <v>6783527</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6782,38 +6782,37 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126244294</v>
+        <v>126243351</v>
       </c>
       <c r="B62" t="n">
-        <v>98373</v>
+        <v>78977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -6821,10 +6820,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>438723</v>
+        <v>438767</v>
       </c>
       <c r="R62" t="n">
-        <v>6783752</v>
+        <v>6783455</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6851,12 +6850,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6884,42 +6883,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126243641</v>
+        <v>126243986</v>
       </c>
       <c r="B63" t="n">
-        <v>98373</v>
+        <v>78977</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6927,10 +6921,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>438790</v>
+        <v>438947</v>
       </c>
       <c r="R63" t="n">
-        <v>6783649</v>
+        <v>6783782</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6990,37 +6984,46 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126243823</v>
+        <v>126243492</v>
       </c>
       <c r="B64" t="n">
-        <v>82789</v>
+        <v>56848</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7028,10 +7031,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>438911</v>
+        <v>438871</v>
       </c>
       <c r="R64" t="n">
-        <v>6783821</v>
+        <v>6783612</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7066,13 +7069,17 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Den tog ett s.k sandbad i sandblottan efter en rofyllda.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7091,37 +7098,38 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126243617</v>
+        <v>126244294</v>
       </c>
       <c r="B65" t="n">
-        <v>91242</v>
+        <v>98373</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7129,10 +7137,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>438797</v>
+        <v>438723</v>
       </c>
       <c r="R65" t="n">
-        <v>6783670</v>
+        <v>6783752</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7159,12 +7167,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7192,10 +7200,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126243492</v>
+        <v>126243641</v>
       </c>
       <c r="B66" t="n">
-        <v>56848</v>
+        <v>98373</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7203,35 +7211,31 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7239,10 +7243,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>438871</v>
+        <v>438790</v>
       </c>
       <c r="R66" t="n">
-        <v>6783612</v>
+        <v>6783649</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7277,17 +7281,13 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Den tog ett s.k sandbad i sandblottan efter en rofyllda.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7407,10 +7407,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126242798</v>
+        <v>126244312</v>
       </c>
       <c r="B68" t="n">
-        <v>57653</v>
+        <v>56839</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7418,16 +7418,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7435,12 +7435,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -7450,10 +7462,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>438938</v>
+        <v>438654</v>
       </c>
       <c r="R68" t="n">
-        <v>6783650</v>
+        <v>6783741</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7480,17 +7492,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Mycket hackspår i den ca 160 åriga naturskogen</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7618,10 +7625,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126244312</v>
+        <v>126242798</v>
       </c>
       <c r="B70" t="n">
-        <v>56839</v>
+        <v>57653</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7629,16 +7636,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7646,24 +7653,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -7673,10 +7668,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>438654</v>
+        <v>438938</v>
       </c>
       <c r="R70" t="n">
-        <v>6783741</v>
+        <v>6783650</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7703,12 +7698,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Mycket hackspår i den ca 160 åriga naturskogen</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7837,32 +7837,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126244274</v>
+        <v>126243314</v>
       </c>
       <c r="B72" t="n">
-        <v>82789</v>
+        <v>91829</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>1179</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>438776</v>
+        <v>438816</v>
       </c>
       <c r="R72" t="n">
-        <v>6783788</v>
+        <v>6783530</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7938,38 +7938,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126244337</v>
+        <v>126243042</v>
       </c>
       <c r="B73" t="n">
-        <v>98270</v>
+        <v>79056</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>223591</v>
+        <v>864</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -7977,10 +7976,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>438574</v>
+        <v>438848</v>
       </c>
       <c r="R73" t="n">
-        <v>6783811</v>
+        <v>6783520</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8007,12 +8006,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8040,32 +8039,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126243314</v>
+        <v>126244274</v>
       </c>
       <c r="B74" t="n">
-        <v>91829</v>
+        <v>82789</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1179</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8078,10 +8077,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>438816</v>
+        <v>438776</v>
       </c>
       <c r="R74" t="n">
-        <v>6783530</v>
+        <v>6783788</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8141,10 +8140,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126243042</v>
+        <v>126243459</v>
       </c>
       <c r="B75" t="n">
-        <v>79056</v>
+        <v>79009</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8152,21 +8151,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8179,10 +8178,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>438848</v>
+        <v>438777</v>
       </c>
       <c r="R75" t="n">
-        <v>6783520</v>
+        <v>6783527</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8242,37 +8241,38 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126243459</v>
+        <v>126244337</v>
       </c>
       <c r="B76" t="n">
-        <v>79009</v>
+        <v>98270</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>223591</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>438777</v>
+        <v>438574</v>
       </c>
       <c r="R76" t="n">
-        <v>6783527</v>
+        <v>6783811</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8310,12 +8310,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8545,10 +8545,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126243586</v>
+        <v>126243363</v>
       </c>
       <c r="B79" t="n">
-        <v>57653</v>
+        <v>79595</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8556,31 +8556,26 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8588,10 +8583,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>438805</v>
+        <v>438739</v>
       </c>
       <c r="R79" t="n">
-        <v>6783685</v>
+        <v>6783474</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8632,6 +8627,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8650,7 +8646,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126243208</v>
+        <v>126243586</v>
       </c>
       <c r="B80" t="n">
         <v>57653</v>
@@ -8693,10 +8689,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438777</v>
+        <v>438805</v>
       </c>
       <c r="R80" t="n">
-        <v>6783503</v>
+        <v>6783685</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8755,10 +8751,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126243363</v>
+        <v>126243208</v>
       </c>
       <c r="B81" t="n">
-        <v>79595</v>
+        <v>57653</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8766,26 +8762,31 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8793,10 +8794,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>438739</v>
+        <v>438777</v>
       </c>
       <c r="R81" t="n">
-        <v>6783474</v>
+        <v>6783503</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8837,7 +8838,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8856,32 +8856,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126243608</v>
+        <v>126243505</v>
       </c>
       <c r="B82" t="n">
-        <v>91600</v>
+        <v>80115</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2062</v>
+        <v>6463</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8894,10 +8894,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>438797</v>
+        <v>438858</v>
       </c>
       <c r="R82" t="n">
-        <v>6783670</v>
+        <v>6783695</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8957,10 +8957,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126243220</v>
+        <v>126243816</v>
       </c>
       <c r="B83" t="n">
-        <v>91207</v>
+        <v>98270</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8968,26 +8968,27 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>223591</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -8995,10 +8996,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>438775</v>
+        <v>438886</v>
       </c>
       <c r="R83" t="n">
-        <v>6783504</v>
+        <v>6783805</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9058,32 +9059,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126243452</v>
+        <v>126243608</v>
       </c>
       <c r="B84" t="n">
-        <v>78977</v>
+        <v>91600</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9096,10 +9097,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>438740</v>
+        <v>438797</v>
       </c>
       <c r="R84" t="n">
-        <v>6783462</v>
+        <v>6783670</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9159,10 +9160,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126243505</v>
+        <v>126243220</v>
       </c>
       <c r="B85" t="n">
-        <v>80115</v>
+        <v>91207</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9170,21 +9171,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9197,10 +9198,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>438858</v>
+        <v>438775</v>
       </c>
       <c r="R85" t="n">
-        <v>6783695</v>
+        <v>6783504</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9260,32 +9261,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126243191</v>
+        <v>126243452</v>
       </c>
       <c r="B86" t="n">
-        <v>79063</v>
+        <v>78977</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9298,10 +9299,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>438777</v>
+        <v>438740</v>
       </c>
       <c r="R86" t="n">
-        <v>6783503</v>
+        <v>6783462</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9361,42 +9362,37 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126243732</v>
+        <v>126243191</v>
       </c>
       <c r="B87" t="n">
-        <v>57653</v>
+        <v>79063</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>6450</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9404,10 +9400,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>438882</v>
+        <v>438777</v>
       </c>
       <c r="R87" t="n">
-        <v>6783685</v>
+        <v>6783503</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9448,6 +9444,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9466,38 +9463,42 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126243816</v>
+        <v>126243732</v>
       </c>
       <c r="B88" t="n">
-        <v>98270</v>
+        <v>57653</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>223591</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -9505,10 +9506,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>438886</v>
+        <v>438882</v>
       </c>
       <c r="R88" t="n">
-        <v>6783805</v>
+        <v>6783685</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9549,7 +9550,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9674,10 +9674,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126243143</v>
+        <v>126249487</v>
       </c>
       <c r="B90" t="n">
-        <v>56848</v>
+        <v>98373</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9685,45 +9685,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Hålberg-Räklitt, Dlr</t>
+          <t>Räklitt, Hållberg, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>438785</v>
+        <v>438890</v>
       </c>
       <c r="R90" t="n">
-        <v>6783487</v>
+        <v>6783610</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9747,17 +9739,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>21:07</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>En hona och 5 kycklingar</t>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>21:07</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9772,22 +9769,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126249487</v>
+        <v>126243143</v>
       </c>
       <c r="B91" t="n">
-        <v>98373</v>
+        <v>56848</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9795,37 +9792,45 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Räklitt, Hållberg, Dlr</t>
+          <t>Hålberg-Räklitt, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>438890</v>
+        <v>438785</v>
       </c>
       <c r="R91" t="n">
-        <v>6783610</v>
+        <v>6783487</v>
       </c>
       <c r="S91" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9849,22 +9854,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>21:07</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>21:07</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>En hona och 5 kycklingar</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9879,12 +9879,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY98"/>
+  <dimension ref="A1:AY123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5667,42 +5667,37 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126242940</v>
+        <v>126243769</v>
       </c>
       <c r="B51" t="n">
-        <v>57653</v>
+        <v>78340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5713,7 +5708,7 @@
         <v>438898</v>
       </c>
       <c r="R51" t="n">
-        <v>6783622</v>
+        <v>6783784</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5754,6 +5749,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5772,32 +5768,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126243769</v>
+        <v>126243499</v>
       </c>
       <c r="B52" t="n">
-        <v>78340</v>
+        <v>82789</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>498</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5810,10 +5806,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>438898</v>
+        <v>438858</v>
       </c>
       <c r="R52" t="n">
-        <v>6783784</v>
+        <v>6783695</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5873,10 +5869,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126243499</v>
+        <v>126244009</v>
       </c>
       <c r="B53" t="n">
-        <v>82789</v>
+        <v>78977</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5884,21 +5880,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5911,10 +5907,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>438858</v>
+        <v>438925</v>
       </c>
       <c r="R53" t="n">
-        <v>6783695</v>
+        <v>6783804</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5974,7 +5970,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126244009</v>
+        <v>126243332</v>
       </c>
       <c r="B54" t="n">
         <v>78977</v>
@@ -6012,10 +6008,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>438925</v>
+        <v>438770</v>
       </c>
       <c r="R54" t="n">
-        <v>6783804</v>
+        <v>6783484</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6075,7 +6071,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126243332</v>
+        <v>126243713</v>
       </c>
       <c r="B55" t="n">
         <v>78977</v>
@@ -6113,10 +6109,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>438770</v>
+        <v>438875</v>
       </c>
       <c r="R55" t="n">
-        <v>6783484</v>
+        <v>6783718</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6176,10 +6172,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126243713</v>
+        <v>126242940</v>
       </c>
       <c r="B56" t="n">
-        <v>78977</v>
+        <v>57653</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6187,26 +6183,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6214,10 +6215,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>438875</v>
+        <v>438898</v>
       </c>
       <c r="R56" t="n">
-        <v>6783718</v>
+        <v>6783622</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6258,7 +6259,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7837,37 +7837,38 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126243314</v>
+        <v>126244337</v>
       </c>
       <c r="B72" t="n">
-        <v>91829</v>
+        <v>98270</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1179</v>
+        <v>223591</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7875,10 +7876,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>438816</v>
+        <v>438574</v>
       </c>
       <c r="R72" t="n">
-        <v>6783530</v>
+        <v>6783811</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7905,12 +7906,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7938,32 +7939,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126243042</v>
+        <v>126243314</v>
       </c>
       <c r="B73" t="n">
-        <v>79056</v>
+        <v>91829</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>864</v>
+        <v>1179</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7976,10 +7977,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>438848</v>
+        <v>438816</v>
       </c>
       <c r="R73" t="n">
-        <v>6783520</v>
+        <v>6783530</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8039,10 +8040,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126244274</v>
+        <v>126243042</v>
       </c>
       <c r="B74" t="n">
-        <v>82789</v>
+        <v>79056</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8050,21 +8051,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8077,10 +8078,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>438776</v>
+        <v>438848</v>
       </c>
       <c r="R74" t="n">
-        <v>6783788</v>
+        <v>6783520</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8140,10 +8141,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126243459</v>
+        <v>126244274</v>
       </c>
       <c r="B75" t="n">
-        <v>79009</v>
+        <v>82789</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8151,21 +8152,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8178,10 +8179,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>438777</v>
+        <v>438776</v>
       </c>
       <c r="R75" t="n">
-        <v>6783527</v>
+        <v>6783788</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8241,38 +8242,37 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126244337</v>
+        <v>126243459</v>
       </c>
       <c r="B76" t="n">
-        <v>98270</v>
+        <v>79009</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>223591</v>
+        <v>185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>438574</v>
+        <v>438777</v>
       </c>
       <c r="R76" t="n">
-        <v>6783811</v>
+        <v>6783527</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8310,12 +8310,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9891,10 +9891,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126243503</v>
+        <v>126243447</v>
       </c>
       <c r="B92" t="n">
-        <v>78977</v>
+        <v>82789</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9902,21 +9902,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>438858</v>
+        <v>438740</v>
       </c>
       <c r="R92" t="n">
-        <v>6783695</v>
+        <v>6783462</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9992,10 +9992,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126243415</v>
+        <v>126243973</v>
       </c>
       <c r="B93" t="n">
-        <v>57653</v>
+        <v>88651</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10003,31 +10003,26 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10035,10 +10030,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>438722</v>
+        <v>438928</v>
       </c>
       <c r="R93" t="n">
-        <v>6783470</v>
+        <v>6783763</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10079,6 +10074,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10097,39 +10093,37 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126244082</v>
+        <v>126243503</v>
       </c>
       <c r="B94" t="n">
-        <v>5176</v>
+        <v>78977</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10137,10 +10131,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>438809</v>
+        <v>438858</v>
       </c>
       <c r="R94" t="n">
-        <v>6783806</v>
+        <v>6783695</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10200,10 +10194,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126244320</v>
+        <v>126244082</v>
       </c>
       <c r="B95" t="n">
-        <v>98270</v>
+        <v>5176</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10211,27 +10205,28 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>223591</v>
+        <v>100526</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10239,10 +10234,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>438606</v>
+        <v>438809</v>
       </c>
       <c r="R95" t="n">
-        <v>6783759</v>
+        <v>6783806</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10269,12 +10264,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10403,10 +10398,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126243447</v>
+        <v>126243415</v>
       </c>
       <c r="B97" t="n">
-        <v>82789</v>
+        <v>57653</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10414,26 +10409,31 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -10441,10 +10441,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>438740</v>
+        <v>438722</v>
       </c>
       <c r="R97" t="n">
-        <v>6783462</v>
+        <v>6783470</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10485,7 +10485,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10504,37 +10503,38 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126243973</v>
+        <v>126244320</v>
       </c>
       <c r="B98" t="n">
-        <v>88651</v>
+        <v>98270</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>510</v>
+        <v>223591</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -10542,10 +10542,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>438928</v>
+        <v>438606</v>
       </c>
       <c r="R98" t="n">
-        <v>6783763</v>
+        <v>6783759</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10572,12 +10572,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10602,6 +10602,2581 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>126461095</v>
+      </c>
+      <c r="B99" t="n">
+        <v>78739</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>438336</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6783605</v>
+      </c>
+      <c r="S99" t="n">
+        <v>5</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>126461102</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79569</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>438336</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6783605</v>
+      </c>
+      <c r="S100" t="n">
+        <v>5</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>126461226</v>
+      </c>
+      <c r="B101" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>438392</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6783641</v>
+      </c>
+      <c r="S101" t="n">
+        <v>5</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>126461087</v>
+      </c>
+      <c r="B102" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>438336</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6783605</v>
+      </c>
+      <c r="S102" t="n">
+        <v>5</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>126461299</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79598</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>438442</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6783684</v>
+      </c>
+      <c r="S103" t="n">
+        <v>5</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF103" t="inlineStr"/>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>126461061</v>
+      </c>
+      <c r="B104" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>438321</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6783652</v>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>126461208</v>
+      </c>
+      <c r="B105" t="n">
+        <v>56840</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>438365</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6783632</v>
+      </c>
+      <c r="S105" t="n">
+        <v>5</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Det är nog samma tupp som sågs tidigare i en annan del av naturskogsområdet.</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>126461364</v>
+      </c>
+      <c r="B106" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>438536</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6783800</v>
+      </c>
+      <c r="S106" t="n">
+        <v>5</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>126461268</v>
+      </c>
+      <c r="B107" t="n">
+        <v>79569</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>438442</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6783684</v>
+      </c>
+      <c r="S107" t="n">
+        <v>5</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>126461349</v>
+      </c>
+      <c r="B108" t="n">
+        <v>78980</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>438555</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6783786</v>
+      </c>
+      <c r="S108" t="n">
+        <v>5</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF108" t="inlineStr"/>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>126461224</v>
+      </c>
+      <c r="B109" t="n">
+        <v>98382</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>438380</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6783647</v>
+      </c>
+      <c r="S109" t="n">
+        <v>5</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="inlineStr"/>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>126461150</v>
+      </c>
+      <c r="B110" t="n">
+        <v>79598</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>438351</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6783622</v>
+      </c>
+      <c r="S110" t="n">
+        <v>5</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="inlineStr"/>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>126461340</v>
+      </c>
+      <c r="B111" t="n">
+        <v>91259</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>438582</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6783777</v>
+      </c>
+      <c r="S111" t="n">
+        <v>5</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF111" t="inlineStr"/>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>126461070</v>
+      </c>
+      <c r="B112" t="n">
+        <v>79569</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>438313</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6783667</v>
+      </c>
+      <c r="S112" t="n">
+        <v>5</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>126461229</v>
+      </c>
+      <c r="B113" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>438392</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6783641</v>
+      </c>
+      <c r="S113" t="n">
+        <v>5</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>126461046</v>
+      </c>
+      <c r="B114" t="n">
+        <v>79598</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>438314</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6783625</v>
+      </c>
+      <c r="S114" t="n">
+        <v>5</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>126461328</v>
+      </c>
+      <c r="B115" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>438561</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6783774</v>
+      </c>
+      <c r="S115" t="n">
+        <v>5</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>126461132</v>
+      </c>
+      <c r="B116" t="n">
+        <v>5176</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>438349</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6783604</v>
+      </c>
+      <c r="S116" t="n">
+        <v>5</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>126461124</v>
+      </c>
+      <c r="B117" t="n">
+        <v>82792</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>438349</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6783604</v>
+      </c>
+      <c r="S117" t="n">
+        <v>5</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>126461255</v>
+      </c>
+      <c r="B118" t="n">
+        <v>80955</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>438442</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6783684</v>
+      </c>
+      <c r="S118" t="n">
+        <v>5</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>126461372</v>
+      </c>
+      <c r="B119" t="n">
+        <v>80955</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Kortskaftad ärgspik</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Microcalicium ahlneri</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>438511</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6783816</v>
+      </c>
+      <c r="S119" t="n">
+        <v>5</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>126461139</v>
+      </c>
+      <c r="B120" t="n">
+        <v>4772</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>438349</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6783604</v>
+      </c>
+      <c r="S120" t="n">
+        <v>5</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>126461004</v>
+      </c>
+      <c r="B121" t="n">
+        <v>98361</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>438748</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6783732</v>
+      </c>
+      <c r="S121" t="n">
+        <v>5</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Enstaka som är ganska gömda i bärriset. Troligen finns det fler i  den gamla grandominerade naturskogen men de är svåra att upptäcka pga. all bärris.</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>126461025</v>
+      </c>
+      <c r="B122" t="n">
+        <v>78738</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>438292</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6783621</v>
+      </c>
+      <c r="S122" t="n">
+        <v>5</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>126461068</v>
+      </c>
+      <c r="B123" t="n">
+        <v>78738</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>438313</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6783667</v>
+      </c>
+      <c r="S123" t="n">
+        <v>5</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126223492</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -889,39 +889,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126244085</v>
+        <v>126243254</v>
       </c>
       <c r="B4" t="n">
-        <v>4772</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -929,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438809</v>
+        <v>438790</v>
       </c>
       <c r="R4" t="n">
-        <v>6783806</v>
+        <v>6783520</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,38 +990,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126243811</v>
+        <v>126242851</v>
       </c>
       <c r="B5" t="n">
-        <v>98373</v>
+        <v>78980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1031,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438886</v>
+        <v>438926</v>
       </c>
       <c r="R5" t="n">
-        <v>6783805</v>
+        <v>6783631</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1094,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126243187</v>
+        <v>126243055</v>
       </c>
       <c r="B6" t="n">
-        <v>80952</v>
+        <v>78980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1105,21 +1102,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438777</v>
+        <v>438823</v>
       </c>
       <c r="R6" t="n">
-        <v>6783503</v>
+        <v>6783513</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1195,10 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126243254</v>
+        <v>126242965</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>57654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1206,26 +1203,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1233,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438790</v>
+        <v>438888</v>
       </c>
       <c r="R7" t="n">
-        <v>6783520</v>
+        <v>6783584</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1277,7 +1279,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1296,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126242851</v>
+        <v>126243187</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>80955</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1334,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438926</v>
+        <v>438777</v>
       </c>
       <c r="R8" t="n">
-        <v>6783631</v>
+        <v>6783503</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,37 +1398,39 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126243055</v>
+        <v>126244085</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>4772</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1435,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438823</v>
+        <v>438809</v>
       </c>
       <c r="R9" t="n">
-        <v>6783513</v>
+        <v>6783806</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1498,42 +1501,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126242965</v>
+        <v>126243811</v>
       </c>
       <c r="B10" t="n">
-        <v>57653</v>
+        <v>98382</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1541,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438888</v>
+        <v>438886</v>
       </c>
       <c r="R10" t="n">
-        <v>6783584</v>
+        <v>6783805</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1585,6 +1584,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>126244046</v>
       </c>
       <c r="B11" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>126243614</v>
       </c>
       <c r="B12" t="n">
-        <v>88651</v>
+        <v>88654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,37 +1806,38 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126243933</v>
+        <v>126243784</v>
       </c>
       <c r="B13" t="n">
-        <v>82789</v>
+        <v>98382</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1844,10 +1845,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438928</v>
+        <v>438893</v>
       </c>
       <c r="R13" t="n">
-        <v>6783763</v>
+        <v>6783787</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1910,7 +1911,7 @@
         <v>126243682</v>
       </c>
       <c r="B14" t="n">
-        <v>88651</v>
+        <v>88654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,10 +2009,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126243724</v>
+        <v>126243933</v>
       </c>
       <c r="B15" t="n">
-        <v>91863</v>
+        <v>82792</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2019,21 +2020,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5454</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438883</v>
+        <v>438928</v>
       </c>
       <c r="R15" t="n">
-        <v>6783662</v>
+        <v>6783763</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2109,38 +2110,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126243784</v>
+        <v>126243724</v>
       </c>
       <c r="B16" t="n">
-        <v>98373</v>
+        <v>91866</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>5454</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438893</v>
+        <v>438883</v>
       </c>
       <c r="R16" t="n">
-        <v>6783787</v>
+        <v>6783662</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2214,7 +2214,7 @@
         <v>126244296</v>
       </c>
       <c r="B17" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>126244055</v>
       </c>
       <c r="B18" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126243709</v>
+        <v>126243527</v>
       </c>
       <c r="B19" t="n">
-        <v>82789</v>
+        <v>91259</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,21 +2424,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438875</v>
+        <v>438826</v>
       </c>
       <c r="R19" t="n">
-        <v>6783718</v>
+        <v>6783693</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2514,10 +2514,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126244007</v>
+        <v>126243709</v>
       </c>
       <c r="B20" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438925</v>
+        <v>438875</v>
       </c>
       <c r="R20" t="n">
-        <v>6783804</v>
+        <v>6783718</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126243757</v>
+        <v>126244007</v>
       </c>
       <c r="B21" t="n">
-        <v>79056</v>
+        <v>82792</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438889</v>
+        <v>438925</v>
       </c>
       <c r="R21" t="n">
-        <v>6783762</v>
+        <v>6783804</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2716,32 +2716,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126243075</v>
+        <v>126243757</v>
       </c>
       <c r="B22" t="n">
-        <v>79063</v>
+        <v>79059</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6450</v>
+        <v>864</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438799</v>
+        <v>438889</v>
       </c>
       <c r="R22" t="n">
-        <v>6783496</v>
+        <v>6783762</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2820,7 +2820,7 @@
         <v>126242913</v>
       </c>
       <c r="B23" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2918,32 +2918,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126243527</v>
+        <v>126243075</v>
       </c>
       <c r="B24" t="n">
-        <v>91256</v>
+        <v>79066</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>6450</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>438826</v>
+        <v>438799</v>
       </c>
       <c r="R24" t="n">
-        <v>6783693</v>
+        <v>6783496</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3022,7 +3022,7 @@
         <v>126243439</v>
       </c>
       <c r="B25" t="n">
-        <v>88651</v>
+        <v>88654</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>126243565</v>
       </c>
       <c r="B26" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3221,10 +3221,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126243148</v>
+        <v>126243742</v>
       </c>
       <c r="B27" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438785</v>
+        <v>438885</v>
       </c>
       <c r="R27" t="n">
-        <v>6783487</v>
+        <v>6783710</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3322,10 +3322,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126243348</v>
+        <v>126243148</v>
       </c>
       <c r="B28" t="n">
-        <v>79009</v>
+        <v>78980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3333,21 +3333,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438767</v>
+        <v>438785</v>
       </c>
       <c r="R28" t="n">
-        <v>6783455</v>
+        <v>6783487</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3423,37 +3423,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126243738</v>
+        <v>126243647</v>
       </c>
       <c r="B29" t="n">
-        <v>79009</v>
+        <v>97239</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3461,10 +3462,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438885</v>
+        <v>438790</v>
       </c>
       <c r="R29" t="n">
-        <v>6783710</v>
+        <v>6783649</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3524,10 +3525,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126243342</v>
+        <v>126243348</v>
       </c>
       <c r="B30" t="n">
-        <v>82789</v>
+        <v>79012</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3535,21 +3536,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3625,10 +3626,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126244253</v>
+        <v>126243738</v>
       </c>
       <c r="B31" t="n">
-        <v>82789</v>
+        <v>79012</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3636,21 +3637,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3663,10 +3664,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438791</v>
+        <v>438885</v>
       </c>
       <c r="R31" t="n">
-        <v>6783795</v>
+        <v>6783710</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3726,10 +3727,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126243742</v>
+        <v>126243342</v>
       </c>
       <c r="B32" t="n">
-        <v>78977</v>
+        <v>82792</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3737,21 +3738,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3764,10 +3765,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438885</v>
+        <v>438767</v>
       </c>
       <c r="R32" t="n">
-        <v>6783710</v>
+        <v>6783455</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3827,38 +3828,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126243647</v>
+        <v>126244253</v>
       </c>
       <c r="B33" t="n">
-        <v>97230</v>
+        <v>82792</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>438790</v>
+        <v>438791</v>
       </c>
       <c r="R33" t="n">
-        <v>6783649</v>
+        <v>6783795</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3929,38 +3929,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126244106</v>
+        <v>126244571</v>
       </c>
       <c r="B34" t="n">
-        <v>98373</v>
+        <v>82792</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3968,10 +3967,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438782</v>
+        <v>438751</v>
       </c>
       <c r="R34" t="n">
-        <v>6783777</v>
+        <v>6783884</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3998,12 +3997,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4031,10 +4030,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126244571</v>
+        <v>126244328</v>
       </c>
       <c r="B35" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4069,10 +4068,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>438751</v>
+        <v>438584</v>
       </c>
       <c r="R35" t="n">
-        <v>6783884</v>
+        <v>6783774</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4132,32 +4131,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126244328</v>
+        <v>126243379</v>
       </c>
       <c r="B36" t="n">
-        <v>82789</v>
+        <v>79066</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>6450</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4170,10 +4169,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>438584</v>
+        <v>438694</v>
       </c>
       <c r="R36" t="n">
-        <v>6783774</v>
+        <v>6783458</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4200,12 +4199,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4233,10 +4232,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126243379</v>
+        <v>126244106</v>
       </c>
       <c r="B37" t="n">
-        <v>79063</v>
+        <v>98382</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4244,26 +4243,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6450</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>438694</v>
+        <v>438782</v>
       </c>
       <c r="R37" t="n">
-        <v>6783458</v>
+        <v>6783777</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4337,7 +4337,7 @@
         <v>126243450</v>
       </c>
       <c r="B38" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         <v>126243521</v>
       </c>
       <c r="B39" t="n">
-        <v>91207</v>
+        <v>91210</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         <v>126242981</v>
       </c>
       <c r="B40" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4640,7 +4640,7 @@
         <v>126244026</v>
       </c>
       <c r="B41" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4739,39 +4739,35 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126243702</v>
+        <v>126244589</v>
       </c>
       <c r="B42" t="n">
-        <v>98352</v>
+        <v>98382</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -4782,10 +4778,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>438786</v>
+        <v>438824</v>
       </c>
       <c r="R42" t="n">
-        <v>6783704</v>
+        <v>6783885</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4812,12 +4808,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4845,10 +4841,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126244589</v>
+        <v>126243995</v>
       </c>
       <c r="B43" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4884,10 +4880,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>438824</v>
+        <v>438953</v>
       </c>
       <c r="R43" t="n">
-        <v>6783885</v>
+        <v>6783788</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4914,12 +4910,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4947,35 +4943,39 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126243995</v>
+        <v>126243702</v>
       </c>
       <c r="B44" t="n">
-        <v>98373</v>
+        <v>98361</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>438953</v>
+        <v>438786</v>
       </c>
       <c r="R44" t="n">
-        <v>6783788</v>
+        <v>6783704</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5052,7 +5052,7 @@
         <v>126244033</v>
       </c>
       <c r="B45" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>126243519</v>
       </c>
       <c r="B46" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>126244099</v>
       </c>
       <c r="B47" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5367,7 +5367,7 @@
         <v>126243010</v>
       </c>
       <c r="B48" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>126243233</v>
       </c>
       <c r="B49" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>126243370</v>
       </c>
       <c r="B50" t="n">
-        <v>79595</v>
+        <v>79598</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         <v>126243769</v>
       </c>
       <c r="B51" t="n">
-        <v>78340</v>
+        <v>78343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5771,7 +5771,7 @@
         <v>126243499</v>
       </c>
       <c r="B52" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>126244009</v>
       </c>
       <c r="B53" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>126243332</v>
       </c>
       <c r="B54" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6074,7 +6074,7 @@
         <v>126243713</v>
       </c>
       <c r="B55" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>126242940</v>
       </c>
       <c r="B56" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>126243617</v>
       </c>
       <c r="B57" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>126243823</v>
       </c>
       <c r="B58" t="n">
-        <v>82789</v>
+        <v>82792</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6479,10 +6479,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126243980</v>
+        <v>126243986</v>
       </c>
       <c r="B59" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6517,10 +6517,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>438928</v>
+        <v>438947</v>
       </c>
       <c r="R59" t="n">
-        <v>6783763</v>
+        <v>6783782</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6580,10 +6580,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126244052</v>
+        <v>126243980</v>
       </c>
       <c r="B60" t="n">
-        <v>79595</v>
+        <v>78980</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6591,21 +6591,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>438821</v>
+        <v>438928</v>
       </c>
       <c r="R60" t="n">
-        <v>6783854</v>
+        <v>6783763</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6684,7 +6684,7 @@
         <v>126243462</v>
       </c>
       <c r="B61" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>126243351</v>
       </c>
       <c r="B62" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6883,10 +6883,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126243986</v>
+        <v>126244052</v>
       </c>
       <c r="B63" t="n">
-        <v>78977</v>
+        <v>79598</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6894,21 +6894,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>438947</v>
+        <v>438821</v>
       </c>
       <c r="R63" t="n">
-        <v>6783782</v>
+        <v>6783854</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6987,7 +6987,7 @@
         <v>126243492</v>
       </c>
       <c r="B64" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7098,10 +7098,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126244294</v>
+        <v>126243641</v>
       </c>
       <c r="B65" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7126,7 +7126,11 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
@@ -7137,10 +7141,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>438723</v>
+        <v>438790</v>
       </c>
       <c r="R65" t="n">
-        <v>6783752</v>
+        <v>6783649</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7167,12 +7171,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7200,10 +7204,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126243641</v>
+        <v>126244294</v>
       </c>
       <c r="B66" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7228,11 +7232,7 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
@@ -7243,10 +7243,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>438790</v>
+        <v>438723</v>
       </c>
       <c r="R66" t="n">
-        <v>6783649</v>
+        <v>6783752</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7273,12 +7273,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7306,37 +7306,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126243259</v>
+        <v>126244312</v>
       </c>
       <c r="B67" t="n">
-        <v>91207</v>
+        <v>56840</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7344,10 +7361,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>438790</v>
+        <v>438654</v>
       </c>
       <c r="R67" t="n">
-        <v>6783520</v>
+        <v>6783741</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7374,12 +7391,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7388,7 +7405,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7407,54 +7423,37 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126244312</v>
+        <v>126243259</v>
       </c>
       <c r="B68" t="n">
-        <v>56839</v>
+        <v>91210</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7462,10 +7461,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>438654</v>
+        <v>438790</v>
       </c>
       <c r="R68" t="n">
-        <v>6783741</v>
+        <v>6783520</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7492,12 +7491,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7506,6 +7505,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7527,7 +7527,7 @@
         <v>126242918</v>
       </c>
       <c r="B69" t="n">
-        <v>79009</v>
+        <v>79012</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>126242798</v>
       </c>
       <c r="B70" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>126244077</v>
       </c>
       <c r="B71" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7837,38 +7837,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126244337</v>
+        <v>126243314</v>
       </c>
       <c r="B72" t="n">
-        <v>98270</v>
+        <v>91832</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>223591</v>
+        <v>1179</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7876,10 +7875,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>438574</v>
+        <v>438816</v>
       </c>
       <c r="R72" t="n">
-        <v>6783811</v>
+        <v>6783530</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7906,12 +7905,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7939,32 +7938,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126243314</v>
+        <v>126243042</v>
       </c>
       <c r="B73" t="n">
-        <v>91829</v>
+        <v>79059</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1179</v>
+        <v>864</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7977,10 +7976,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>438816</v>
+        <v>438848</v>
       </c>
       <c r="R73" t="n">
-        <v>6783530</v>
+        <v>6783520</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8040,10 +8039,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126243042</v>
+        <v>126244274</v>
       </c>
       <c r="B74" t="n">
-        <v>79056</v>
+        <v>82792</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8051,21 +8050,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8078,10 +8077,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>438848</v>
+        <v>438776</v>
       </c>
       <c r="R74" t="n">
-        <v>6783520</v>
+        <v>6783788</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8141,10 +8140,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126244274</v>
+        <v>126243459</v>
       </c>
       <c r="B75" t="n">
-        <v>82789</v>
+        <v>79012</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8152,21 +8151,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8179,10 +8178,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>438776</v>
+        <v>438777</v>
       </c>
       <c r="R75" t="n">
-        <v>6783788</v>
+        <v>6783527</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8242,37 +8241,38 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126243459</v>
+        <v>126244337</v>
       </c>
       <c r="B76" t="n">
-        <v>79009</v>
+        <v>98279</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>185</v>
+        <v>223591</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>438777</v>
+        <v>438574</v>
       </c>
       <c r="R76" t="n">
-        <v>6783527</v>
+        <v>6783811</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8310,12 +8310,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8346,7 +8346,7 @@
         <v>126243070</v>
       </c>
       <c r="B77" t="n">
-        <v>79009</v>
+        <v>79012</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>126243991</v>
       </c>
       <c r="B78" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8545,10 +8545,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126243363</v>
+        <v>126243586</v>
       </c>
       <c r="B79" t="n">
-        <v>79595</v>
+        <v>57654</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8556,26 +8556,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8583,10 +8588,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>438739</v>
+        <v>438805</v>
       </c>
       <c r="R79" t="n">
-        <v>6783474</v>
+        <v>6783685</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8627,7 +8632,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8646,10 +8650,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126243586</v>
+        <v>126243208</v>
       </c>
       <c r="B80" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8689,10 +8693,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438805</v>
+        <v>438777</v>
       </c>
       <c r="R80" t="n">
-        <v>6783685</v>
+        <v>6783503</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8751,10 +8755,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126243208</v>
+        <v>126243363</v>
       </c>
       <c r="B81" t="n">
-        <v>57653</v>
+        <v>79598</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8762,31 +8766,26 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8794,10 +8793,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>438777</v>
+        <v>438739</v>
       </c>
       <c r="R81" t="n">
-        <v>6783503</v>
+        <v>6783474</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8838,6 +8837,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8856,10 +8856,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126243505</v>
+        <v>126243220</v>
       </c>
       <c r="B82" t="n">
-        <v>80115</v>
+        <v>91210</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8867,21 +8867,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8894,10 +8894,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>438858</v>
+        <v>438775</v>
       </c>
       <c r="R82" t="n">
-        <v>6783695</v>
+        <v>6783504</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8957,38 +8957,37 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126243816</v>
+        <v>126243452</v>
       </c>
       <c r="B83" t="n">
-        <v>98270</v>
+        <v>78980</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>223591</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -8996,10 +8995,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>438886</v>
+        <v>438740</v>
       </c>
       <c r="R83" t="n">
-        <v>6783805</v>
+        <v>6783462</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9059,32 +9058,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126243608</v>
+        <v>126243505</v>
       </c>
       <c r="B84" t="n">
-        <v>91600</v>
+        <v>80118</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2062</v>
+        <v>6463</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9097,10 +9096,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>438797</v>
+        <v>438858</v>
       </c>
       <c r="R84" t="n">
-        <v>6783670</v>
+        <v>6783695</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9160,10 +9159,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126243220</v>
+        <v>126243191</v>
       </c>
       <c r="B85" t="n">
-        <v>91207</v>
+        <v>79066</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9171,21 +9170,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5447</v>
+        <v>6450</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9198,10 +9197,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>438775</v>
+        <v>438777</v>
       </c>
       <c r="R85" t="n">
-        <v>6783504</v>
+        <v>6783503</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9261,32 +9260,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126243452</v>
+        <v>126243608</v>
       </c>
       <c r="B86" t="n">
-        <v>78977</v>
+        <v>91603</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9299,10 +9298,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>438740</v>
+        <v>438797</v>
       </c>
       <c r="R86" t="n">
-        <v>6783462</v>
+        <v>6783670</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9362,37 +9361,42 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126243191</v>
+        <v>126243732</v>
       </c>
       <c r="B87" t="n">
-        <v>79063</v>
+        <v>57654</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6450</v>
+        <v>100049</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9400,10 +9404,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>438777</v>
+        <v>438882</v>
       </c>
       <c r="R87" t="n">
-        <v>6783503</v>
+        <v>6783685</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9444,7 +9448,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9463,42 +9466,42 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126243732</v>
+        <v>126243676</v>
       </c>
       <c r="B88" t="n">
-        <v>57653</v>
+        <v>98382</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>221952</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -9506,10 +9509,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>438882</v>
+        <v>438813</v>
       </c>
       <c r="R88" t="n">
-        <v>6783685</v>
+        <v>6783722</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9550,6 +9553,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9568,10 +9572,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126243676</v>
+        <v>126243816</v>
       </c>
       <c r="B89" t="n">
-        <v>98373</v>
+        <v>98279</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9579,28 +9583,24 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221952</v>
+        <v>223591</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
@@ -9611,10 +9611,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>438813</v>
+        <v>438886</v>
       </c>
       <c r="R89" t="n">
-        <v>6783722</v>
+        <v>6783805</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9674,10 +9674,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126249487</v>
+        <v>126243143</v>
       </c>
       <c r="B90" t="n">
-        <v>98373</v>
+        <v>56849</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9685,37 +9685,45 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Räklitt, Hållberg, Dlr</t>
+          <t>Hålberg-Räklitt, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>438890</v>
+        <v>438785</v>
       </c>
       <c r="R90" t="n">
-        <v>6783610</v>
+        <v>6783487</v>
       </c>
       <c r="S90" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9739,22 +9747,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>21:07</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>21:07</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>En hona och 5 kycklingar</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9769,22 +9772,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126243143</v>
+        <v>126249487</v>
       </c>
       <c r="B91" t="n">
-        <v>56848</v>
+        <v>98382</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9792,45 +9795,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Hålberg-Räklitt, Dlr</t>
+          <t>Räklitt, Hållberg, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>438785</v>
+        <v>438890</v>
       </c>
       <c r="R91" t="n">
-        <v>6783487</v>
+        <v>6783610</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9854,17 +9849,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>21:07</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>En hona och 5 kycklingar</t>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>21:07</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9879,49 +9879,50 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126243447</v>
+        <v>126244320</v>
       </c>
       <c r="B92" t="n">
-        <v>82789</v>
+        <v>98279</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1312</v>
+        <v>223591</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -9929,10 +9930,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>438740</v>
+        <v>438606</v>
       </c>
       <c r="R92" t="n">
-        <v>6783462</v>
+        <v>6783759</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9959,12 +9960,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9995,7 +9996,7 @@
         <v>126243973</v>
       </c>
       <c r="B93" t="n">
-        <v>88651</v>
+        <v>88654</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10093,10 +10094,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126243503</v>
+        <v>126243447</v>
       </c>
       <c r="B94" t="n">
-        <v>78977</v>
+        <v>82792</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10104,21 +10105,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10131,10 +10132,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>438858</v>
+        <v>438740</v>
       </c>
       <c r="R94" t="n">
-        <v>6783695</v>
+        <v>6783462</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10194,39 +10195,37 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126244082</v>
+        <v>126243503</v>
       </c>
       <c r="B95" t="n">
-        <v>5176</v>
+        <v>78980</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10234,10 +10233,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>438809</v>
+        <v>438858</v>
       </c>
       <c r="R95" t="n">
-        <v>6783806</v>
+        <v>6783695</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10297,10 +10296,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126243395</v>
+        <v>126243415</v>
       </c>
       <c r="B96" t="n">
-        <v>79566</v>
+        <v>57654</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10308,26 +10307,31 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10335,10 +10339,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>438682</v>
+        <v>438722</v>
       </c>
       <c r="R96" t="n">
-        <v>6783454</v>
+        <v>6783470</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10379,7 +10383,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10398,42 +10401,39 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126243415</v>
+        <v>126244082</v>
       </c>
       <c r="B97" t="n">
-        <v>57653</v>
+        <v>5176</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -10441,10 +10441,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>438722</v>
+        <v>438809</v>
       </c>
       <c r="R97" t="n">
-        <v>6783470</v>
+        <v>6783806</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10485,6 +10485,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10503,38 +10504,37 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126244320</v>
+        <v>126243395</v>
       </c>
       <c r="B98" t="n">
-        <v>98270</v>
+        <v>79569</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>223591</v>
+        <v>229821</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -10542,10 +10542,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>438606</v>
+        <v>438682</v>
       </c>
       <c r="R98" t="n">
-        <v>6783759</v>
+        <v>6783454</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10572,12 +10572,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12057,38 +12057,37 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>126461229</v>
+        <v>126461046</v>
       </c>
       <c r="B113" t="n">
-        <v>98279</v>
+        <v>79598</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>223591</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -12096,10 +12095,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>438392</v>
+        <v>438314</v>
       </c>
       <c r="R113" t="n">
-        <v>6783641</v>
+        <v>6783625</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -12159,37 +12158,38 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126461046</v>
+        <v>126461229</v>
       </c>
       <c r="B114" t="n">
-        <v>79598</v>
+        <v>98279</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>223591</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
@@ -12197,10 +12197,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>438314</v>
+        <v>438392</v>
       </c>
       <c r="R114" t="n">
-        <v>6783625</v>
+        <v>6783641</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -12566,7 +12566,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>126461255</v>
+        <v>126461372</v>
       </c>
       <c r="B118" t="n">
         <v>80955</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>438442</v>
+        <v>438511</v>
       </c>
       <c r="R118" t="n">
-        <v>6783684</v>
+        <v>6783816</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12667,7 +12667,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>126461372</v>
+        <v>126461255</v>
       </c>
       <c r="B119" t="n">
         <v>80955</v>
@@ -12705,10 +12705,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>438511</v>
+        <v>438442</v>
       </c>
       <c r="R119" t="n">
-        <v>6783816</v>
+        <v>6783684</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126243254</v>
+        <v>126243187</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>80955</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438790</v>
+        <v>438777</v>
       </c>
       <c r="R4" t="n">
-        <v>6783520</v>
+        <v>6783503</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -990,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126242851</v>
+        <v>126243254</v>
       </c>
       <c r="B5" t="n">
         <v>78980</v>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438926</v>
+        <v>438790</v>
       </c>
       <c r="R5" t="n">
-        <v>6783631</v>
+        <v>6783520</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1091,7 +1091,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126243055</v>
+        <v>126242851</v>
       </c>
       <c r="B6" t="n">
         <v>78980</v>
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438823</v>
+        <v>438926</v>
       </c>
       <c r="R6" t="n">
-        <v>6783513</v>
+        <v>6783631</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1297,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126243187</v>
+        <v>126243055</v>
       </c>
       <c r="B8" t="n">
-        <v>80955</v>
+        <v>78980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438777</v>
+        <v>438823</v>
       </c>
       <c r="R8" t="n">
-        <v>6783503</v>
+        <v>6783513</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -3322,10 +3322,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126243148</v>
+        <v>126243348</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>79012</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3333,21 +3333,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438785</v>
+        <v>438767</v>
       </c>
       <c r="R28" t="n">
-        <v>6783487</v>
+        <v>6783455</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3423,38 +3423,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126243647</v>
+        <v>126243738</v>
       </c>
       <c r="B29" t="n">
-        <v>97239</v>
+        <v>79012</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3462,10 +3461,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438790</v>
+        <v>438885</v>
       </c>
       <c r="R29" t="n">
-        <v>6783649</v>
+        <v>6783710</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3525,10 +3524,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126243348</v>
+        <v>126243342</v>
       </c>
       <c r="B30" t="n">
-        <v>79012</v>
+        <v>82792</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3536,21 +3535,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3626,10 +3625,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126243738</v>
+        <v>126244253</v>
       </c>
       <c r="B31" t="n">
-        <v>79012</v>
+        <v>82792</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3637,21 +3636,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3664,10 +3663,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438885</v>
+        <v>438791</v>
       </c>
       <c r="R31" t="n">
-        <v>6783710</v>
+        <v>6783795</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3727,10 +3726,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126243342</v>
+        <v>126243148</v>
       </c>
       <c r="B32" t="n">
-        <v>82792</v>
+        <v>78980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3738,21 +3737,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3765,10 +3764,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438767</v>
+        <v>438785</v>
       </c>
       <c r="R32" t="n">
-        <v>6783455</v>
+        <v>6783487</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3828,37 +3827,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126244253</v>
+        <v>126243647</v>
       </c>
       <c r="B33" t="n">
-        <v>82792</v>
+        <v>97239</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>438791</v>
+        <v>438790</v>
       </c>
       <c r="R33" t="n">
-        <v>6783795</v>
+        <v>6783649</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -5263,10 +5263,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126244099</v>
+        <v>126243010</v>
       </c>
       <c r="B47" t="n">
-        <v>82792</v>
+        <v>78980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5274,21 +5274,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>438804</v>
+        <v>438852</v>
       </c>
       <c r="R47" t="n">
-        <v>6783800</v>
+        <v>6783530</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5364,7 +5364,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126243010</v>
+        <v>126243233</v>
       </c>
       <c r="B48" t="n">
         <v>78980</v>
@@ -5402,10 +5402,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>438852</v>
+        <v>438775</v>
       </c>
       <c r="R48" t="n">
-        <v>6783530</v>
+        <v>6783504</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5465,10 +5465,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126243233</v>
+        <v>126244099</v>
       </c>
       <c r="B49" t="n">
-        <v>78980</v>
+        <v>82792</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5476,21 +5476,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>438775</v>
+        <v>438804</v>
       </c>
       <c r="R49" t="n">
-        <v>6783504</v>
+        <v>6783800</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5768,10 +5768,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126243499</v>
+        <v>126244009</v>
       </c>
       <c r="B52" t="n">
-        <v>82792</v>
+        <v>78980</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5779,21 +5779,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>438858</v>
+        <v>438925</v>
       </c>
       <c r="R52" t="n">
-        <v>6783695</v>
+        <v>6783804</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5869,7 +5869,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126244009</v>
+        <v>126243332</v>
       </c>
       <c r="B53" t="n">
         <v>78980</v>
@@ -5907,10 +5907,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>438925</v>
+        <v>438770</v>
       </c>
       <c r="R53" t="n">
-        <v>6783804</v>
+        <v>6783484</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5970,7 +5970,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126243332</v>
+        <v>126243713</v>
       </c>
       <c r="B54" t="n">
         <v>78980</v>
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>438770</v>
+        <v>438875</v>
       </c>
       <c r="R54" t="n">
-        <v>6783484</v>
+        <v>6783718</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6071,10 +6071,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126243713</v>
+        <v>126242940</v>
       </c>
       <c r="B55" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6082,26 +6082,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6109,10 +6114,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>438875</v>
+        <v>438898</v>
       </c>
       <c r="R55" t="n">
-        <v>6783718</v>
+        <v>6783622</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6153,7 +6158,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6172,10 +6176,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126242940</v>
+        <v>126243499</v>
       </c>
       <c r="B56" t="n">
-        <v>57654</v>
+        <v>82792</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6183,31 +6187,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6215,10 +6214,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>438898</v>
+        <v>438858</v>
       </c>
       <c r="R56" t="n">
-        <v>6783622</v>
+        <v>6783695</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6259,6 +6258,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7423,10 +7423,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126243259</v>
+        <v>126244077</v>
       </c>
       <c r="B68" t="n">
-        <v>91210</v>
+        <v>98382</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7434,26 +7434,27 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7461,10 +7462,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>438790</v>
+        <v>438852</v>
       </c>
       <c r="R68" t="n">
-        <v>6783520</v>
+        <v>6783837</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7524,32 +7525,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126242918</v>
+        <v>126243259</v>
       </c>
       <c r="B69" t="n">
-        <v>79012</v>
+        <v>91210</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7562,10 +7563,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>438917</v>
+        <v>438790</v>
       </c>
       <c r="R69" t="n">
-        <v>6783626</v>
+        <v>6783520</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7625,10 +7626,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126242798</v>
+        <v>126242918</v>
       </c>
       <c r="B70" t="n">
-        <v>57654</v>
+        <v>79012</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7636,31 +7637,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7668,10 +7664,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>438938</v>
+        <v>438917</v>
       </c>
       <c r="R70" t="n">
-        <v>6783650</v>
+        <v>6783626</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7706,17 +7702,13 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Mycket hackspår i den ca 160 åriga naturskogen</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7735,38 +7727,42 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126244077</v>
+        <v>126242798</v>
       </c>
       <c r="B71" t="n">
-        <v>98382</v>
+        <v>57654</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7774,10 +7770,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>438852</v>
+        <v>438938</v>
       </c>
       <c r="R71" t="n">
-        <v>6783837</v>
+        <v>6783650</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7812,13 +7808,17 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Mycket hackspår i den ca 160 åriga naturskogen</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7837,32 +7837,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126243314</v>
+        <v>126243459</v>
       </c>
       <c r="B72" t="n">
-        <v>91832</v>
+        <v>79012</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1179</v>
+        <v>185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>438816</v>
+        <v>438777</v>
       </c>
       <c r="R72" t="n">
-        <v>6783530</v>
+        <v>6783527</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7938,37 +7938,38 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126243042</v>
+        <v>126244337</v>
       </c>
       <c r="B73" t="n">
-        <v>79059</v>
+        <v>98279</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>864</v>
+        <v>223591</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -7976,10 +7977,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>438848</v>
+        <v>438574</v>
       </c>
       <c r="R73" t="n">
-        <v>6783520</v>
+        <v>6783811</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8006,12 +8007,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8039,32 +8040,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126244274</v>
+        <v>126243314</v>
       </c>
       <c r="B74" t="n">
-        <v>82792</v>
+        <v>91832</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>1179</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8077,10 +8078,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>438776</v>
+        <v>438816</v>
       </c>
       <c r="R74" t="n">
-        <v>6783788</v>
+        <v>6783530</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8140,10 +8141,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126243459</v>
+        <v>126243042</v>
       </c>
       <c r="B75" t="n">
-        <v>79012</v>
+        <v>79059</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8151,21 +8152,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8178,10 +8179,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>438777</v>
+        <v>438848</v>
       </c>
       <c r="R75" t="n">
-        <v>6783527</v>
+        <v>6783520</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8241,38 +8242,37 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126244337</v>
+        <v>126244274</v>
       </c>
       <c r="B76" t="n">
-        <v>98279</v>
+        <v>82792</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>223591</v>
+        <v>1312</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>438574</v>
+        <v>438776</v>
       </c>
       <c r="R76" t="n">
-        <v>6783811</v>
+        <v>6783788</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8310,12 +8310,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8545,10 +8545,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126243586</v>
+        <v>126243363</v>
       </c>
       <c r="B79" t="n">
-        <v>57654</v>
+        <v>79598</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8556,31 +8556,26 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8588,10 +8583,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>438805</v>
+        <v>438739</v>
       </c>
       <c r="R79" t="n">
-        <v>6783685</v>
+        <v>6783474</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8632,6 +8627,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8650,7 +8646,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126243208</v>
+        <v>126243586</v>
       </c>
       <c r="B80" t="n">
         <v>57654</v>
@@ -8693,10 +8689,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438777</v>
+        <v>438805</v>
       </c>
       <c r="R80" t="n">
-        <v>6783503</v>
+        <v>6783685</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8755,10 +8751,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126243363</v>
+        <v>126243208</v>
       </c>
       <c r="B81" t="n">
-        <v>79598</v>
+        <v>57654</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8766,26 +8762,31 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8793,10 +8794,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>438739</v>
+        <v>438777</v>
       </c>
       <c r="R81" t="n">
-        <v>6783474</v>
+        <v>6783503</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8837,7 +8838,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8856,10 +8856,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126243220</v>
+        <v>126243816</v>
       </c>
       <c r="B82" t="n">
-        <v>91210</v>
+        <v>98279</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8867,26 +8867,27 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5447</v>
+        <v>223591</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -8894,10 +8895,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>438775</v>
+        <v>438886</v>
       </c>
       <c r="R82" t="n">
-        <v>6783504</v>
+        <v>6783805</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8957,32 +8958,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126243452</v>
+        <v>126243220</v>
       </c>
       <c r="B83" t="n">
-        <v>78980</v>
+        <v>91210</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8995,10 +8996,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>438740</v>
+        <v>438775</v>
       </c>
       <c r="R83" t="n">
-        <v>6783462</v>
+        <v>6783504</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9058,27 +9059,27 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126243505</v>
+        <v>126243452</v>
       </c>
       <c r="B84" t="n">
-        <v>80118</v>
+        <v>78980</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9096,10 +9097,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>438858</v>
+        <v>438740</v>
       </c>
       <c r="R84" t="n">
-        <v>6783695</v>
+        <v>6783462</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9159,10 +9160,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126243191</v>
+        <v>126243505</v>
       </c>
       <c r="B85" t="n">
-        <v>79066</v>
+        <v>80118</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9170,21 +9171,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6450</v>
+        <v>6463</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9197,10 +9198,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>438777</v>
+        <v>438858</v>
       </c>
       <c r="R85" t="n">
-        <v>6783503</v>
+        <v>6783695</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9260,32 +9261,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126243608</v>
+        <v>126243191</v>
       </c>
       <c r="B86" t="n">
-        <v>91603</v>
+        <v>79066</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2062</v>
+        <v>6450</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9298,10 +9299,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>438797</v>
+        <v>438777</v>
       </c>
       <c r="R86" t="n">
-        <v>6783670</v>
+        <v>6783503</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9361,42 +9362,37 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126243732</v>
+        <v>126243608</v>
       </c>
       <c r="B87" t="n">
-        <v>57654</v>
+        <v>91603</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -9404,10 +9400,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>438882</v>
+        <v>438797</v>
       </c>
       <c r="R87" t="n">
-        <v>6783685</v>
+        <v>6783670</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9448,6 +9444,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9466,42 +9463,42 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126243676</v>
+        <v>126243732</v>
       </c>
       <c r="B88" t="n">
-        <v>98382</v>
+        <v>57654</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -9509,10 +9506,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>438813</v>
+        <v>438882</v>
       </c>
       <c r="R88" t="n">
-        <v>6783722</v>
+        <v>6783685</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9553,7 +9550,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9572,10 +9568,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126243816</v>
+        <v>126243676</v>
       </c>
       <c r="B89" t="n">
-        <v>98279</v>
+        <v>98382</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9583,24 +9579,28 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>223591</v>
+        <v>221952</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
@@ -9611,10 +9611,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>438886</v>
+        <v>438813</v>
       </c>
       <c r="R89" t="n">
-        <v>6783805</v>
+        <v>6783722</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9891,38 +9891,37 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126244320</v>
+        <v>126243973</v>
       </c>
       <c r="B92" t="n">
-        <v>98279</v>
+        <v>88654</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>223591</v>
+        <v>510</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -9930,10 +9929,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>438606</v>
+        <v>438928</v>
       </c>
       <c r="R92" t="n">
-        <v>6783759</v>
+        <v>6783763</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9960,12 +9959,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9993,10 +9992,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126243973</v>
+        <v>126243447</v>
       </c>
       <c r="B93" t="n">
-        <v>88654</v>
+        <v>82792</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10004,21 +10003,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10031,10 +10030,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>438928</v>
+        <v>438740</v>
       </c>
       <c r="R93" t="n">
-        <v>6783763</v>
+        <v>6783462</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10094,10 +10093,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126243447</v>
+        <v>126243503</v>
       </c>
       <c r="B94" t="n">
-        <v>82792</v>
+        <v>78980</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10105,21 +10104,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10132,10 +10131,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>438740</v>
+        <v>438858</v>
       </c>
       <c r="R94" t="n">
-        <v>6783462</v>
+        <v>6783695</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10195,10 +10194,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126243503</v>
+        <v>126243415</v>
       </c>
       <c r="B95" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10206,26 +10205,31 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10233,10 +10237,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>438858</v>
+        <v>438722</v>
       </c>
       <c r="R95" t="n">
-        <v>6783695</v>
+        <v>6783470</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10277,7 +10281,6 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10296,42 +10299,39 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126243415</v>
+        <v>126244082</v>
       </c>
       <c r="B96" t="n">
-        <v>57654</v>
+        <v>5176</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10339,10 +10339,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>438722</v>
+        <v>438809</v>
       </c>
       <c r="R96" t="n">
-        <v>6783470</v>
+        <v>6783806</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10383,6 +10383,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10401,10 +10402,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126244082</v>
+        <v>126244320</v>
       </c>
       <c r="B97" t="n">
-        <v>5176</v>
+        <v>98279</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10412,28 +10413,27 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100526</v>
+        <v>223591</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -10441,10 +10441,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>438809</v>
+        <v>438606</v>
       </c>
       <c r="R97" t="n">
-        <v>6783806</v>
+        <v>6783759</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10471,12 +10471,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10706,10 +10706,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>126461102</v>
+        <v>126461226</v>
       </c>
       <c r="B100" t="n">
-        <v>79569</v>
+        <v>78980</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10717,21 +10717,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10744,10 +10744,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>438336</v>
+        <v>438392</v>
       </c>
       <c r="R100" t="n">
-        <v>6783605</v>
+        <v>6783641</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10807,10 +10807,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>126461226</v>
+        <v>126461102</v>
       </c>
       <c r="B101" t="n">
-        <v>78980</v>
+        <v>79569</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10818,21 +10818,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10845,10 +10845,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>438392</v>
+        <v>438336</v>
       </c>
       <c r="R101" t="n">
-        <v>6783641</v>
+        <v>6783605</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126243254</v>
+        <v>126242965</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,26 +1001,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1028,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438790</v>
+        <v>438888</v>
       </c>
       <c r="R5" t="n">
-        <v>6783520</v>
+        <v>6783584</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1072,7 +1077,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1091,37 +1095,39 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126242851</v>
+        <v>126244085</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>4772</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1129,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438926</v>
+        <v>438809</v>
       </c>
       <c r="R6" t="n">
-        <v>6783631</v>
+        <v>6783806</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1192,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126242965</v>
+        <v>126243254</v>
       </c>
       <c r="B7" t="n">
-        <v>57654</v>
+        <v>78980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1203,31 +1209,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1235,10 +1236,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438888</v>
+        <v>438790</v>
       </c>
       <c r="R7" t="n">
-        <v>6783584</v>
+        <v>6783520</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1279,6 +1280,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1297,7 +1299,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126243055</v>
+        <v>126242851</v>
       </c>
       <c r="B8" t="n">
         <v>78980</v>
@@ -1335,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438823</v>
+        <v>438926</v>
       </c>
       <c r="R8" t="n">
-        <v>6783513</v>
+        <v>6783631</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1398,39 +1400,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126244085</v>
+        <v>126243055</v>
       </c>
       <c r="B9" t="n">
-        <v>4772</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1438,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438809</v>
+        <v>438823</v>
       </c>
       <c r="R9" t="n">
-        <v>6783806</v>
+        <v>6783513</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1806,38 +1806,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126243784</v>
+        <v>126243682</v>
       </c>
       <c r="B13" t="n">
-        <v>98382</v>
+        <v>88654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1845,10 +1844,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438893</v>
+        <v>438813</v>
       </c>
       <c r="R13" t="n">
-        <v>6783787</v>
+        <v>6783722</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1908,10 +1907,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126243682</v>
+        <v>126243933</v>
       </c>
       <c r="B14" t="n">
-        <v>88654</v>
+        <v>82792</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1919,21 +1918,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1946,10 +1945,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>438813</v>
+        <v>438928</v>
       </c>
       <c r="R14" t="n">
-        <v>6783722</v>
+        <v>6783763</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2009,10 +2008,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126243933</v>
+        <v>126243724</v>
       </c>
       <c r="B15" t="n">
-        <v>82792</v>
+        <v>91866</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2020,21 +2019,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>5454</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2047,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>438928</v>
+        <v>438883</v>
       </c>
       <c r="R15" t="n">
-        <v>6783763</v>
+        <v>6783662</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2110,37 +2109,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126243724</v>
+        <v>126243784</v>
       </c>
       <c r="B16" t="n">
-        <v>91866</v>
+        <v>98382</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5454</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>438883</v>
+        <v>438893</v>
       </c>
       <c r="R16" t="n">
-        <v>6783662</v>
+        <v>6783787</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2211,10 +2211,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126244296</v>
+        <v>126243527</v>
       </c>
       <c r="B17" t="n">
-        <v>82792</v>
+        <v>91259</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2222,21 +2222,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438723</v>
+        <v>438826</v>
       </c>
       <c r="R17" t="n">
-        <v>6783752</v>
+        <v>6783693</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2279,12 +2279,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2413,32 +2413,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126243527</v>
+        <v>126243075</v>
       </c>
       <c r="B19" t="n">
-        <v>91259</v>
+        <v>79066</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>6450</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438826</v>
+        <v>438799</v>
       </c>
       <c r="R19" t="n">
-        <v>6783693</v>
+        <v>6783496</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2514,10 +2514,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126243709</v>
+        <v>126242913</v>
       </c>
       <c r="B20" t="n">
-        <v>82792</v>
+        <v>78980</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2525,21 +2525,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438875</v>
+        <v>438938</v>
       </c>
       <c r="R20" t="n">
-        <v>6783718</v>
+        <v>6783637</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126244007</v>
+        <v>126243757</v>
       </c>
       <c r="B21" t="n">
-        <v>82792</v>
+        <v>79059</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438925</v>
+        <v>438889</v>
       </c>
       <c r="R21" t="n">
-        <v>6783804</v>
+        <v>6783762</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2716,10 +2716,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126243757</v>
+        <v>126244296</v>
       </c>
       <c r="B22" t="n">
-        <v>79059</v>
+        <v>82792</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2727,21 +2727,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438889</v>
+        <v>438723</v>
       </c>
       <c r="R22" t="n">
-        <v>6783762</v>
+        <v>6783752</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2784,12 +2784,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126242913</v>
+        <v>126244007</v>
       </c>
       <c r="B23" t="n">
-        <v>78980</v>
+        <v>82792</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2828,21 +2828,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>438938</v>
+        <v>438925</v>
       </c>
       <c r="R23" t="n">
-        <v>6783637</v>
+        <v>6783804</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2918,32 +2918,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126243075</v>
+        <v>126243709</v>
       </c>
       <c r="B24" t="n">
-        <v>79066</v>
+        <v>82792</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>438799</v>
+        <v>438875</v>
       </c>
       <c r="R24" t="n">
-        <v>6783496</v>
+        <v>6783718</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126243565</v>
+        <v>126243348</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>79012</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3131,21 +3131,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>438805</v>
+        <v>438767</v>
       </c>
       <c r="R26" t="n">
-        <v>6783685</v>
+        <v>6783455</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3221,10 +3221,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126243742</v>
+        <v>126243738</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>79012</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3232,21 +3232,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3322,10 +3322,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126243348</v>
+        <v>126244253</v>
       </c>
       <c r="B28" t="n">
-        <v>79012</v>
+        <v>82792</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3333,21 +3333,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438767</v>
+        <v>438791</v>
       </c>
       <c r="R28" t="n">
-        <v>6783455</v>
+        <v>6783795</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3423,10 +3423,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126243738</v>
+        <v>126243342</v>
       </c>
       <c r="B29" t="n">
-        <v>79012</v>
+        <v>82792</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3434,21 +3434,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3461,10 +3461,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>438885</v>
+        <v>438767</v>
       </c>
       <c r="R29" t="n">
-        <v>6783710</v>
+        <v>6783455</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3524,10 +3524,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126243342</v>
+        <v>126243565</v>
       </c>
       <c r="B30" t="n">
-        <v>82792</v>
+        <v>78980</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3535,21 +3535,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3562,10 +3562,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438767</v>
+        <v>438805</v>
       </c>
       <c r="R30" t="n">
-        <v>6783455</v>
+        <v>6783685</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3625,10 +3625,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126244253</v>
+        <v>126243148</v>
       </c>
       <c r="B31" t="n">
-        <v>82792</v>
+        <v>78980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3636,21 +3636,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438791</v>
+        <v>438785</v>
       </c>
       <c r="R31" t="n">
-        <v>6783795</v>
+        <v>6783487</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3726,7 +3726,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126243148</v>
+        <v>126243742</v>
       </c>
       <c r="B32" t="n">
         <v>78980</v>
@@ -3764,10 +3764,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438785</v>
+        <v>438885</v>
       </c>
       <c r="R32" t="n">
-        <v>6783487</v>
+        <v>6783710</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3929,32 +3929,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126244571</v>
+        <v>126243379</v>
       </c>
       <c r="B34" t="n">
-        <v>82792</v>
+        <v>79066</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>6450</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>438751</v>
+        <v>438694</v>
       </c>
       <c r="R34" t="n">
-        <v>6783884</v>
+        <v>6783458</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4030,37 +4030,38 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126244328</v>
+        <v>126244106</v>
       </c>
       <c r="B35" t="n">
-        <v>82792</v>
+        <v>98382</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4068,10 +4069,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>438584</v>
+        <v>438782</v>
       </c>
       <c r="R35" t="n">
-        <v>6783774</v>
+        <v>6783777</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4098,12 +4099,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4131,32 +4132,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126243379</v>
+        <v>126244571</v>
       </c>
       <c r="B36" t="n">
-        <v>79066</v>
+        <v>82792</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4169,10 +4170,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>438694</v>
+        <v>438751</v>
       </c>
       <c r="R36" t="n">
-        <v>6783458</v>
+        <v>6783884</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4199,12 +4200,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4232,38 +4233,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126244106</v>
+        <v>126244328</v>
       </c>
       <c r="B37" t="n">
-        <v>98382</v>
+        <v>82792</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>438782</v>
+        <v>438584</v>
       </c>
       <c r="R37" t="n">
-        <v>6783777</v>
+        <v>6783774</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4301,12 +4301,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4334,32 +4334,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126243450</v>
+        <v>126242981</v>
       </c>
       <c r="B38" t="n">
-        <v>91210</v>
+        <v>78980</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>438740</v>
+        <v>438894</v>
       </c>
       <c r="R38" t="n">
-        <v>6783462</v>
+        <v>6783561</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4435,7 +4435,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126243521</v>
+        <v>126243450</v>
       </c>
       <c r="B39" t="n">
         <v>91210</v>
@@ -4473,10 +4473,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>438845</v>
+        <v>438740</v>
       </c>
       <c r="R39" t="n">
-        <v>6783696</v>
+        <v>6783462</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4536,32 +4536,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126242981</v>
+        <v>126243521</v>
       </c>
       <c r="B40" t="n">
-        <v>78980</v>
+        <v>91210</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4574,10 +4574,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>438894</v>
+        <v>438845</v>
       </c>
       <c r="R40" t="n">
-        <v>6783561</v>
+        <v>6783696</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5049,10 +5049,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126244033</v>
+        <v>126243519</v>
       </c>
       <c r="B45" t="n">
-        <v>82792</v>
+        <v>57817</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5060,26 +5060,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5087,10 +5100,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>438911</v>
+        <v>438845</v>
       </c>
       <c r="R45" t="n">
-        <v>6783847</v>
+        <v>6783696</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5131,7 +5144,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5150,10 +5162,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126243519</v>
+        <v>126244033</v>
       </c>
       <c r="B46" t="n">
-        <v>57817</v>
+        <v>82792</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5161,39 +5173,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5201,10 +5200,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>438845</v>
+        <v>438911</v>
       </c>
       <c r="R46" t="n">
-        <v>6783696</v>
+        <v>6783847</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5245,6 +5244,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5465,10 +5465,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126244099</v>
+        <v>126243370</v>
       </c>
       <c r="B49" t="n">
-        <v>82792</v>
+        <v>79598</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5476,21 +5476,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>438804</v>
+        <v>438714</v>
       </c>
       <c r="R49" t="n">
-        <v>6783800</v>
+        <v>6783492</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5566,10 +5566,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126243370</v>
+        <v>126244099</v>
       </c>
       <c r="B50" t="n">
-        <v>79598</v>
+        <v>82792</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5577,21 +5577,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>438714</v>
+        <v>438804</v>
       </c>
       <c r="R50" t="n">
-        <v>6783492</v>
+        <v>6783800</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5768,10 +5768,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126244009</v>
+        <v>126243499</v>
       </c>
       <c r="B52" t="n">
-        <v>78980</v>
+        <v>82792</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5779,21 +5779,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5806,10 +5806,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>438925</v>
+        <v>438858</v>
       </c>
       <c r="R52" t="n">
-        <v>6783804</v>
+        <v>6783695</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5869,7 +5869,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126243332</v>
+        <v>126244009</v>
       </c>
       <c r="B53" t="n">
         <v>78980</v>
@@ -5907,10 +5907,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>438770</v>
+        <v>438925</v>
       </c>
       <c r="R53" t="n">
-        <v>6783484</v>
+        <v>6783804</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5970,7 +5970,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126243713</v>
+        <v>126243332</v>
       </c>
       <c r="B54" t="n">
         <v>78980</v>
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>438875</v>
+        <v>438770</v>
       </c>
       <c r="R54" t="n">
-        <v>6783718</v>
+        <v>6783484</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6071,10 +6071,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126242940</v>
+        <v>126243713</v>
       </c>
       <c r="B55" t="n">
-        <v>57654</v>
+        <v>78980</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6082,31 +6082,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6114,10 +6109,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>438898</v>
+        <v>438875</v>
       </c>
       <c r="R55" t="n">
-        <v>6783622</v>
+        <v>6783718</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6158,6 +6153,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6176,10 +6172,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126243499</v>
+        <v>126242940</v>
       </c>
       <c r="B56" t="n">
-        <v>82792</v>
+        <v>57654</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6187,26 +6183,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6214,10 +6215,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>438858</v>
+        <v>438898</v>
       </c>
       <c r="R56" t="n">
-        <v>6783695</v>
+        <v>6783622</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6258,7 +6259,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6378,10 +6378,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126243823</v>
+        <v>126243980</v>
       </c>
       <c r="B58" t="n">
-        <v>82792</v>
+        <v>78980</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6389,21 +6389,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6416,10 +6416,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>438911</v>
+        <v>438928</v>
       </c>
       <c r="R58" t="n">
-        <v>6783821</v>
+        <v>6783763</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6479,10 +6479,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126243986</v>
+        <v>126244052</v>
       </c>
       <c r="B59" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6490,21 +6490,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6517,10 +6517,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>438947</v>
+        <v>438821</v>
       </c>
       <c r="R59" t="n">
-        <v>6783782</v>
+        <v>6783854</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6580,7 +6580,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126243980</v>
+        <v>126243462</v>
       </c>
       <c r="B60" t="n">
         <v>78980</v>
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>438928</v>
+        <v>438777</v>
       </c>
       <c r="R60" t="n">
-        <v>6783763</v>
+        <v>6783527</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6681,7 +6681,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126243462</v>
+        <v>126243351</v>
       </c>
       <c r="B61" t="n">
         <v>78980</v>
@@ -6719,10 +6719,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>438777</v>
+        <v>438767</v>
       </c>
       <c r="R61" t="n">
-        <v>6783527</v>
+        <v>6783455</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6782,7 +6782,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126243351</v>
+        <v>126243986</v>
       </c>
       <c r="B62" t="n">
         <v>78980</v>
@@ -6820,10 +6820,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>438767</v>
+        <v>438947</v>
       </c>
       <c r="R62" t="n">
-        <v>6783455</v>
+        <v>6783782</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6883,37 +6883,46 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126244052</v>
+        <v>126243492</v>
       </c>
       <c r="B63" t="n">
-        <v>79598</v>
+        <v>56849</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6921,10 +6930,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>438821</v>
+        <v>438871</v>
       </c>
       <c r="R63" t="n">
-        <v>6783854</v>
+        <v>6783612</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6959,13 +6968,17 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Den tog ett s.k sandbad i sandblottan efter en rofyllda.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6984,46 +6997,37 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126243492</v>
+        <v>126243823</v>
       </c>
       <c r="B64" t="n">
-        <v>56849</v>
+        <v>82792</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7031,10 +7035,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>438871</v>
+        <v>438911</v>
       </c>
       <c r="R64" t="n">
-        <v>6783612</v>
+        <v>6783821</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7069,17 +7073,13 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Den tog ett s.k sandbad i sandblottan efter en rofyllda.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7306,10 +7306,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126244312</v>
+        <v>126242918</v>
       </c>
       <c r="B67" t="n">
-        <v>56840</v>
+        <v>79012</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7317,43 +7317,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102612</v>
+        <v>185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7361,10 +7344,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>438654</v>
+        <v>438917</v>
       </c>
       <c r="R67" t="n">
-        <v>6783741</v>
+        <v>6783626</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7391,12 +7374,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7405,6 +7388,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7423,10 +7407,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126244077</v>
+        <v>126243259</v>
       </c>
       <c r="B68" t="n">
-        <v>98382</v>
+        <v>91210</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7434,27 +7418,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7462,10 +7445,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>438852</v>
+        <v>438790</v>
       </c>
       <c r="R68" t="n">
-        <v>6783837</v>
+        <v>6783520</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7525,37 +7508,42 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126243259</v>
+        <v>126242798</v>
       </c>
       <c r="B69" t="n">
-        <v>91210</v>
+        <v>57654</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7563,10 +7551,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>438790</v>
+        <v>438938</v>
       </c>
       <c r="R69" t="n">
-        <v>6783520</v>
+        <v>6783650</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7601,13 +7589,17 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Mycket hackspår i den ca 160 åriga naturskogen</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7626,10 +7618,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126242918</v>
+        <v>126244312</v>
       </c>
       <c r="B70" t="n">
-        <v>79012</v>
+        <v>56840</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7637,26 +7629,43 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>185</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7664,10 +7673,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>438917</v>
+        <v>438654</v>
       </c>
       <c r="R70" t="n">
-        <v>6783626</v>
+        <v>6783741</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7694,12 +7703,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7708,7 +7717,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7727,42 +7735,38 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126242798</v>
+        <v>126244077</v>
       </c>
       <c r="B71" t="n">
-        <v>57654</v>
+        <v>98382</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>221952</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7770,10 +7774,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>438938</v>
+        <v>438852</v>
       </c>
       <c r="R71" t="n">
-        <v>6783650</v>
+        <v>6783837</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7808,17 +7812,13 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Mycket hackspår i den ca 160 åriga naturskogen</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7837,32 +7837,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126243459</v>
+        <v>126243314</v>
       </c>
       <c r="B72" t="n">
-        <v>79012</v>
+        <v>91832</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>185</v>
+        <v>1179</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>438777</v>
+        <v>438816</v>
       </c>
       <c r="R72" t="n">
-        <v>6783527</v>
+        <v>6783530</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7938,38 +7938,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126244337</v>
+        <v>126243042</v>
       </c>
       <c r="B73" t="n">
-        <v>98279</v>
+        <v>79059</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>223591</v>
+        <v>864</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -7977,10 +7976,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>438574</v>
+        <v>438848</v>
       </c>
       <c r="R73" t="n">
-        <v>6783811</v>
+        <v>6783520</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8007,12 +8006,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8040,32 +8039,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126243314</v>
+        <v>126244274</v>
       </c>
       <c r="B74" t="n">
-        <v>91832</v>
+        <v>82792</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1179</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8078,10 +8077,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>438816</v>
+        <v>438776</v>
       </c>
       <c r="R74" t="n">
-        <v>6783530</v>
+        <v>6783788</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8141,10 +8140,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126243042</v>
+        <v>126243459</v>
       </c>
       <c r="B75" t="n">
-        <v>79059</v>
+        <v>79012</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8152,21 +8151,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8179,10 +8178,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>438848</v>
+        <v>438777</v>
       </c>
       <c r="R75" t="n">
-        <v>6783520</v>
+        <v>6783527</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8242,37 +8241,38 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126244274</v>
+        <v>126244337</v>
       </c>
       <c r="B76" t="n">
-        <v>82792</v>
+        <v>98279</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1312</v>
+        <v>223591</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>438776</v>
+        <v>438574</v>
       </c>
       <c r="R76" t="n">
-        <v>6783788</v>
+        <v>6783811</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8310,12 +8310,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8646,7 +8646,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126243586</v>
+        <v>126243208</v>
       </c>
       <c r="B80" t="n">
         <v>57654</v>
@@ -8689,10 +8689,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>438805</v>
+        <v>438777</v>
       </c>
       <c r="R80" t="n">
-        <v>6783685</v>
+        <v>6783503</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8751,7 +8751,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126243208</v>
+        <v>126243586</v>
       </c>
       <c r="B81" t="n">
         <v>57654</v>
@@ -8794,10 +8794,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>438777</v>
+        <v>438805</v>
       </c>
       <c r="R81" t="n">
-        <v>6783503</v>
+        <v>6783685</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8958,32 +8958,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126243220</v>
+        <v>126243608</v>
       </c>
       <c r="B83" t="n">
-        <v>91210</v>
+        <v>91603</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8996,10 +8996,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>438775</v>
+        <v>438797</v>
       </c>
       <c r="R83" t="n">
-        <v>6783504</v>
+        <v>6783670</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9059,27 +9059,27 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126243452</v>
+        <v>126243505</v>
       </c>
       <c r="B84" t="n">
-        <v>78980</v>
+        <v>80118</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9097,10 +9097,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>438740</v>
+        <v>438858</v>
       </c>
       <c r="R84" t="n">
-        <v>6783462</v>
+        <v>6783695</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9160,27 +9160,27 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126243505</v>
+        <v>126243452</v>
       </c>
       <c r="B85" t="n">
-        <v>80118</v>
+        <v>78980</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9198,10 +9198,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>438858</v>
+        <v>438740</v>
       </c>
       <c r="R85" t="n">
-        <v>6783695</v>
+        <v>6783462</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9362,32 +9362,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126243608</v>
+        <v>126243220</v>
       </c>
       <c r="B87" t="n">
-        <v>91603</v>
+        <v>91210</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9400,10 +9400,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>438797</v>
+        <v>438775</v>
       </c>
       <c r="R87" t="n">
-        <v>6783670</v>
+        <v>6783504</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9674,10 +9674,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126243143</v>
+        <v>126249487</v>
       </c>
       <c r="B90" t="n">
-        <v>56849</v>
+        <v>98382</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9685,45 +9685,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Hålberg-Räklitt, Dlr</t>
+          <t>Räklitt, Hållberg, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>438785</v>
+        <v>438890</v>
       </c>
       <c r="R90" t="n">
-        <v>6783487</v>
+        <v>6783610</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9747,17 +9739,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>21:07</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>En hona och 5 kycklingar</t>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>21:07</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9772,22 +9769,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126249487</v>
+        <v>126243143</v>
       </c>
       <c r="B91" t="n">
-        <v>98382</v>
+        <v>56849</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9795,37 +9792,45 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Räklitt, Hållberg, Dlr</t>
+          <t>Hålberg-Räklitt, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>438890</v>
+        <v>438785</v>
       </c>
       <c r="R91" t="n">
-        <v>6783610</v>
+        <v>6783487</v>
       </c>
       <c r="S91" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9849,22 +9854,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>21:07</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>21:07</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>En hona och 5 kycklingar</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9879,12 +9879,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10093,37 +10093,39 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126243503</v>
+        <v>126244082</v>
       </c>
       <c r="B94" t="n">
-        <v>78980</v>
+        <v>5176</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10131,10 +10133,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>438858</v>
+        <v>438809</v>
       </c>
       <c r="R94" t="n">
-        <v>6783695</v>
+        <v>6783806</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10194,10 +10196,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126243415</v>
+        <v>126243503</v>
       </c>
       <c r="B95" t="n">
-        <v>57654</v>
+        <v>78980</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10205,31 +10207,26 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -10237,10 +10234,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>438722</v>
+        <v>438858</v>
       </c>
       <c r="R95" t="n">
-        <v>6783470</v>
+        <v>6783695</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10281,6 +10278,7 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -10299,39 +10297,42 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126244082</v>
+        <v>126243415</v>
       </c>
       <c r="B96" t="n">
-        <v>5176</v>
+        <v>57654</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10339,10 +10340,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>438809</v>
+        <v>438722</v>
       </c>
       <c r="R96" t="n">
-        <v>6783806</v>
+        <v>6783470</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10383,7 +10384,6 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10402,38 +10402,37 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126244320</v>
+        <v>126243395</v>
       </c>
       <c r="B97" t="n">
-        <v>98279</v>
+        <v>79569</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>223591</v>
+        <v>229821</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -10441,10 +10440,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>438606</v>
+        <v>438682</v>
       </c>
       <c r="R97" t="n">
-        <v>6783759</v>
+        <v>6783454</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10471,12 +10470,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10504,37 +10503,38 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126243395</v>
+        <v>126244320</v>
       </c>
       <c r="B98" t="n">
-        <v>79569</v>
+        <v>98279</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>223591</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -10542,10 +10542,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>438682</v>
+        <v>438606</v>
       </c>
       <c r="R98" t="n">
-        <v>6783454</v>
+        <v>6783759</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10572,12 +10572,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11652,38 +11652,37 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126461224</v>
+        <v>126461150</v>
       </c>
       <c r="B109" t="n">
-        <v>98382</v>
+        <v>79598</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -11691,10 +11690,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>438380</v>
+        <v>438351</v>
       </c>
       <c r="R109" t="n">
-        <v>6783647</v>
+        <v>6783622</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11754,37 +11753,38 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126461150</v>
+        <v>126461224</v>
       </c>
       <c r="B110" t="n">
-        <v>79598</v>
+        <v>98382</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -11792,10 +11792,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>438351</v>
+        <v>438380</v>
       </c>
       <c r="R110" t="n">
-        <v>6783622</v>
+        <v>6783647</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12978,7 +12978,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>126461025</v>
+        <v>126461068</v>
       </c>
       <c r="B122" t="n">
         <v>78738</v>
@@ -13016,10 +13016,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>438292</v>
+        <v>438313</v>
       </c>
       <c r="R122" t="n">
-        <v>6783621</v>
+        <v>6783667</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -13079,7 +13079,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126461068</v>
+        <v>126461025</v>
       </c>
       <c r="B123" t="n">
         <v>78738</v>
@@ -13117,10 +13117,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>438313</v>
+        <v>438292</v>
       </c>
       <c r="R123" t="n">
-        <v>6783667</v>
+        <v>6783621</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -3120,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126243348</v>
+        <v>126243565</v>
       </c>
       <c r="B26" t="n">
-        <v>79012</v>
+        <v>78980</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3131,21 +3131,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>438767</v>
+        <v>438805</v>
       </c>
       <c r="R26" t="n">
-        <v>6783455</v>
+        <v>6783685</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3221,10 +3221,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126243738</v>
+        <v>126243148</v>
       </c>
       <c r="B27" t="n">
-        <v>79012</v>
+        <v>78980</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3232,21 +3232,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438885</v>
+        <v>438785</v>
       </c>
       <c r="R27" t="n">
-        <v>6783710</v>
+        <v>6783487</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3322,10 +3322,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126244253</v>
+        <v>126243742</v>
       </c>
       <c r="B28" t="n">
-        <v>82792</v>
+        <v>78980</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3333,21 +3333,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438791</v>
+        <v>438885</v>
       </c>
       <c r="R28" t="n">
-        <v>6783795</v>
+        <v>6783710</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3423,10 +3423,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126243342</v>
+        <v>126243348</v>
       </c>
       <c r="B29" t="n">
-        <v>82792</v>
+        <v>79012</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3434,21 +3434,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3524,10 +3524,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126243565</v>
+        <v>126243738</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>79012</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3535,21 +3535,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3562,10 +3562,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438805</v>
+        <v>438885</v>
       </c>
       <c r="R30" t="n">
-        <v>6783685</v>
+        <v>6783710</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3625,10 +3625,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126243148</v>
+        <v>126244253</v>
       </c>
       <c r="B31" t="n">
-        <v>78980</v>
+        <v>82792</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3636,21 +3636,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3663,10 +3663,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438785</v>
+        <v>438791</v>
       </c>
       <c r="R31" t="n">
-        <v>6783487</v>
+        <v>6783795</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3726,10 +3726,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126243742</v>
+        <v>126243342</v>
       </c>
       <c r="B32" t="n">
-        <v>78980</v>
+        <v>82792</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3737,21 +3737,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3764,10 +3764,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438885</v>
+        <v>438767</v>
       </c>
       <c r="R32" t="n">
-        <v>6783710</v>
+        <v>6783455</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -5049,10 +5049,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126243519</v>
+        <v>126244033</v>
       </c>
       <c r="B45" t="n">
-        <v>57817</v>
+        <v>82792</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5060,39 +5060,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5100,10 +5087,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>438845</v>
+        <v>438911</v>
       </c>
       <c r="R45" t="n">
-        <v>6783696</v>
+        <v>6783847</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5144,6 +5131,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5162,10 +5150,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126244033</v>
+        <v>126243519</v>
       </c>
       <c r="B46" t="n">
-        <v>82792</v>
+        <v>57817</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5173,26 +5161,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5200,10 +5201,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>438911</v>
+        <v>438845</v>
       </c>
       <c r="R46" t="n">
-        <v>6783847</v>
+        <v>6783696</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5244,7 +5245,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5263,10 +5263,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126243010</v>
+        <v>126244099</v>
       </c>
       <c r="B47" t="n">
-        <v>78980</v>
+        <v>82792</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5274,21 +5274,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>438852</v>
+        <v>438804</v>
       </c>
       <c r="R47" t="n">
-        <v>6783530</v>
+        <v>6783800</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5364,7 +5364,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126243233</v>
+        <v>126243010</v>
       </c>
       <c r="B48" t="n">
         <v>78980</v>
@@ -5402,10 +5402,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>438775</v>
+        <v>438852</v>
       </c>
       <c r="R48" t="n">
-        <v>6783504</v>
+        <v>6783530</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5465,10 +5465,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126243370</v>
+        <v>126243233</v>
       </c>
       <c r="B49" t="n">
-        <v>79598</v>
+        <v>78980</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5476,21 +5476,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>438714</v>
+        <v>438775</v>
       </c>
       <c r="R49" t="n">
-        <v>6783492</v>
+        <v>6783504</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5566,10 +5566,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126244099</v>
+        <v>126243370</v>
       </c>
       <c r="B50" t="n">
-        <v>82792</v>
+        <v>79598</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5577,21 +5577,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>438804</v>
+        <v>438714</v>
       </c>
       <c r="R50" t="n">
-        <v>6783800</v>
+        <v>6783492</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -8856,10 +8856,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126243816</v>
+        <v>126243220</v>
       </c>
       <c r="B82" t="n">
-        <v>98279</v>
+        <v>91210</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8867,27 +8867,26 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>223591</v>
+        <v>5447</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -8895,10 +8894,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>438886</v>
+        <v>438775</v>
       </c>
       <c r="R82" t="n">
-        <v>6783805</v>
+        <v>6783504</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8958,32 +8957,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126243608</v>
+        <v>126243505</v>
       </c>
       <c r="B83" t="n">
-        <v>91603</v>
+        <v>80118</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2062</v>
+        <v>6463</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8996,10 +8995,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>438797</v>
+        <v>438858</v>
       </c>
       <c r="R83" t="n">
-        <v>6783670</v>
+        <v>6783695</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9059,27 +9058,27 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126243505</v>
+        <v>126243452</v>
       </c>
       <c r="B84" t="n">
-        <v>80118</v>
+        <v>78980</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9097,10 +9096,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>438858</v>
+        <v>438740</v>
       </c>
       <c r="R84" t="n">
-        <v>6783695</v>
+        <v>6783462</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9160,32 +9159,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126243452</v>
+        <v>126243191</v>
       </c>
       <c r="B85" t="n">
-        <v>78980</v>
+        <v>79066</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9198,10 +9197,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>438740</v>
+        <v>438777</v>
       </c>
       <c r="R85" t="n">
-        <v>6783462</v>
+        <v>6783503</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9261,37 +9260,42 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126243191</v>
+        <v>126243732</v>
       </c>
       <c r="B86" t="n">
-        <v>79066</v>
+        <v>57654</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6450</v>
+        <v>100049</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9299,10 +9303,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>438777</v>
+        <v>438882</v>
       </c>
       <c r="R86" t="n">
-        <v>6783503</v>
+        <v>6783685</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9343,7 +9347,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9362,32 +9365,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126243220</v>
+        <v>126243608</v>
       </c>
       <c r="B87" t="n">
-        <v>91210</v>
+        <v>91603</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5447</v>
+        <v>2062</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9400,10 +9403,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>438775</v>
+        <v>438797</v>
       </c>
       <c r="R87" t="n">
-        <v>6783504</v>
+        <v>6783670</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9463,42 +9466,42 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126243732</v>
+        <v>126243676</v>
       </c>
       <c r="B88" t="n">
-        <v>57654</v>
+        <v>98382</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>221952</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -9506,10 +9509,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>438882</v>
+        <v>438813</v>
       </c>
       <c r="R88" t="n">
-        <v>6783685</v>
+        <v>6783722</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9550,6 +9553,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9568,10 +9572,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126243676</v>
+        <v>126243816</v>
       </c>
       <c r="B89" t="n">
-        <v>98382</v>
+        <v>98279</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9579,28 +9583,24 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221952</v>
+        <v>223591</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
@@ -9611,10 +9611,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>438813</v>
+        <v>438886</v>
       </c>
       <c r="R89" t="n">
-        <v>6783722</v>
+        <v>6783805</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9891,37 +9891,38 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126243973</v>
+        <v>126244320</v>
       </c>
       <c r="B92" t="n">
-        <v>88654</v>
+        <v>98279</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>510</v>
+        <v>223591</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -9929,10 +9930,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>438928</v>
+        <v>438606</v>
       </c>
       <c r="R92" t="n">
-        <v>6783763</v>
+        <v>6783759</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -9959,12 +9960,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9992,10 +9993,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126243447</v>
+        <v>126243503</v>
       </c>
       <c r="B93" t="n">
-        <v>82792</v>
+        <v>78980</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10003,21 +10004,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10030,10 +10031,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>438740</v>
+        <v>438858</v>
       </c>
       <c r="R93" t="n">
-        <v>6783462</v>
+        <v>6783695</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10093,39 +10094,37 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126244082</v>
+        <v>126243973</v>
       </c>
       <c r="B94" t="n">
-        <v>5176</v>
+        <v>88654</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100526</v>
+        <v>510</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -10133,10 +10132,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>438809</v>
+        <v>438928</v>
       </c>
       <c r="R94" t="n">
-        <v>6783806</v>
+        <v>6783763</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10196,10 +10195,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126243503</v>
+        <v>126243447</v>
       </c>
       <c r="B95" t="n">
-        <v>78980</v>
+        <v>82792</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10207,21 +10206,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10234,10 +10233,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>438858</v>
+        <v>438740</v>
       </c>
       <c r="R95" t="n">
-        <v>6783695</v>
+        <v>6783462</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10402,37 +10401,39 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126243395</v>
+        <v>126244082</v>
       </c>
       <c r="B97" t="n">
-        <v>79569</v>
+        <v>5176</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>229821</v>
+        <v>100526</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -10440,10 +10441,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>438682</v>
+        <v>438809</v>
       </c>
       <c r="R97" t="n">
-        <v>6783454</v>
+        <v>6783806</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10503,38 +10504,37 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126244320</v>
+        <v>126243395</v>
       </c>
       <c r="B98" t="n">
-        <v>98279</v>
+        <v>79569</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>223591</v>
+        <v>229821</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -10542,10 +10542,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>438606</v>
+        <v>438682</v>
       </c>
       <c r="R98" t="n">
-        <v>6783759</v>
+        <v>6783454</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10572,12 +10572,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11652,37 +11652,38 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126461150</v>
+        <v>126461224</v>
       </c>
       <c r="B109" t="n">
-        <v>79598</v>
+        <v>98382</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -11690,10 +11691,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>438351</v>
+        <v>438380</v>
       </c>
       <c r="R109" t="n">
-        <v>6783622</v>
+        <v>6783647</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11753,38 +11754,37 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126461224</v>
+        <v>126461150</v>
       </c>
       <c r="B110" t="n">
-        <v>98382</v>
+        <v>79598</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -11792,10 +11792,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>438380</v>
+        <v>438351</v>
       </c>
       <c r="R110" t="n">
-        <v>6783647</v>
+        <v>6783622</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12362,39 +12362,37 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126461132</v>
+        <v>126461124</v>
       </c>
       <c r="B116" t="n">
-        <v>5176</v>
+        <v>82792</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100526</v>
+        <v>1312</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12465,37 +12463,39 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126461124</v>
+        <v>126461132</v>
       </c>
       <c r="B117" t="n">
-        <v>82792</v>
+        <v>5176</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1312</v>
+        <v>100526</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -4739,35 +4739,39 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126244589</v>
+        <v>126243702</v>
       </c>
       <c r="B42" t="n">
-        <v>98382</v>
+        <v>98361</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -4778,10 +4782,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>438824</v>
+        <v>438786</v>
       </c>
       <c r="R42" t="n">
-        <v>6783885</v>
+        <v>6783704</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4808,12 +4812,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4841,7 +4845,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126243995</v>
+        <v>126244589</v>
       </c>
       <c r="B43" t="n">
         <v>98382</v>
@@ -4880,10 +4884,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>438953</v>
+        <v>438824</v>
       </c>
       <c r="R43" t="n">
-        <v>6783788</v>
+        <v>6783885</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4910,12 +4914,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4943,39 +4947,35 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126243702</v>
+        <v>126243995</v>
       </c>
       <c r="B44" t="n">
-        <v>98361</v>
+        <v>98382</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>438786</v>
+        <v>438953</v>
       </c>
       <c r="R44" t="n">
-        <v>6783704</v>
+        <v>6783788</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5049,10 +5049,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126244033</v>
+        <v>126243519</v>
       </c>
       <c r="B45" t="n">
-        <v>82792</v>
+        <v>57817</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5060,26 +5060,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5087,10 +5100,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>438911</v>
+        <v>438845</v>
       </c>
       <c r="R45" t="n">
-        <v>6783847</v>
+        <v>6783696</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5131,7 +5144,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5150,10 +5162,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126243519</v>
+        <v>126244033</v>
       </c>
       <c r="B46" t="n">
-        <v>57817</v>
+        <v>82792</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5161,39 +5173,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5201,10 +5200,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>438845</v>
+        <v>438911</v>
       </c>
       <c r="R46" t="n">
-        <v>6783696</v>
+        <v>6783847</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5245,6 +5244,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -7837,32 +7837,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126243314</v>
+        <v>126243459</v>
       </c>
       <c r="B72" t="n">
-        <v>91832</v>
+        <v>79012</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1179</v>
+        <v>185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>438816</v>
+        <v>438777</v>
       </c>
       <c r="R72" t="n">
-        <v>6783530</v>
+        <v>6783527</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7938,37 +7938,38 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126243042</v>
+        <v>126244337</v>
       </c>
       <c r="B73" t="n">
-        <v>79059</v>
+        <v>98279</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>864</v>
+        <v>223591</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -7976,10 +7977,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>438848</v>
+        <v>438574</v>
       </c>
       <c r="R73" t="n">
-        <v>6783520</v>
+        <v>6783811</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8006,12 +8007,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8039,32 +8040,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126244274</v>
+        <v>126243314</v>
       </c>
       <c r="B74" t="n">
-        <v>82792</v>
+        <v>91832</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>1179</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8077,10 +8078,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>438776</v>
+        <v>438816</v>
       </c>
       <c r="R74" t="n">
-        <v>6783788</v>
+        <v>6783530</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8140,10 +8141,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126243459</v>
+        <v>126243042</v>
       </c>
       <c r="B75" t="n">
-        <v>79012</v>
+        <v>79059</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8151,21 +8152,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8178,10 +8179,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>438777</v>
+        <v>438848</v>
       </c>
       <c r="R75" t="n">
-        <v>6783527</v>
+        <v>6783520</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8241,38 +8242,37 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126244337</v>
+        <v>126244274</v>
       </c>
       <c r="B76" t="n">
-        <v>98279</v>
+        <v>82792</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>223591</v>
+        <v>1312</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>438574</v>
+        <v>438776</v>
       </c>
       <c r="R76" t="n">
-        <v>6783811</v>
+        <v>6783788</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8310,12 +8310,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -11652,38 +11652,37 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126461224</v>
+        <v>126461150</v>
       </c>
       <c r="B109" t="n">
-        <v>98382</v>
+        <v>79598</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
@@ -11691,10 +11690,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>438380</v>
+        <v>438351</v>
       </c>
       <c r="R109" t="n">
-        <v>6783647</v>
+        <v>6783622</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11754,37 +11753,38 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>126461150</v>
+        <v>126461224</v>
       </c>
       <c r="B110" t="n">
-        <v>79598</v>
+        <v>98382</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
@@ -11792,10 +11792,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>438351</v>
+        <v>438380</v>
       </c>
       <c r="R110" t="n">
-        <v>6783622</v>
+        <v>6783647</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -12362,37 +12362,39 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>126461124</v>
+        <v>126461132</v>
       </c>
       <c r="B116" t="n">
-        <v>82792</v>
+        <v>5176</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1312</v>
+        <v>100526</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -12463,39 +12465,37 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>126461132</v>
+        <v>126461124</v>
       </c>
       <c r="B117" t="n">
-        <v>5176</v>
+        <v>82792</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100526</v>
+        <v>1312</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -2211,10 +2211,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126243527</v>
+        <v>126243757</v>
       </c>
       <c r="B17" t="n">
-        <v>91259</v>
+        <v>79059</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2222,21 +2222,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2249,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>438826</v>
+        <v>438889</v>
       </c>
       <c r="R17" t="n">
-        <v>6783693</v>
+        <v>6783762</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2312,7 +2312,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126244055</v>
+        <v>126244296</v>
       </c>
       <c r="B18" t="n">
         <v>82792</v>
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>438833</v>
+        <v>438723</v>
       </c>
       <c r="R18" t="n">
-        <v>6783826</v>
+        <v>6783752</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2380,12 +2380,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2413,32 +2413,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126243075</v>
+        <v>126244007</v>
       </c>
       <c r="B19" t="n">
-        <v>79066</v>
+        <v>82792</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>438799</v>
+        <v>438925</v>
       </c>
       <c r="R19" t="n">
-        <v>6783496</v>
+        <v>6783804</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2514,32 +2514,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126242913</v>
+        <v>126243075</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>79066</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6450</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>438938</v>
+        <v>438799</v>
       </c>
       <c r="R20" t="n">
-        <v>6783637</v>
+        <v>6783496</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126243757</v>
+        <v>126242913</v>
       </c>
       <c r="B21" t="n">
-        <v>79059</v>
+        <v>78980</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2626,21 +2626,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>438889</v>
+        <v>438938</v>
       </c>
       <c r="R21" t="n">
-        <v>6783762</v>
+        <v>6783637</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2716,10 +2716,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126244296</v>
+        <v>126243527</v>
       </c>
       <c r="B22" t="n">
-        <v>82792</v>
+        <v>91259</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2727,21 +2727,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>438723</v>
+        <v>438826</v>
       </c>
       <c r="R22" t="n">
-        <v>6783752</v>
+        <v>6783693</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2784,12 +2784,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2817,7 +2817,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126244007</v>
+        <v>126244055</v>
       </c>
       <c r="B23" t="n">
         <v>82792</v>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>438925</v>
+        <v>438833</v>
       </c>
       <c r="R23" t="n">
-        <v>6783804</v>
+        <v>6783826</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126243565</v>
+        <v>126243348</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>79012</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3131,21 +3131,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3158,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>438805</v>
+        <v>438767</v>
       </c>
       <c r="R26" t="n">
-        <v>6783685</v>
+        <v>6783455</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3221,10 +3221,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126243148</v>
+        <v>126243738</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>79012</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3232,21 +3232,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>438785</v>
+        <v>438885</v>
       </c>
       <c r="R27" t="n">
-        <v>6783487</v>
+        <v>6783710</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3322,10 +3322,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126243742</v>
+        <v>126244253</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>82792</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3333,21 +3333,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3360,10 +3360,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>438885</v>
+        <v>438791</v>
       </c>
       <c r="R28" t="n">
-        <v>6783710</v>
+        <v>6783795</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3423,10 +3423,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126243348</v>
+        <v>126243342</v>
       </c>
       <c r="B29" t="n">
-        <v>79012</v>
+        <v>82792</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3434,21 +3434,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3524,37 +3524,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126243738</v>
+        <v>126243647</v>
       </c>
       <c r="B30" t="n">
-        <v>79012</v>
+        <v>97239</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3562,10 +3563,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>438885</v>
+        <v>438790</v>
       </c>
       <c r="R30" t="n">
-        <v>6783710</v>
+        <v>6783649</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3625,10 +3626,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126244253</v>
+        <v>126243565</v>
       </c>
       <c r="B31" t="n">
-        <v>82792</v>
+        <v>78980</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3636,21 +3637,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3663,10 +3664,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>438791</v>
+        <v>438805</v>
       </c>
       <c r="R31" t="n">
-        <v>6783795</v>
+        <v>6783685</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3726,10 +3727,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126243342</v>
+        <v>126243148</v>
       </c>
       <c r="B32" t="n">
-        <v>82792</v>
+        <v>78980</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3737,21 +3738,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3764,10 +3765,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>438767</v>
+        <v>438785</v>
       </c>
       <c r="R32" t="n">
-        <v>6783455</v>
+        <v>6783487</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3827,38 +3828,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126243647</v>
+        <v>126243742</v>
       </c>
       <c r="B33" t="n">
-        <v>97239</v>
+        <v>78980</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3866,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>438790</v>
+        <v>438885</v>
       </c>
       <c r="R33" t="n">
-        <v>6783649</v>
+        <v>6783710</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4030,38 +4030,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126244106</v>
+        <v>126244571</v>
       </c>
       <c r="B35" t="n">
-        <v>98382</v>
+        <v>82792</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>1312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4069,10 +4068,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>438782</v>
+        <v>438751</v>
       </c>
       <c r="R35" t="n">
-        <v>6783777</v>
+        <v>6783884</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4099,12 +4098,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4132,7 +4131,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126244571</v>
+        <v>126244328</v>
       </c>
       <c r="B36" t="n">
         <v>82792</v>
@@ -4170,10 +4169,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>438751</v>
+        <v>438584</v>
       </c>
       <c r="R36" t="n">
-        <v>6783884</v>
+        <v>6783774</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4233,37 +4232,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126244328</v>
+        <v>126244106</v>
       </c>
       <c r="B37" t="n">
-        <v>82792</v>
+        <v>98382</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>221952</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>438584</v>
+        <v>438782</v>
       </c>
       <c r="R37" t="n">
-        <v>6783774</v>
+        <v>6783777</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4301,12 +4301,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4739,39 +4739,35 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126243702</v>
+        <v>126244589</v>
       </c>
       <c r="B42" t="n">
-        <v>98361</v>
+        <v>98382</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
@@ -4782,10 +4778,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>438786</v>
+        <v>438824</v>
       </c>
       <c r="R42" t="n">
-        <v>6783704</v>
+        <v>6783885</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4812,12 +4808,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4845,7 +4841,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126244589</v>
+        <v>126243995</v>
       </c>
       <c r="B43" t="n">
         <v>98382</v>
@@ -4884,10 +4880,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>438824</v>
+        <v>438953</v>
       </c>
       <c r="R43" t="n">
-        <v>6783885</v>
+        <v>6783788</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4914,12 +4910,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4947,35 +4943,39 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126243995</v>
+        <v>126243702</v>
       </c>
       <c r="B44" t="n">
-        <v>98382</v>
+        <v>98361</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
@@ -4986,10 +4986,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>438953</v>
+        <v>438786</v>
       </c>
       <c r="R44" t="n">
-        <v>6783788</v>
+        <v>6783704</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5263,10 +5263,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126244099</v>
+        <v>126243010</v>
       </c>
       <c r="B47" t="n">
-        <v>82792</v>
+        <v>78980</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5274,21 +5274,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>438804</v>
+        <v>438852</v>
       </c>
       <c r="R47" t="n">
-        <v>6783800</v>
+        <v>6783530</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5364,7 +5364,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126243010</v>
+        <v>126243233</v>
       </c>
       <c r="B48" t="n">
         <v>78980</v>
@@ -5402,10 +5402,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>438852</v>
+        <v>438775</v>
       </c>
       <c r="R48" t="n">
-        <v>6783530</v>
+        <v>6783504</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5465,10 +5465,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126243233</v>
+        <v>126243370</v>
       </c>
       <c r="B49" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5476,21 +5476,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5503,10 +5503,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>438775</v>
+        <v>438714</v>
       </c>
       <c r="R49" t="n">
-        <v>6783504</v>
+        <v>6783492</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5566,10 +5566,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126243370</v>
+        <v>126244099</v>
       </c>
       <c r="B50" t="n">
-        <v>79598</v>
+        <v>82792</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5577,21 +5577,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5604,10 +5604,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>438714</v>
+        <v>438804</v>
       </c>
       <c r="R50" t="n">
-        <v>6783492</v>
+        <v>6783800</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6277,37 +6277,42 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126243617</v>
+        <v>126243641</v>
       </c>
       <c r="B57" t="n">
-        <v>91245</v>
+        <v>98382</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6315,10 +6320,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>438797</v>
+        <v>438790</v>
       </c>
       <c r="R57" t="n">
-        <v>6783670</v>
+        <v>6783649</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6378,37 +6383,38 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126243980</v>
+        <v>126244294</v>
       </c>
       <c r="B58" t="n">
-        <v>78980</v>
+        <v>98382</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6416,10 +6422,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>438928</v>
+        <v>438723</v>
       </c>
       <c r="R58" t="n">
-        <v>6783763</v>
+        <v>6783752</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6446,12 +6452,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6479,10 +6485,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126244052</v>
+        <v>126243617</v>
       </c>
       <c r="B59" t="n">
-        <v>79598</v>
+        <v>91245</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6490,21 +6496,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6517,10 +6523,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>438821</v>
+        <v>438797</v>
       </c>
       <c r="R59" t="n">
-        <v>6783854</v>
+        <v>6783670</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6580,10 +6586,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126243462</v>
+        <v>126243823</v>
       </c>
       <c r="B60" t="n">
-        <v>78980</v>
+        <v>82792</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6591,21 +6597,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6618,10 +6624,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>438777</v>
+        <v>438911</v>
       </c>
       <c r="R60" t="n">
-        <v>6783527</v>
+        <v>6783821</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6681,7 +6687,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126243351</v>
+        <v>126243980</v>
       </c>
       <c r="B61" t="n">
         <v>78980</v>
@@ -6719,10 +6725,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>438767</v>
+        <v>438928</v>
       </c>
       <c r="R61" t="n">
-        <v>6783455</v>
+        <v>6783763</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6782,10 +6788,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126243986</v>
+        <v>126244052</v>
       </c>
       <c r="B62" t="n">
-        <v>78980</v>
+        <v>79598</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6793,21 +6799,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6820,10 +6826,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>438947</v>
+        <v>438821</v>
       </c>
       <c r="R62" t="n">
-        <v>6783782</v>
+        <v>6783854</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6883,46 +6889,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126243492</v>
+        <v>126243462</v>
       </c>
       <c r="B63" t="n">
-        <v>56849</v>
+        <v>78980</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6930,10 +6927,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>438871</v>
+        <v>438777</v>
       </c>
       <c r="R63" t="n">
-        <v>6783612</v>
+        <v>6783527</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6968,17 +6965,13 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Den tog ett s.k sandbad i sandblottan efter en rofyllda.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6997,10 +6990,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126243823</v>
+        <v>126243351</v>
       </c>
       <c r="B64" t="n">
-        <v>82792</v>
+        <v>78980</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7008,21 +7001,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7035,10 +7028,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>438911</v>
+        <v>438767</v>
       </c>
       <c r="R64" t="n">
-        <v>6783821</v>
+        <v>6783455</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -7098,42 +7091,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126243641</v>
+        <v>126243986</v>
       </c>
       <c r="B65" t="n">
-        <v>98382</v>
+        <v>78980</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7141,10 +7129,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>438790</v>
+        <v>438947</v>
       </c>
       <c r="R65" t="n">
-        <v>6783649</v>
+        <v>6783782</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7204,10 +7192,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126244294</v>
+        <v>126243492</v>
       </c>
       <c r="B66" t="n">
-        <v>98382</v>
+        <v>56849</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7215,27 +7203,35 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7243,10 +7239,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>438723</v>
+        <v>438871</v>
       </c>
       <c r="R66" t="n">
-        <v>6783752</v>
+        <v>6783612</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7273,12 +7269,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Den tog ett s.k sandbad i sandblottan efter en rofyllda.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7287,7 +7288,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7837,32 +7837,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126243459</v>
+        <v>126243314</v>
       </c>
       <c r="B72" t="n">
-        <v>79012</v>
+        <v>91832</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>185</v>
+        <v>1179</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>438777</v>
+        <v>438816</v>
       </c>
       <c r="R72" t="n">
-        <v>6783527</v>
+        <v>6783530</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7938,38 +7938,37 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126244337</v>
+        <v>126243042</v>
       </c>
       <c r="B73" t="n">
-        <v>98279</v>
+        <v>79059</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>223591</v>
+        <v>864</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -7977,10 +7976,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>438574</v>
+        <v>438848</v>
       </c>
       <c r="R73" t="n">
-        <v>6783811</v>
+        <v>6783520</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8007,12 +8006,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8040,32 +8039,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126243314</v>
+        <v>126244274</v>
       </c>
       <c r="B74" t="n">
-        <v>91832</v>
+        <v>82792</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1179</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8078,10 +8077,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>438816</v>
+        <v>438776</v>
       </c>
       <c r="R74" t="n">
-        <v>6783530</v>
+        <v>6783788</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8141,10 +8140,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126243042</v>
+        <v>126243459</v>
       </c>
       <c r="B75" t="n">
-        <v>79059</v>
+        <v>79012</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8152,21 +8151,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8179,10 +8178,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>438848</v>
+        <v>438777</v>
       </c>
       <c r="R75" t="n">
-        <v>6783520</v>
+        <v>6783527</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8242,37 +8241,38 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126244274</v>
+        <v>126244337</v>
       </c>
       <c r="B76" t="n">
-        <v>82792</v>
+        <v>98279</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1312</v>
+        <v>223591</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>438776</v>
+        <v>438574</v>
       </c>
       <c r="R76" t="n">
-        <v>6783788</v>
+        <v>6783811</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8310,12 +8310,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8856,10 +8856,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126243220</v>
+        <v>126243816</v>
       </c>
       <c r="B82" t="n">
-        <v>91210</v>
+        <v>98279</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8867,26 +8867,27 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5447</v>
+        <v>223591</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -8894,10 +8895,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>438775</v>
+        <v>438886</v>
       </c>
       <c r="R82" t="n">
-        <v>6783504</v>
+        <v>6783805</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8957,32 +8958,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126243505</v>
+        <v>126243608</v>
       </c>
       <c r="B83" t="n">
-        <v>80118</v>
+        <v>91603</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6463</v>
+        <v>2062</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8995,10 +8996,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>438858</v>
+        <v>438797</v>
       </c>
       <c r="R83" t="n">
-        <v>6783695</v>
+        <v>6783670</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -9058,27 +9059,27 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126243452</v>
+        <v>126243505</v>
       </c>
       <c r="B84" t="n">
-        <v>78980</v>
+        <v>80118</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9096,10 +9097,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>438740</v>
+        <v>438858</v>
       </c>
       <c r="R84" t="n">
-        <v>6783462</v>
+        <v>6783695</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9159,32 +9160,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126243191</v>
+        <v>126243452</v>
       </c>
       <c r="B85" t="n">
-        <v>79066</v>
+        <v>78980</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6450</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9197,10 +9198,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>438777</v>
+        <v>438740</v>
       </c>
       <c r="R85" t="n">
-        <v>6783503</v>
+        <v>6783462</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9260,42 +9261,37 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126243732</v>
+        <v>126243191</v>
       </c>
       <c r="B86" t="n">
-        <v>57654</v>
+        <v>79066</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100049</v>
+        <v>6450</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9303,10 +9299,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>438882</v>
+        <v>438777</v>
       </c>
       <c r="R86" t="n">
-        <v>6783685</v>
+        <v>6783503</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9347,6 +9343,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9365,32 +9362,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126243608</v>
+        <v>126243220</v>
       </c>
       <c r="B87" t="n">
-        <v>91603</v>
+        <v>91210</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9403,10 +9400,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>438797</v>
+        <v>438775</v>
       </c>
       <c r="R87" t="n">
-        <v>6783670</v>
+        <v>6783504</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9466,42 +9463,42 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126243676</v>
+        <v>126243732</v>
       </c>
       <c r="B88" t="n">
-        <v>98382</v>
+        <v>57654</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -9509,10 +9506,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>438813</v>
+        <v>438882</v>
       </c>
       <c r="R88" t="n">
-        <v>6783722</v>
+        <v>6783685</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9553,7 +9550,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9572,10 +9568,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126243816</v>
+        <v>126243676</v>
       </c>
       <c r="B89" t="n">
-        <v>98279</v>
+        <v>98382</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9583,24 +9579,28 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>223591</v>
+        <v>221952</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
@@ -9611,10 +9611,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>438886</v>
+        <v>438813</v>
       </c>
       <c r="R89" t="n">
-        <v>6783805</v>
+        <v>6783722</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9674,10 +9674,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126249487</v>
+        <v>126243143</v>
       </c>
       <c r="B90" t="n">
-        <v>98382</v>
+        <v>56849</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9685,37 +9685,45 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221952</v>
+        <v>100138</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Räklitt, Hållberg, Dlr</t>
+          <t>Hålberg-Räklitt, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>438890</v>
+        <v>438785</v>
       </c>
       <c r="R90" t="n">
-        <v>6783610</v>
+        <v>6783487</v>
       </c>
       <c r="S90" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9739,22 +9747,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>21:07</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>21:07</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>En hona och 5 kycklingar</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9769,22 +9772,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Steve Daurer</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126243143</v>
+        <v>126249487</v>
       </c>
       <c r="B91" t="n">
-        <v>56849</v>
+        <v>98382</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9792,45 +9795,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Hålberg-Räklitt, Dlr</t>
+          <t>Räklitt, Hållberg, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>438785</v>
+        <v>438890</v>
       </c>
       <c r="R91" t="n">
-        <v>6783487</v>
+        <v>6783610</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9854,17 +9849,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>21:07</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>En hona och 5 kycklingar</t>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>21:07</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9879,12 +9879,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -9993,10 +9993,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126243503</v>
+        <v>126243395</v>
       </c>
       <c r="B93" t="n">
-        <v>78980</v>
+        <v>79569</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10004,21 +10004,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10031,10 +10031,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>438858</v>
+        <v>438682</v>
       </c>
       <c r="R93" t="n">
-        <v>6783695</v>
+        <v>6783454</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10094,10 +10094,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126243973</v>
+        <v>126243503</v>
       </c>
       <c r="B94" t="n">
-        <v>88654</v>
+        <v>78980</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10105,21 +10105,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10132,10 +10132,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>438928</v>
+        <v>438858</v>
       </c>
       <c r="R94" t="n">
-        <v>6783763</v>
+        <v>6783695</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10195,10 +10195,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126243447</v>
+        <v>126243973</v>
       </c>
       <c r="B95" t="n">
-        <v>82792</v>
+        <v>88654</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10206,21 +10206,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10233,10 +10233,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>438740</v>
+        <v>438928</v>
       </c>
       <c r="R95" t="n">
-        <v>6783462</v>
+        <v>6783763</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10296,10 +10296,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126243415</v>
+        <v>126243447</v>
       </c>
       <c r="B96" t="n">
-        <v>57654</v>
+        <v>82792</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10307,31 +10307,26 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -10339,10 +10334,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>438722</v>
+        <v>438740</v>
       </c>
       <c r="R96" t="n">
-        <v>6783470</v>
+        <v>6783462</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10383,6 +10378,7 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -10401,39 +10397,42 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126244082</v>
+        <v>126243415</v>
       </c>
       <c r="B97" t="n">
-        <v>5176</v>
+        <v>57654</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -10441,10 +10440,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>438809</v>
+        <v>438722</v>
       </c>
       <c r="R97" t="n">
-        <v>6783806</v>
+        <v>6783470</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10485,7 +10484,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10504,37 +10502,39 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126243395</v>
+        <v>126244082</v>
       </c>
       <c r="B98" t="n">
-        <v>79569</v>
+        <v>5176</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>100526</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -10542,10 +10542,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>438682</v>
+        <v>438809</v>
       </c>
       <c r="R98" t="n">
-        <v>6783454</v>
+        <v>6783806</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY123"/>
+  <dimension ref="A1:AY149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13178,6 +13178,2743 @@
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>128395406</v>
+      </c>
+      <c r="B124" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>438818</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6783477</v>
+      </c>
+      <c r="S124" t="n">
+        <v>5</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Garnlav på tall.</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>128395378</v>
+      </c>
+      <c r="B125" t="n">
+        <v>57833</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>438818</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6783477</v>
+      </c>
+      <c r="S125" t="n">
+        <v>5</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>En talltita i sitt permanenta revir. Om delar av skogen avverkas förlorar talltitan reviret för redan nu är den resterande olikåldriga och skiktade kontinuitetsskogen på gränsen för minsta revirstorlek en talltita kräver.</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>128395197</v>
+      </c>
+      <c r="B126" t="n">
+        <v>57670</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>438915</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6783590</v>
+      </c>
+      <c r="S126" t="n">
+        <v>5</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Hanen har tidigare observerats I reviret respektive den gamla kontinuitetsskogen. Det noterades att det undan för undan har kalavverkats samma kontinuitetsskog även tidigare och vid det angränsande och ca 3 år gamla hygget räknades upp till 230 årsringar på flertalet avverkade tallar. Med tanke på detta är det ytterst viktig att aktuell kontinuitetsskog och reviret ej avverkas för det finns inte mycket kvar av kontinuitetsskog och lämplig revir för spillkråkan i trakten.</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>128395880</v>
+      </c>
+      <c r="B127" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>438950</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6783777</v>
+      </c>
+      <c r="S127" t="n">
+        <v>5</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>128395535</v>
+      </c>
+      <c r="B128" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>438876</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6783682</v>
+      </c>
+      <c r="S128" t="n">
+        <v>5</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>En växtlokal med ett tjugotal plantor.</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128395870</v>
+      </c>
+      <c r="B129" t="n">
+        <v>91812</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>438950</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6783777</v>
+      </c>
+      <c r="S129" t="n">
+        <v>5</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128395275</v>
+      </c>
+      <c r="B130" t="n">
+        <v>91323</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>438938</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6783582</v>
+      </c>
+      <c r="S130" t="n">
+        <v>5</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF130" t="inlineStr"/>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>128395203</v>
+      </c>
+      <c r="B131" t="n">
+        <v>79118</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>438915</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6783590</v>
+      </c>
+      <c r="S131" t="n">
+        <v>5</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF131" t="inlineStr"/>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>128395068</v>
+      </c>
+      <c r="B132" t="n">
+        <v>79650</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>438904</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6783667</v>
+      </c>
+      <c r="S132" t="n">
+        <v>5</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF132" t="inlineStr"/>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>128395657</v>
+      </c>
+      <c r="B133" t="n">
+        <v>82873</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>438915</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6783789</v>
+      </c>
+      <c r="S133" t="n">
+        <v>5</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF133" t="inlineStr"/>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>128395093</v>
+      </c>
+      <c r="B134" t="n">
+        <v>79118</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>438902</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6783655</v>
+      </c>
+      <c r="S134" t="n">
+        <v>5</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF134" t="inlineStr"/>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>128395497</v>
+      </c>
+      <c r="B135" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>438878</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6783567</v>
+      </c>
+      <c r="S135" t="n">
+        <v>5</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Färska och typiska hackmärken av tretåig hackspett i en mindre gran. Själva hackspetten en hane sågs samma dag i närheten.</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>128395841</v>
+      </c>
+      <c r="B136" t="n">
+        <v>92055</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>438897</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6783810</v>
+      </c>
+      <c r="S136" t="n">
+        <v>5</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF136" t="inlineStr"/>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>128395056</v>
+      </c>
+      <c r="B137" t="n">
+        <v>56867</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>438973</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6783689</v>
+      </c>
+      <c r="S137" t="n">
+        <v>5</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>En större flock som troligen hade höstspel i kanten till den gamla kontinuitetsskogen. Nu för tiden är det ganska ovanligt med större flockar och man endast vid spelaktivitet kan observera flera.</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>128395313</v>
+      </c>
+      <c r="B138" t="n">
+        <v>98476</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>438888</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6783535</v>
+      </c>
+      <c r="S138" t="n">
+        <v>5</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>En växtlokal med ett tiotal plantor.</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF138" t="inlineStr"/>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>128395667</v>
+      </c>
+      <c r="B139" t="n">
+        <v>75153</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>311</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Brun nållav</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Chaenotheca phaeocephala</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Turner) Th.Fr.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>438913</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6783798</v>
+      </c>
+      <c r="S139" t="n">
+        <v>5</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF139" t="inlineStr"/>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>128395852</v>
+      </c>
+      <c r="B140" t="n">
+        <v>82873</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>438930</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6783803</v>
+      </c>
+      <c r="S140" t="n">
+        <v>5</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF140" t="inlineStr"/>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>128395820</v>
+      </c>
+      <c r="B141" t="n">
+        <v>57673</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>438897</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6783810</v>
+      </c>
+      <c r="S141" t="n">
+        <v>5</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>En hane som troligen håller på att etablera revir i den gamla kontinuitetsskogen. Förutom själv observationen av fågeln sågs även färska ringhack som indikerar revir respektive revirbildning. Efter trettio år av iakttagelser och egna studier om tretåig hackspett har jag som observatör och erfaren skogsekolog förstod att ringhack är främst ett sätt att markera revir och har inget med att dricka sav att göra. För de allra flesta ringhack sker i gran och tall som knappast har någon sav utan istället kåda och så sker ringhack även utanför trädens savtid. Skulle det vara att dricka sav skulle enstaka hack i en björk räcka för ändamålet.</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>128395876</v>
+      </c>
+      <c r="B142" t="n">
+        <v>82873</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>438950</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6783777</v>
+      </c>
+      <c r="S142" t="n">
+        <v>5</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF142" t="inlineStr"/>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>128395118</v>
+      </c>
+      <c r="B143" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>438926</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6783632</v>
+      </c>
+      <c r="S143" t="n">
+        <v>5</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF143" t="inlineStr"/>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>128395878</v>
+      </c>
+      <c r="B144" t="n">
+        <v>91376</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>438950</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6783777</v>
+      </c>
+      <c r="S144" t="n">
+        <v>5</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF144" t="inlineStr"/>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>128395863</v>
+      </c>
+      <c r="B145" t="n">
+        <v>75153</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>311</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Brun nållav</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Chaenotheca phaeocephala</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Turner) Th.Fr.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>438948</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6783801</v>
+      </c>
+      <c r="S145" t="n">
+        <v>5</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>128395091</v>
+      </c>
+      <c r="B146" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>438902</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6783655</v>
+      </c>
+      <c r="S146" t="n">
+        <v>5</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF146" t="inlineStr"/>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>128395650</v>
+      </c>
+      <c r="B147" t="n">
+        <v>79032</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>438915</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6783789</v>
+      </c>
+      <c r="S147" t="n">
+        <v>5</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>128395641</v>
+      </c>
+      <c r="B148" t="n">
+        <v>56864</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>438915</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6783789</v>
+      </c>
+      <c r="S148" t="n">
+        <v>5</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>En stationär höna. Tidigare sågs troligen samma höna med flera kycklingar i närheten och det är uppenbart att den gamla kontinuitetsskogen som är den sista riktiga skogen med intakt ekosystem i plantagehavet är avgörande för tjädrarna.</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>128395834</v>
+      </c>
+      <c r="B149" t="n">
+        <v>82873</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Hålberg-Räklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>438897</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6783810</v>
+      </c>
+      <c r="S149" t="n">
+        <v>5</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF149" t="inlineStr"/>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -13404,10 +13404,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128395197</v>
+        <v>128395880</v>
       </c>
       <c r="B126" t="n">
-        <v>57670</v>
+        <v>79032</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13415,43 +13415,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
@@ -13459,10 +13442,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>438915</v>
+        <v>438950</v>
       </c>
       <c r="R126" t="n">
-        <v>6783590</v>
+        <v>6783777</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13497,17 +13480,13 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Hanen har tidigare observerats I reviret respektive den gamla kontinuitetsskogen. Det noterades att det undan för undan har kalavverkats samma kontinuitetsskog även tidigare och vid det angränsande och ca 3 år gamla hygget räknades upp till 230 årsringar på flertalet avverkade tallar. Med tanke på detta är det ytterst viktig att aktuell kontinuitetsskog och reviret ej avverkas för det finns inte mycket kvar av kontinuitetsskog och lämplig revir för spillkråkan i trakten.</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13526,10 +13505,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128395880</v>
+        <v>128395197</v>
       </c>
       <c r="B127" t="n">
-        <v>79032</v>
+        <v>57670</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13537,26 +13516,43 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -13564,10 +13560,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>438950</v>
+        <v>438915</v>
       </c>
       <c r="R127" t="n">
-        <v>6783777</v>
+        <v>6783590</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -13602,13 +13598,17 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Hanen har tidigare observerats I reviret respektive den gamla kontinuitetsskogen. Det noterades att det undan för undan har kalavverkats samma kontinuitetsskog även tidigare och vid det angränsande och ca 3 år gamla hygget räknades upp till 230 årsringar på flertalet avverkade tallar. Med tanke på detta är det ytterst viktig att aktuell kontinuitetsskog och reviret ej avverkas för det finns inte mycket kvar av kontinuitetsskog och lämplig revir för spillkråkan i trakten.</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13630,7 +13630,7 @@
         <v>128395535</v>
       </c>
       <c r="B128" t="n">
-        <v>98476</v>
+        <v>98478</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13734,32 +13734,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128395870</v>
+        <v>128395275</v>
       </c>
       <c r="B129" t="n">
-        <v>91812</v>
+        <v>91325</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13772,10 +13772,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>438950</v>
+        <v>438938</v>
       </c>
       <c r="R129" t="n">
-        <v>6783777</v>
+        <v>6783582</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -13835,32 +13835,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128395275</v>
+        <v>128395870</v>
       </c>
       <c r="B130" t="n">
-        <v>91323</v>
+        <v>91814</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13873,10 +13873,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>438938</v>
+        <v>438950</v>
       </c>
       <c r="R130" t="n">
-        <v>6783582</v>
+        <v>6783777</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -13936,32 +13936,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128395203</v>
+        <v>128395068</v>
       </c>
       <c r="B131" t="n">
-        <v>79118</v>
+        <v>79650</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6450</v>
+        <v>6453</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13974,10 +13974,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>438915</v>
+        <v>438904</v>
       </c>
       <c r="R131" t="n">
-        <v>6783590</v>
+        <v>6783667</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -14037,32 +14037,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128395068</v>
+        <v>128395203</v>
       </c>
       <c r="B132" t="n">
-        <v>79650</v>
+        <v>79118</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6453</v>
+        <v>6450</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14075,10 +14075,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>438904</v>
+        <v>438915</v>
       </c>
       <c r="R132" t="n">
-        <v>6783667</v>
+        <v>6783590</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -14138,32 +14138,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128395657</v>
+        <v>128395093</v>
       </c>
       <c r="B133" t="n">
-        <v>82873</v>
+        <v>79118</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1312</v>
+        <v>6450</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14176,10 +14176,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>438915</v>
+        <v>438902</v>
       </c>
       <c r="R133" t="n">
-        <v>6783789</v>
+        <v>6783655</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -14239,32 +14239,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128395093</v>
+        <v>128395657</v>
       </c>
       <c r="B134" t="n">
-        <v>79118</v>
+        <v>82873</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14277,10 +14277,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>438902</v>
+        <v>438915</v>
       </c>
       <c r="R134" t="n">
-        <v>6783655</v>
+        <v>6783789</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -14453,7 +14453,7 @@
         <v>128395841</v>
       </c>
       <c r="B136" t="n">
-        <v>92055</v>
+        <v>92057</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14661,38 +14661,37 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128395313</v>
+        <v>128395667</v>
       </c>
       <c r="B138" t="n">
-        <v>98476</v>
+        <v>75153</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>311</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
@@ -14700,10 +14699,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>438888</v>
+        <v>438913</v>
       </c>
       <c r="R138" t="n">
-        <v>6783535</v>
+        <v>6783798</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -14736,11 +14735,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>En växtlokal med ett tiotal plantor.</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14768,32 +14762,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128395667</v>
+        <v>128395852</v>
       </c>
       <c r="B139" t="n">
-        <v>75153</v>
+        <v>82873</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>311</v>
+        <v>1312</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14806,10 +14800,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>438913</v>
+        <v>438930</v>
       </c>
       <c r="R139" t="n">
-        <v>6783798</v>
+        <v>6783803</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -14869,10 +14863,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128395852</v>
+        <v>128395820</v>
       </c>
       <c r="B140" t="n">
-        <v>82873</v>
+        <v>57673</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14880,26 +14874,39 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -14907,10 +14914,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>438930</v>
+        <v>438897</v>
       </c>
       <c r="R140" t="n">
-        <v>6783803</v>
+        <v>6783810</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -14945,13 +14952,17 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>En hane som troligen håller på att etablera revir i den gamla kontinuitetsskogen. Förutom själv observationen av fågeln sågs även färska ringhack som indikerar revir respektive revirbildning. Efter trettio år av iakttagelser och egna studier om tretåig hackspett har jag som observatör och erfaren skogsekolog förstod att ringhack är främst ett sätt att markera revir och har inget med att dricka sav att göra. För de allra flesta ringhack sker i gran och tall som knappast har någon sav utan istället kåda och så sker ringhack även utanför trädens savtid. Skulle det vara att dricka sav skulle enstaka hack i en björk räcka för ändamålet.</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14970,50 +14981,38 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128395820</v>
+        <v>128395313</v>
       </c>
       <c r="B141" t="n">
-        <v>57673</v>
+        <v>98478</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -15021,10 +15020,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>438897</v>
+        <v>438888</v>
       </c>
       <c r="R141" t="n">
-        <v>6783810</v>
+        <v>6783535</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -15061,7 +15060,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>En hane som troligen håller på att etablera revir i den gamla kontinuitetsskogen. Förutom själv observationen av fågeln sågs även färska ringhack som indikerar revir respektive revirbildning. Efter trettio år av iakttagelser och egna studier om tretåig hackspett har jag som observatör och erfaren skogsekolog förstod att ringhack är främst ett sätt att markera revir och har inget med att dricka sav att göra. För de allra flesta ringhack sker i gran och tall som knappast har någon sav utan istället kåda och så sker ringhack även utanför trädens savtid. Skulle det vara att dricka sav skulle enstaka hack i en björk räcka för ändamålet.</t>
+          <t>En växtlokal med ett tiotal plantor.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15070,6 +15069,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15088,10 +15088,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128395876</v>
+        <v>128395118</v>
       </c>
       <c r="B142" t="n">
-        <v>82873</v>
+        <v>79032</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15099,21 +15099,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15126,10 +15126,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>438950</v>
+        <v>438926</v>
       </c>
       <c r="R142" t="n">
-        <v>6783777</v>
+        <v>6783632</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15189,10 +15189,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128395118</v>
+        <v>128395876</v>
       </c>
       <c r="B143" t="n">
-        <v>79032</v>
+        <v>82873</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15200,21 +15200,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15227,10 +15227,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>438926</v>
+        <v>438950</v>
       </c>
       <c r="R143" t="n">
-        <v>6783632</v>
+        <v>6783777</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -15293,7 +15293,7 @@
         <v>128395878</v>
       </c>
       <c r="B144" t="n">
-        <v>91376</v>
+        <v>91378</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -13183,7 +13183,7 @@
         <v>128395406</v>
       </c>
       <c r="B124" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>128395378</v>
       </c>
       <c r="B125" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>128395880</v>
       </c>
       <c r="B126" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>128395197</v>
       </c>
       <c r="B127" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>128395535</v>
       </c>
       <c r="B128" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13734,32 +13734,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128395275</v>
+        <v>128395870</v>
       </c>
       <c r="B129" t="n">
-        <v>91325</v>
+        <v>91906</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13772,10 +13772,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>438938</v>
+        <v>438950</v>
       </c>
       <c r="R129" t="n">
-        <v>6783582</v>
+        <v>6783777</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -13835,32 +13835,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128395870</v>
+        <v>128395275</v>
       </c>
       <c r="B130" t="n">
-        <v>91814</v>
+        <v>91417</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13873,10 +13873,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>438950</v>
+        <v>438938</v>
       </c>
       <c r="R130" t="n">
-        <v>6783777</v>
+        <v>6783582</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -13939,7 +13939,7 @@
         <v>128395068</v>
       </c>
       <c r="B131" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>128395203</v>
       </c>
       <c r="B132" t="n">
-        <v>79118</v>
+        <v>79169</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>128395093</v>
       </c>
       <c r="B133" t="n">
-        <v>79118</v>
+        <v>79169</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>128395657</v>
       </c>
       <c r="B134" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>128395497</v>
       </c>
       <c r="B135" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>128395841</v>
       </c>
       <c r="B136" t="n">
-        <v>92057</v>
+        <v>92149</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>128395056</v>
       </c>
       <c r="B137" t="n">
-        <v>56867</v>
+        <v>56879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>128395667</v>
       </c>
       <c r="B138" t="n">
-        <v>75153</v>
+        <v>75168</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>128395852</v>
       </c>
       <c r="B139" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>128395820</v>
       </c>
       <c r="B140" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>128395313</v>
       </c>
       <c r="B141" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15088,10 +15088,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128395118</v>
+        <v>128395876</v>
       </c>
       <c r="B142" t="n">
-        <v>79032</v>
+        <v>82942</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15099,21 +15099,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15126,10 +15126,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>438926</v>
+        <v>438950</v>
       </c>
       <c r="R142" t="n">
-        <v>6783632</v>
+        <v>6783777</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15189,10 +15189,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128395876</v>
+        <v>128395118</v>
       </c>
       <c r="B143" t="n">
-        <v>82873</v>
+        <v>79083</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15200,21 +15200,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15227,10 +15227,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>438950</v>
+        <v>438926</v>
       </c>
       <c r="R143" t="n">
-        <v>6783777</v>
+        <v>6783632</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -15293,7 +15293,7 @@
         <v>128395878</v>
       </c>
       <c r="B144" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>128395863</v>
       </c>
       <c r="B145" t="n">
-        <v>75153</v>
+        <v>75168</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>128395091</v>
       </c>
       <c r="B146" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>128395650</v>
       </c>
       <c r="B147" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>128395641</v>
       </c>
       <c r="B148" t="n">
-        <v>56864</v>
+        <v>56876</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>128395834</v>
       </c>
       <c r="B149" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -14138,32 +14138,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128395093</v>
+        <v>128395657</v>
       </c>
       <c r="B133" t="n">
-        <v>79169</v>
+        <v>82942</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14176,10 +14176,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>438902</v>
+        <v>438915</v>
       </c>
       <c r="R133" t="n">
-        <v>6783655</v>
+        <v>6783789</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -14239,32 +14239,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128395657</v>
+        <v>128395093</v>
       </c>
       <c r="B134" t="n">
-        <v>82942</v>
+        <v>79169</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1312</v>
+        <v>6450</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14277,10 +14277,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>438915</v>
+        <v>438902</v>
       </c>
       <c r="R134" t="n">
-        <v>6783789</v>
+        <v>6783655</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -14762,10 +14762,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128395852</v>
+        <v>128395820</v>
       </c>
       <c r="B139" t="n">
-        <v>82942</v>
+        <v>57685</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14773,26 +14773,39 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
@@ -14800,10 +14813,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>438930</v>
+        <v>438897</v>
       </c>
       <c r="R139" t="n">
-        <v>6783803</v>
+        <v>6783810</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -14838,13 +14851,17 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>En hane som troligen håller på att etablera revir i den gamla kontinuitetsskogen. Förutom själv observationen av fågeln sågs även färska ringhack som indikerar revir respektive revirbildning. Efter trettio år av iakttagelser och egna studier om tretåig hackspett har jag som observatör och erfaren skogsekolog förstod att ringhack är främst ett sätt att markera revir och har inget med att dricka sav att göra. För de allra flesta ringhack sker i gran och tall som knappast har någon sav utan istället kåda och så sker ringhack även utanför trädens savtid. Skulle det vara att dricka sav skulle enstaka hack i en björk räcka för ändamålet.</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14863,50 +14880,38 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128395820</v>
+        <v>128395313</v>
       </c>
       <c r="B140" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -14914,10 +14919,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>438897</v>
+        <v>438888</v>
       </c>
       <c r="R140" t="n">
-        <v>6783810</v>
+        <v>6783535</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -14954,7 +14959,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>En hane som troligen håller på att etablera revir i den gamla kontinuitetsskogen. Förutom själv observationen av fågeln sågs även färska ringhack som indikerar revir respektive revirbildning. Efter trettio år av iakttagelser och egna studier om tretåig hackspett har jag som observatör och erfaren skogsekolog förstod att ringhack är främst ett sätt att markera revir och har inget med att dricka sav att göra. För de allra flesta ringhack sker i gran och tall som knappast har någon sav utan istället kåda och så sker ringhack även utanför trädens savtid. Skulle det vara att dricka sav skulle enstaka hack i en björk räcka för ändamålet.</t>
+          <t>En växtlokal med ett tiotal plantor.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14963,6 +14968,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14981,38 +14987,37 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128395313</v>
+        <v>128395852</v>
       </c>
       <c r="B141" t="n">
-        <v>98571</v>
+        <v>82942</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -15020,10 +15025,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>438888</v>
+        <v>438930</v>
       </c>
       <c r="R141" t="n">
-        <v>6783535</v>
+        <v>6783803</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -15056,11 +15061,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>En växtlokal med ett tiotal plantor.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15088,10 +15088,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128395876</v>
+        <v>128395118</v>
       </c>
       <c r="B142" t="n">
-        <v>82942</v>
+        <v>79083</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15099,21 +15099,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15126,10 +15126,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>438950</v>
+        <v>438926</v>
       </c>
       <c r="R142" t="n">
-        <v>6783777</v>
+        <v>6783632</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15189,10 +15189,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128395118</v>
+        <v>128395876</v>
       </c>
       <c r="B143" t="n">
-        <v>79083</v>
+        <v>82942</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15200,21 +15200,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15227,10 +15227,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>438926</v>
+        <v>438950</v>
       </c>
       <c r="R143" t="n">
-        <v>6783632</v>
+        <v>6783777</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -13404,10 +13404,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128395880</v>
+        <v>128395197</v>
       </c>
       <c r="B126" t="n">
-        <v>79083</v>
+        <v>57682</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13415,26 +13415,43 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
@@ -13442,10 +13459,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>438950</v>
+        <v>438915</v>
       </c>
       <c r="R126" t="n">
-        <v>6783777</v>
+        <v>6783590</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13480,13 +13497,17 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Hanen har tidigare observerats I reviret respektive den gamla kontinuitetsskogen. Det noterades att det undan för undan har kalavverkats samma kontinuitetsskog även tidigare och vid det angränsande och ca 3 år gamla hygget räknades upp till 230 årsringar på flertalet avverkade tallar. Med tanke på detta är det ytterst viktig att aktuell kontinuitetsskog och reviret ej avverkas för det finns inte mycket kvar av kontinuitetsskog och lämplig revir för spillkråkan i trakten.</t>
+        </is>
+      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13505,10 +13526,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128395197</v>
+        <v>128395880</v>
       </c>
       <c r="B127" t="n">
-        <v>57682</v>
+        <v>79083</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13516,43 +13537,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -13560,10 +13564,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>438915</v>
+        <v>438950</v>
       </c>
       <c r="R127" t="n">
-        <v>6783590</v>
+        <v>6783777</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -13598,17 +13602,13 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Hanen har tidigare observerats I reviret respektive den gamla kontinuitetsskogen. Det noterades att det undan för undan har kalavverkats samma kontinuitetsskog även tidigare och vid det angränsande och ca 3 år gamla hygget räknades upp till 230 årsringar på flertalet avverkade tallar. Med tanke på detta är det ytterst viktig att aktuell kontinuitetsskog och reviret ej avverkas för det finns inte mycket kvar av kontinuitetsskog och lämplig revir för spillkråkan i trakten.</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -14762,10 +14762,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128395820</v>
+        <v>128395852</v>
       </c>
       <c r="B139" t="n">
-        <v>57685</v>
+        <v>82942</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14773,39 +14773,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
@@ -14813,10 +14800,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>438897</v>
+        <v>438930</v>
       </c>
       <c r="R139" t="n">
-        <v>6783810</v>
+        <v>6783803</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -14851,17 +14838,13 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>En hane som troligen håller på att etablera revir i den gamla kontinuitetsskogen. Förutom själv observationen av fågeln sågs även färska ringhack som indikerar revir respektive revirbildning. Efter trettio år av iakttagelser och egna studier om tretåig hackspett har jag som observatör och erfaren skogsekolog förstod att ringhack är främst ett sätt att markera revir och har inget med att dricka sav att göra. För de allra flesta ringhack sker i gran och tall som knappast har någon sav utan istället kåda och så sker ringhack även utanför trädens savtid. Skulle det vara att dricka sav skulle enstaka hack i en björk räcka för ändamålet.</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14880,38 +14863,50 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128395313</v>
+        <v>128395820</v>
       </c>
       <c r="B140" t="n">
-        <v>98571</v>
+        <v>57685</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -14919,10 +14914,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>438888</v>
+        <v>438897</v>
       </c>
       <c r="R140" t="n">
-        <v>6783535</v>
+        <v>6783810</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -14959,7 +14954,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>En växtlokal med ett tiotal plantor.</t>
+          <t>En hane som troligen håller på att etablera revir i den gamla kontinuitetsskogen. Förutom själv observationen av fågeln sågs även färska ringhack som indikerar revir respektive revirbildning. Efter trettio år av iakttagelser och egna studier om tretåig hackspett har jag som observatör och erfaren skogsekolog förstod att ringhack är främst ett sätt att markera revir och har inget med att dricka sav att göra. För de allra flesta ringhack sker i gran och tall som knappast har någon sav utan istället kåda och så sker ringhack även utanför trädens savtid. Skulle det vara att dricka sav skulle enstaka hack i en björk räcka för ändamålet.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14968,7 +14963,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14987,37 +14981,38 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128395852</v>
+        <v>128395313</v>
       </c>
       <c r="B141" t="n">
-        <v>82942</v>
+        <v>98571</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -15025,10 +15020,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>438930</v>
+        <v>438888</v>
       </c>
       <c r="R141" t="n">
-        <v>6783803</v>
+        <v>6783535</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -15061,6 +15056,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>En växtlokal med ett tiotal plantor.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15088,10 +15088,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128395118</v>
+        <v>128395876</v>
       </c>
       <c r="B142" t="n">
-        <v>79083</v>
+        <v>82942</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15099,21 +15099,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15126,10 +15126,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>438926</v>
+        <v>438950</v>
       </c>
       <c r="R142" t="n">
-        <v>6783632</v>
+        <v>6783777</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15189,10 +15189,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128395876</v>
+        <v>128395118</v>
       </c>
       <c r="B143" t="n">
-        <v>82942</v>
+        <v>79083</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15200,21 +15200,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15227,10 +15227,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>438950</v>
+        <v>438926</v>
       </c>
       <c r="R143" t="n">
-        <v>6783777</v>
+        <v>6783632</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -13734,32 +13734,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128395870</v>
+        <v>128395275</v>
       </c>
       <c r="B129" t="n">
-        <v>91906</v>
+        <v>91417</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13772,10 +13772,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>438950</v>
+        <v>438938</v>
       </c>
       <c r="R129" t="n">
-        <v>6783777</v>
+        <v>6783582</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -13835,32 +13835,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128395275</v>
+        <v>128395870</v>
       </c>
       <c r="B130" t="n">
-        <v>91417</v>
+        <v>91906</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13873,10 +13873,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>438938</v>
+        <v>438950</v>
       </c>
       <c r="R130" t="n">
-        <v>6783582</v>
+        <v>6783777</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -14762,10 +14762,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128395852</v>
+        <v>128395820</v>
       </c>
       <c r="B139" t="n">
-        <v>82942</v>
+        <v>57685</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14773,26 +14773,39 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
@@ -14800,10 +14813,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>438930</v>
+        <v>438897</v>
       </c>
       <c r="R139" t="n">
-        <v>6783803</v>
+        <v>6783810</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -14838,13 +14851,17 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>En hane som troligen håller på att etablera revir i den gamla kontinuitetsskogen. Förutom själv observationen av fågeln sågs även färska ringhack som indikerar revir respektive revirbildning. Efter trettio år av iakttagelser och egna studier om tretåig hackspett har jag som observatör och erfaren skogsekolog förstod att ringhack är främst ett sätt att markera revir och har inget med att dricka sav att göra. För de allra flesta ringhack sker i gran och tall som knappast har någon sav utan istället kåda och så sker ringhack även utanför trädens savtid. Skulle det vara att dricka sav skulle enstaka hack i en björk räcka för ändamålet.</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14863,50 +14880,38 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128395820</v>
+        <v>128395313</v>
       </c>
       <c r="B140" t="n">
-        <v>57685</v>
+        <v>98571</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -14914,10 +14919,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>438897</v>
+        <v>438888</v>
       </c>
       <c r="R140" t="n">
-        <v>6783810</v>
+        <v>6783535</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -14954,7 +14959,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>En hane som troligen håller på att etablera revir i den gamla kontinuitetsskogen. Förutom själv observationen av fågeln sågs även färska ringhack som indikerar revir respektive revirbildning. Efter trettio år av iakttagelser och egna studier om tretåig hackspett har jag som observatör och erfaren skogsekolog förstod att ringhack är främst ett sätt att markera revir och har inget med att dricka sav att göra. För de allra flesta ringhack sker i gran och tall som knappast har någon sav utan istället kåda och så sker ringhack även utanför trädens savtid. Skulle det vara att dricka sav skulle enstaka hack i en björk räcka för ändamålet.</t>
+          <t>En växtlokal med ett tiotal plantor.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14963,6 +14968,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14981,38 +14987,37 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128395313</v>
+        <v>128395852</v>
       </c>
       <c r="B141" t="n">
-        <v>98571</v>
+        <v>82942</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -15020,10 +15025,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>438888</v>
+        <v>438930</v>
       </c>
       <c r="R141" t="n">
-        <v>6783535</v>
+        <v>6783803</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -15056,11 +15061,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>En växtlokal med ett tiotal plantor.</t>
         </is>
       </c>
       <c r="AD141" t="b">

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -13183,7 +13183,7 @@
         <v>128395406</v>
       </c>
       <c r="B124" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>128395378</v>
       </c>
       <c r="B125" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13404,10 +13404,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128395197</v>
+        <v>128395880</v>
       </c>
       <c r="B126" t="n">
-        <v>57682</v>
+        <v>79087</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13415,43 +13415,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
@@ -13459,10 +13442,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>438915</v>
+        <v>438950</v>
       </c>
       <c r="R126" t="n">
-        <v>6783590</v>
+        <v>6783777</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13497,17 +13480,13 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Hanen har tidigare observerats I reviret respektive den gamla kontinuitetsskogen. Det noterades att det undan för undan har kalavverkats samma kontinuitetsskog även tidigare och vid det angränsande och ca 3 år gamla hygget räknades upp till 230 årsringar på flertalet avverkade tallar. Med tanke på detta är det ytterst viktig att aktuell kontinuitetsskog och reviret ej avverkas för det finns inte mycket kvar av kontinuitetsskog och lämplig revir för spillkråkan i trakten.</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13526,10 +13505,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128395880</v>
+        <v>128395197</v>
       </c>
       <c r="B127" t="n">
-        <v>79083</v>
+        <v>57686</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13537,26 +13516,43 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -13564,10 +13560,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>438950</v>
+        <v>438915</v>
       </c>
       <c r="R127" t="n">
-        <v>6783777</v>
+        <v>6783590</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -13602,13 +13598,17 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Hanen har tidigare observerats I reviret respektive den gamla kontinuitetsskogen. Det noterades att det undan för undan har kalavverkats samma kontinuitetsskog även tidigare och vid det angränsande och ca 3 år gamla hygget räknades upp till 230 årsringar på flertalet avverkade tallar. Med tanke på detta är det ytterst viktig att aktuell kontinuitetsskog och reviret ej avverkas för det finns inte mycket kvar av kontinuitetsskog och lämplig revir för spillkråkan i trakten.</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13630,7 +13630,7 @@
         <v>128395535</v>
       </c>
       <c r="B128" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>128395275</v>
       </c>
       <c r="B129" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>128395870</v>
       </c>
       <c r="B130" t="n">
-        <v>91906</v>
+        <v>91918</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>128395068</v>
       </c>
       <c r="B131" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>128395203</v>
       </c>
       <c r="B132" t="n">
-        <v>79169</v>
+        <v>79173</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14138,32 +14138,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128395657</v>
+        <v>128395093</v>
       </c>
       <c r="B133" t="n">
-        <v>82942</v>
+        <v>79173</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1312</v>
+        <v>6450</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14176,10 +14176,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>438915</v>
+        <v>438902</v>
       </c>
       <c r="R133" t="n">
-        <v>6783789</v>
+        <v>6783655</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -14239,32 +14239,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128395093</v>
+        <v>128395657</v>
       </c>
       <c r="B134" t="n">
-        <v>79169</v>
+        <v>82946</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14277,10 +14277,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>438902</v>
+        <v>438915</v>
       </c>
       <c r="R134" t="n">
-        <v>6783655</v>
+        <v>6783789</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -14343,7 +14343,7 @@
         <v>128395497</v>
       </c>
       <c r="B135" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>128395841</v>
       </c>
       <c r="B136" t="n">
-        <v>92149</v>
+        <v>92161</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>128395056</v>
       </c>
       <c r="B137" t="n">
-        <v>56879</v>
+        <v>56883</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>128395667</v>
       </c>
       <c r="B138" t="n">
-        <v>75168</v>
+        <v>75172</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14762,10 +14762,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128395820</v>
+        <v>128395852</v>
       </c>
       <c r="B139" t="n">
-        <v>57685</v>
+        <v>82946</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14773,39 +14773,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
@@ -14813,10 +14800,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>438897</v>
+        <v>438930</v>
       </c>
       <c r="R139" t="n">
-        <v>6783810</v>
+        <v>6783803</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -14851,17 +14838,13 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>En hane som troligen håller på att etablera revir i den gamla kontinuitetsskogen. Förutom själv observationen av fågeln sågs även färska ringhack som indikerar revir respektive revirbildning. Efter trettio år av iakttagelser och egna studier om tretåig hackspett har jag som observatör och erfaren skogsekolog förstod att ringhack är främst ett sätt att markera revir och har inget med att dricka sav att göra. För de allra flesta ringhack sker i gran och tall som knappast har någon sav utan istället kåda och så sker ringhack även utanför trädens savtid. Skulle det vara att dricka sav skulle enstaka hack i en björk räcka för ändamålet.</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14880,38 +14863,50 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128395313</v>
+        <v>128395820</v>
       </c>
       <c r="B140" t="n">
-        <v>98571</v>
+        <v>57689</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -14919,10 +14914,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>438888</v>
+        <v>438897</v>
       </c>
       <c r="R140" t="n">
-        <v>6783535</v>
+        <v>6783810</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -14959,7 +14954,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>En växtlokal med ett tiotal plantor.</t>
+          <t>En hane som troligen håller på att etablera revir i den gamla kontinuitetsskogen. Förutom själv observationen av fågeln sågs även färska ringhack som indikerar revir respektive revirbildning. Efter trettio år av iakttagelser och egna studier om tretåig hackspett har jag som observatör och erfaren skogsekolog förstod att ringhack är främst ett sätt att markera revir och har inget med att dricka sav att göra. För de allra flesta ringhack sker i gran och tall som knappast har någon sav utan istället kåda och så sker ringhack även utanför trädens savtid. Skulle det vara att dricka sav skulle enstaka hack i en björk räcka för ändamålet.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14968,7 +14963,6 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14987,37 +14981,38 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128395852</v>
+        <v>128395313</v>
       </c>
       <c r="B141" t="n">
-        <v>82942</v>
+        <v>98585</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -15025,10 +15020,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>438930</v>
+        <v>438888</v>
       </c>
       <c r="R141" t="n">
-        <v>6783803</v>
+        <v>6783535</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -15061,6 +15056,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>En växtlokal med ett tiotal plantor.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15091,7 +15091,7 @@
         <v>128395876</v>
       </c>
       <c r="B142" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>128395118</v>
       </c>
       <c r="B143" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>128395878</v>
       </c>
       <c r="B144" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15391,32 +15391,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128395863</v>
+        <v>128395091</v>
       </c>
       <c r="B145" t="n">
-        <v>75168</v>
+        <v>79087</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>311</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15429,10 +15429,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>438948</v>
+        <v>438902</v>
       </c>
       <c r="R145" t="n">
-        <v>6783801</v>
+        <v>6783655</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -15492,32 +15492,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128395091</v>
+        <v>128395863</v>
       </c>
       <c r="B146" t="n">
-        <v>79083</v>
+        <v>75172</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>311</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15530,10 +15530,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>438902</v>
+        <v>438948</v>
       </c>
       <c r="R146" t="n">
-        <v>6783655</v>
+        <v>6783801</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -15596,7 +15596,7 @@
         <v>128395650</v>
       </c>
       <c r="B147" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>128395641</v>
       </c>
       <c r="B148" t="n">
-        <v>56876</v>
+        <v>56880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>128395834</v>
       </c>
       <c r="B149" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -13183,7 +13183,7 @@
         <v>128395406</v>
       </c>
       <c r="B124" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>128395880</v>
       </c>
       <c r="B126" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>128395535</v>
       </c>
       <c r="B128" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13734,32 +13734,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128395275</v>
+        <v>128395870</v>
       </c>
       <c r="B129" t="n">
-        <v>91429</v>
+        <v>91920</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13772,10 +13772,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>438938</v>
+        <v>438950</v>
       </c>
       <c r="R129" t="n">
-        <v>6783582</v>
+        <v>6783777</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -13835,32 +13835,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128395870</v>
+        <v>128395275</v>
       </c>
       <c r="B130" t="n">
-        <v>91918</v>
+        <v>91431</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13873,10 +13873,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>438950</v>
+        <v>438938</v>
       </c>
       <c r="R130" t="n">
-        <v>6783777</v>
+        <v>6783582</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -13939,7 +13939,7 @@
         <v>128395068</v>
       </c>
       <c r="B131" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>128395203</v>
       </c>
       <c r="B132" t="n">
-        <v>79173</v>
+        <v>79175</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14138,32 +14138,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128395093</v>
+        <v>128395657</v>
       </c>
       <c r="B133" t="n">
-        <v>79173</v>
+        <v>82948</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14176,10 +14176,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>438902</v>
+        <v>438915</v>
       </c>
       <c r="R133" t="n">
-        <v>6783655</v>
+        <v>6783789</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -14239,32 +14239,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128395657</v>
+        <v>128395093</v>
       </c>
       <c r="B134" t="n">
-        <v>82946</v>
+        <v>79175</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1312</v>
+        <v>6450</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14277,10 +14277,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>438915</v>
+        <v>438902</v>
       </c>
       <c r="R134" t="n">
-        <v>6783789</v>
+        <v>6783655</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -14453,7 +14453,7 @@
         <v>128395841</v>
       </c>
       <c r="B136" t="n">
-        <v>92161</v>
+        <v>92163</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>128395667</v>
       </c>
       <c r="B138" t="n">
-        <v>75172</v>
+        <v>75174</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>128395852</v>
       </c>
       <c r="B139" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>128395313</v>
       </c>
       <c r="B141" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15088,10 +15088,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128395876</v>
+        <v>128395118</v>
       </c>
       <c r="B142" t="n">
-        <v>82946</v>
+        <v>79089</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15099,21 +15099,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15126,10 +15126,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>438950</v>
+        <v>438926</v>
       </c>
       <c r="R142" t="n">
-        <v>6783777</v>
+        <v>6783632</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15189,10 +15189,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128395118</v>
+        <v>128395876</v>
       </c>
       <c r="B143" t="n">
-        <v>79087</v>
+        <v>82948</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15200,21 +15200,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15227,10 +15227,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>438926</v>
+        <v>438950</v>
       </c>
       <c r="R143" t="n">
-        <v>6783632</v>
+        <v>6783777</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -15293,7 +15293,7 @@
         <v>128395878</v>
       </c>
       <c r="B144" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15391,32 +15391,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128395091</v>
+        <v>128395863</v>
       </c>
       <c r="B145" t="n">
-        <v>79087</v>
+        <v>75174</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>311</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15429,10 +15429,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>438902</v>
+        <v>438948</v>
       </c>
       <c r="R145" t="n">
-        <v>6783655</v>
+        <v>6783801</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -15492,32 +15492,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128395863</v>
+        <v>128395091</v>
       </c>
       <c r="B146" t="n">
-        <v>75172</v>
+        <v>79089</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>311</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15530,10 +15530,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>438948</v>
+        <v>438902</v>
       </c>
       <c r="R146" t="n">
-        <v>6783801</v>
+        <v>6783655</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -15596,7 +15596,7 @@
         <v>128395650</v>
       </c>
       <c r="B147" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>128395834</v>
       </c>
       <c r="B149" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -13404,10 +13404,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128395880</v>
+        <v>128395197</v>
       </c>
       <c r="B126" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13415,26 +13415,43 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
@@ -13442,10 +13459,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>438950</v>
+        <v>438915</v>
       </c>
       <c r="R126" t="n">
-        <v>6783777</v>
+        <v>6783590</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13480,13 +13497,17 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Hanen har tidigare observerats I reviret respektive den gamla kontinuitetsskogen. Det noterades att det undan för undan har kalavverkats samma kontinuitetsskog även tidigare och vid det angränsande och ca 3 år gamla hygget räknades upp till 230 årsringar på flertalet avverkade tallar. Med tanke på detta är det ytterst viktig att aktuell kontinuitetsskog och reviret ej avverkas för det finns inte mycket kvar av kontinuitetsskog och lämplig revir för spillkråkan i trakten.</t>
+        </is>
+      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13505,10 +13526,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128395197</v>
+        <v>128395880</v>
       </c>
       <c r="B127" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13516,43 +13537,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -13560,10 +13564,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>438915</v>
+        <v>438950</v>
       </c>
       <c r="R127" t="n">
-        <v>6783590</v>
+        <v>6783777</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -13598,17 +13602,13 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Hanen har tidigare observerats I reviret respektive den gamla kontinuitetsskogen. Det noterades att det undan för undan har kalavverkats samma kontinuitetsskog även tidigare och vid det angränsande och ca 3 år gamla hygget räknades upp till 230 årsringar på flertalet avverkade tallar. Med tanke på detta är det ytterst viktig att aktuell kontinuitetsskog och reviret ej avverkas för det finns inte mycket kvar av kontinuitetsskog och lämplig revir för spillkråkan i trakten.</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13630,7 +13630,7 @@
         <v>128395535</v>
       </c>
       <c r="B128" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13734,32 +13734,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128395870</v>
+        <v>128395275</v>
       </c>
       <c r="B129" t="n">
-        <v>91920</v>
+        <v>91431</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13772,10 +13772,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>438950</v>
+        <v>438938</v>
       </c>
       <c r="R129" t="n">
-        <v>6783777</v>
+        <v>6783582</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -13835,32 +13835,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128395275</v>
+        <v>128395870</v>
       </c>
       <c r="B130" t="n">
-        <v>91431</v>
+        <v>91920</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13873,10 +13873,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>438938</v>
+        <v>438950</v>
       </c>
       <c r="R130" t="n">
-        <v>6783582</v>
+        <v>6783777</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -14138,32 +14138,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128395657</v>
+        <v>128395093</v>
       </c>
       <c r="B133" t="n">
-        <v>82948</v>
+        <v>79175</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1312</v>
+        <v>6450</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14176,10 +14176,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>438915</v>
+        <v>438902</v>
       </c>
       <c r="R133" t="n">
-        <v>6783789</v>
+        <v>6783655</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -14239,32 +14239,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128395093</v>
+        <v>128395657</v>
       </c>
       <c r="B134" t="n">
-        <v>79175</v>
+        <v>82948</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14277,10 +14277,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>438902</v>
+        <v>438915</v>
       </c>
       <c r="R134" t="n">
-        <v>6783655</v>
+        <v>6783789</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -14984,7 +14984,7 @@
         <v>128395313</v>
       </c>
       <c r="B141" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15088,10 +15088,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128395118</v>
+        <v>128395876</v>
       </c>
       <c r="B142" t="n">
-        <v>79089</v>
+        <v>82948</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15099,21 +15099,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15126,10 +15126,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>438926</v>
+        <v>438950</v>
       </c>
       <c r="R142" t="n">
-        <v>6783632</v>
+        <v>6783777</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15189,10 +15189,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128395876</v>
+        <v>128395118</v>
       </c>
       <c r="B143" t="n">
-        <v>82948</v>
+        <v>79089</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15200,21 +15200,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15227,10 +15227,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>438950</v>
+        <v>438926</v>
       </c>
       <c r="R143" t="n">
-        <v>6783777</v>
+        <v>6783632</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -14138,32 +14138,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128395093</v>
+        <v>128395657</v>
       </c>
       <c r="B133" t="n">
-        <v>79175</v>
+        <v>82948</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14176,10 +14176,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>438902</v>
+        <v>438915</v>
       </c>
       <c r="R133" t="n">
-        <v>6783655</v>
+        <v>6783789</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -14239,32 +14239,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128395657</v>
+        <v>128395093</v>
       </c>
       <c r="B134" t="n">
-        <v>82948</v>
+        <v>79175</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1312</v>
+        <v>6450</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14277,10 +14277,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>438915</v>
+        <v>438902</v>
       </c>
       <c r="R134" t="n">
-        <v>6783789</v>
+        <v>6783655</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -13404,10 +13404,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128395197</v>
+        <v>128395880</v>
       </c>
       <c r="B126" t="n">
-        <v>57686</v>
+        <v>79089</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13415,43 +13415,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
@@ -13459,10 +13442,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>438915</v>
+        <v>438950</v>
       </c>
       <c r="R126" t="n">
-        <v>6783590</v>
+        <v>6783777</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13497,17 +13480,13 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Hanen har tidigare observerats I reviret respektive den gamla kontinuitetsskogen. Det noterades att det undan för undan har kalavverkats samma kontinuitetsskog även tidigare och vid det angränsande och ca 3 år gamla hygget räknades upp till 230 årsringar på flertalet avverkade tallar. Med tanke på detta är det ytterst viktig att aktuell kontinuitetsskog och reviret ej avverkas för det finns inte mycket kvar av kontinuitetsskog och lämplig revir för spillkråkan i trakten.</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13526,10 +13505,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128395880</v>
+        <v>128395197</v>
       </c>
       <c r="B127" t="n">
-        <v>79089</v>
+        <v>57686</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13537,26 +13516,43 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -13564,10 +13560,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>438950</v>
+        <v>438915</v>
       </c>
       <c r="R127" t="n">
-        <v>6783777</v>
+        <v>6783590</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -13602,13 +13598,17 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Hanen har tidigare observerats I reviret respektive den gamla kontinuitetsskogen. Det noterades att det undan för undan har kalavverkats samma kontinuitetsskog även tidigare och vid det angränsande och ca 3 år gamla hygget räknades upp till 230 årsringar på flertalet avverkade tallar. Med tanke på detta är det ytterst viktig att aktuell kontinuitetsskog och reviret ej avverkas för det finns inte mycket kvar av kontinuitetsskog och lämplig revir för spillkråkan i trakten.</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13630,7 +13630,7 @@
         <v>128395535</v>
       </c>
       <c r="B128" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13734,32 +13734,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128395275</v>
+        <v>128395870</v>
       </c>
       <c r="B129" t="n">
-        <v>91431</v>
+        <v>91921</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13772,10 +13772,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>438938</v>
+        <v>438950</v>
       </c>
       <c r="R129" t="n">
-        <v>6783582</v>
+        <v>6783777</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -13835,32 +13835,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128395870</v>
+        <v>128395275</v>
       </c>
       <c r="B130" t="n">
-        <v>91920</v>
+        <v>91432</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13873,10 +13873,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>438950</v>
+        <v>438938</v>
       </c>
       <c r="R130" t="n">
-        <v>6783777</v>
+        <v>6783582</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -14453,7 +14453,7 @@
         <v>128395841</v>
       </c>
       <c r="B136" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>128395313</v>
       </c>
       <c r="B141" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>128395878</v>
       </c>
       <c r="B144" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -13183,7 +13183,7 @@
         <v>128395406</v>
       </c>
       <c r="B124" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>128395378</v>
       </c>
       <c r="B125" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>128395880</v>
       </c>
       <c r="B126" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>128395197</v>
       </c>
       <c r="B127" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>128395535</v>
       </c>
       <c r="B128" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>128395870</v>
       </c>
       <c r="B129" t="n">
-        <v>91921</v>
+        <v>91948</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>128395275</v>
       </c>
       <c r="B130" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>128395068</v>
       </c>
       <c r="B131" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>128395203</v>
       </c>
       <c r="B132" t="n">
-        <v>79175</v>
+        <v>79202</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>128395657</v>
       </c>
       <c r="B133" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>128395093</v>
       </c>
       <c r="B134" t="n">
-        <v>79175</v>
+        <v>79202</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>128395497</v>
       </c>
       <c r="B135" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>128395841</v>
       </c>
       <c r="B136" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>128395056</v>
       </c>
       <c r="B137" t="n">
-        <v>56883</v>
+        <v>56910</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>128395667</v>
       </c>
       <c r="B138" t="n">
-        <v>75174</v>
+        <v>75201</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>128395852</v>
       </c>
       <c r="B139" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14863,50 +14863,38 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128395820</v>
+        <v>128395313</v>
       </c>
       <c r="B140" t="n">
-        <v>57689</v>
+        <v>98619</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -14914,10 +14902,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>438897</v>
+        <v>438888</v>
       </c>
       <c r="R140" t="n">
-        <v>6783810</v>
+        <v>6783535</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -14954,7 +14942,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>En hane som troligen håller på att etablera revir i den gamla kontinuitetsskogen. Förutom själv observationen av fågeln sågs även färska ringhack som indikerar revir respektive revirbildning. Efter trettio år av iakttagelser och egna studier om tretåig hackspett har jag som observatör och erfaren skogsekolog förstod att ringhack är främst ett sätt att markera revir och har inget med att dricka sav att göra. För de allra flesta ringhack sker i gran och tall som knappast har någon sav utan istället kåda och så sker ringhack även utanför trädens savtid. Skulle det vara att dricka sav skulle enstaka hack i en björk räcka för ändamålet.</t>
+          <t>En växtlokal med ett tiotal plantor.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14963,6 +14951,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14981,38 +14970,50 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128395313</v>
+        <v>128395820</v>
       </c>
       <c r="B141" t="n">
-        <v>98592</v>
+        <v>57716</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -15020,10 +15021,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>438888</v>
+        <v>438897</v>
       </c>
       <c r="R141" t="n">
-        <v>6783535</v>
+        <v>6783810</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -15060,7 +15061,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>En växtlokal med ett tiotal plantor.</t>
+          <t>En hane som troligen håller på att etablera revir i den gamla kontinuitetsskogen. Förutom själv observationen av fågeln sågs även färska ringhack som indikerar revir respektive revirbildning. Efter trettio år av iakttagelser och egna studier om tretåig hackspett har jag som observatör och erfaren skogsekolog förstod att ringhack är främst ett sätt att markera revir och har inget med att dricka sav att göra. För de allra flesta ringhack sker i gran och tall som knappast har någon sav utan istället kåda och så sker ringhack även utanför trädens savtid. Skulle det vara att dricka sav skulle enstaka hack i en björk räcka för ändamålet.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15069,7 +15070,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15088,10 +15088,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128395876</v>
+        <v>128395118</v>
       </c>
       <c r="B142" t="n">
-        <v>82948</v>
+        <v>79116</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15099,21 +15099,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15126,10 +15126,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>438950</v>
+        <v>438926</v>
       </c>
       <c r="R142" t="n">
-        <v>6783777</v>
+        <v>6783632</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15189,10 +15189,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128395118</v>
+        <v>128395876</v>
       </c>
       <c r="B143" t="n">
-        <v>79089</v>
+        <v>82975</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15200,21 +15200,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15227,10 +15227,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>438926</v>
+        <v>438950</v>
       </c>
       <c r="R143" t="n">
-        <v>6783632</v>
+        <v>6783777</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -15293,7 +15293,7 @@
         <v>128395878</v>
       </c>
       <c r="B144" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>128395863</v>
       </c>
       <c r="B145" t="n">
-        <v>75174</v>
+        <v>75201</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>128395091</v>
       </c>
       <c r="B146" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>128395650</v>
       </c>
       <c r="B147" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>128395641</v>
       </c>
       <c r="B148" t="n">
-        <v>56880</v>
+        <v>56907</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>128395834</v>
       </c>
       <c r="B149" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -14661,37 +14661,50 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128395667</v>
+        <v>128395820</v>
       </c>
       <c r="B138" t="n">
-        <v>75201</v>
+        <v>57716</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>311</v>
+        <v>100109</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
@@ -14699,10 +14712,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>438913</v>
+        <v>438897</v>
       </c>
       <c r="R138" t="n">
-        <v>6783798</v>
+        <v>6783810</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -14737,13 +14750,17 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>En hane som troligen håller på att etablera revir i den gamla kontinuitetsskogen. Förutom själv observationen av fågeln sågs även färska ringhack som indikerar revir respektive revirbildning. Efter trettio år av iakttagelser och egna studier om tretåig hackspett har jag som observatör och erfaren skogsekolog förstod att ringhack är främst ett sätt att markera revir och har inget med att dricka sav att göra. För de allra flesta ringhack sker i gran och tall som knappast har någon sav utan istället kåda och så sker ringhack även utanför trädens savtid. Skulle det vara att dricka sav skulle enstaka hack i en björk räcka för ändamålet.</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14762,37 +14779,38 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128395852</v>
+        <v>128395313</v>
       </c>
       <c r="B139" t="n">
-        <v>82975</v>
+        <v>98619</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
@@ -14800,10 +14818,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>438930</v>
+        <v>438888</v>
       </c>
       <c r="R139" t="n">
-        <v>6783803</v>
+        <v>6783535</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -14836,6 +14854,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>En växtlokal med ett tiotal plantor.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14863,38 +14886,37 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128395313</v>
+        <v>128395667</v>
       </c>
       <c r="B140" t="n">
-        <v>98619</v>
+        <v>75201</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>311</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -14902,10 +14924,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>438888</v>
+        <v>438913</v>
       </c>
       <c r="R140" t="n">
-        <v>6783535</v>
+        <v>6783798</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -14938,11 +14960,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>En växtlokal med ett tiotal plantor.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14970,10 +14987,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128395820</v>
+        <v>128395852</v>
       </c>
       <c r="B141" t="n">
-        <v>57716</v>
+        <v>82975</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14981,39 +14998,26 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -15021,10 +15025,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>438897</v>
+        <v>438930</v>
       </c>
       <c r="R141" t="n">
-        <v>6783810</v>
+        <v>6783803</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -15059,17 +15063,13 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>En hane som troligen håller på att etablera revir i den gamla kontinuitetsskogen. Förutom själv observationen av fågeln sågs även färska ringhack som indikerar revir respektive revirbildning. Efter trettio år av iakttagelser och egna studier om tretåig hackspett har jag som observatör och erfaren skogsekolog förstod att ringhack är främst ett sätt att markera revir och har inget med att dricka sav att göra. För de allra flesta ringhack sker i gran och tall som knappast har någon sav utan istället kåda och så sker ringhack även utanför trädens savtid. Skulle det vara att dricka sav skulle enstaka hack i en björk räcka för ändamålet.</t>
-        </is>
-      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15088,10 +15088,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128395118</v>
+        <v>128395876</v>
       </c>
       <c r="B142" t="n">
-        <v>79116</v>
+        <v>82975</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15099,21 +15099,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15126,10 +15126,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>438926</v>
+        <v>438950</v>
       </c>
       <c r="R142" t="n">
-        <v>6783632</v>
+        <v>6783777</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15189,10 +15189,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128395876</v>
+        <v>128395118</v>
       </c>
       <c r="B143" t="n">
-        <v>82975</v>
+        <v>79116</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15200,21 +15200,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15227,10 +15227,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>438950</v>
+        <v>438926</v>
       </c>
       <c r="R143" t="n">
-        <v>6783777</v>
+        <v>6783632</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -15391,32 +15391,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128395863</v>
+        <v>128395091</v>
       </c>
       <c r="B145" t="n">
-        <v>75201</v>
+        <v>79116</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>311</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15429,10 +15429,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>438948</v>
+        <v>438902</v>
       </c>
       <c r="R145" t="n">
-        <v>6783801</v>
+        <v>6783655</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -15492,32 +15492,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128395091</v>
+        <v>128395863</v>
       </c>
       <c r="B146" t="n">
-        <v>79116</v>
+        <v>75201</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>311</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15530,10 +15530,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>438902</v>
+        <v>438948</v>
       </c>
       <c r="R146" t="n">
-        <v>6783655</v>
+        <v>6783801</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -13183,7 +13183,7 @@
         <v>128395406</v>
       </c>
       <c r="B124" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>128395880</v>
       </c>
       <c r="B126" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>128395535</v>
       </c>
       <c r="B128" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13734,32 +13734,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128395870</v>
+        <v>128395275</v>
       </c>
       <c r="B129" t="n">
-        <v>91948</v>
+        <v>91469</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13772,10 +13772,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>438950</v>
+        <v>438938</v>
       </c>
       <c r="R129" t="n">
-        <v>6783777</v>
+        <v>6783582</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -13835,32 +13835,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128395275</v>
+        <v>128395870</v>
       </c>
       <c r="B130" t="n">
-        <v>91459</v>
+        <v>91958</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13873,10 +13873,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>438938</v>
+        <v>438950</v>
       </c>
       <c r="R130" t="n">
-        <v>6783582</v>
+        <v>6783777</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -13939,7 +13939,7 @@
         <v>128395068</v>
       </c>
       <c r="B131" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>128395203</v>
       </c>
       <c r="B132" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14138,32 +14138,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128395657</v>
+        <v>128395093</v>
       </c>
       <c r="B133" t="n">
-        <v>82975</v>
+        <v>79206</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1312</v>
+        <v>6450</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14176,10 +14176,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>438915</v>
+        <v>438902</v>
       </c>
       <c r="R133" t="n">
-        <v>6783789</v>
+        <v>6783655</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -14239,32 +14239,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128395093</v>
+        <v>128395657</v>
       </c>
       <c r="B134" t="n">
-        <v>79202</v>
+        <v>82979</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14277,10 +14277,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>438902</v>
+        <v>438915</v>
       </c>
       <c r="R134" t="n">
-        <v>6783655</v>
+        <v>6783789</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -14453,7 +14453,7 @@
         <v>128395841</v>
       </c>
       <c r="B136" t="n">
-        <v>92191</v>
+        <v>92201</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14661,10 +14661,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128395820</v>
+        <v>128395852</v>
       </c>
       <c r="B138" t="n">
-        <v>57716</v>
+        <v>82979</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14672,39 +14672,26 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
@@ -14712,10 +14699,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>438897</v>
+        <v>438930</v>
       </c>
       <c r="R138" t="n">
-        <v>6783810</v>
+        <v>6783803</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -14750,17 +14737,13 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>En hane som troligen håller på att etablera revir i den gamla kontinuitetsskogen. Förutom själv observationen av fågeln sågs även färska ringhack som indikerar revir respektive revirbildning. Efter trettio år av iakttagelser och egna studier om tretåig hackspett har jag som observatör och erfaren skogsekolog förstod att ringhack är främst ett sätt att markera revir och har inget med att dricka sav att göra. För de allra flesta ringhack sker i gran och tall som knappast har någon sav utan istället kåda och så sker ringhack även utanför trädens savtid. Skulle det vara att dricka sav skulle enstaka hack i en björk räcka för ändamålet.</t>
-        </is>
-      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14779,38 +14762,37 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128395313</v>
+        <v>128395667</v>
       </c>
       <c r="B139" t="n">
-        <v>98619</v>
+        <v>75202</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>311</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
@@ -14818,10 +14800,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>438888</v>
+        <v>438913</v>
       </c>
       <c r="R139" t="n">
-        <v>6783535</v>
+        <v>6783798</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -14854,11 +14836,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>En växtlokal med ett tiotal plantor.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14886,37 +14863,38 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128395667</v>
+        <v>128395313</v>
       </c>
       <c r="B140" t="n">
-        <v>75201</v>
+        <v>98632</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>311</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -14924,10 +14902,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>438913</v>
+        <v>438888</v>
       </c>
       <c r="R140" t="n">
-        <v>6783798</v>
+        <v>6783535</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -14960,6 +14938,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>En växtlokal med ett tiotal plantor.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14987,10 +14970,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128395852</v>
+        <v>128395820</v>
       </c>
       <c r="B141" t="n">
-        <v>82975</v>
+        <v>57716</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14998,26 +14981,39 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -15025,10 +15021,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>438930</v>
+        <v>438897</v>
       </c>
       <c r="R141" t="n">
-        <v>6783803</v>
+        <v>6783810</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -15063,13 +15059,17 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>En hane som troligen håller på att etablera revir i den gamla kontinuitetsskogen. Förutom själv observationen av fågeln sågs även färska ringhack som indikerar revir respektive revirbildning. Efter trettio år av iakttagelser och egna studier om tretåig hackspett har jag som observatör och erfaren skogsekolog förstod att ringhack är främst ett sätt att markera revir och har inget med att dricka sav att göra. För de allra flesta ringhack sker i gran och tall som knappast har någon sav utan istället kåda och så sker ringhack även utanför trädens savtid. Skulle det vara att dricka sav skulle enstaka hack i en björk räcka för ändamålet.</t>
+        </is>
+      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15088,10 +15088,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128395876</v>
+        <v>128395118</v>
       </c>
       <c r="B142" t="n">
-        <v>82975</v>
+        <v>79120</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15099,21 +15099,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15126,10 +15126,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>438950</v>
+        <v>438926</v>
       </c>
       <c r="R142" t="n">
-        <v>6783777</v>
+        <v>6783632</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15189,10 +15189,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128395118</v>
+        <v>128395876</v>
       </c>
       <c r="B143" t="n">
-        <v>79116</v>
+        <v>82979</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15200,21 +15200,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15227,10 +15227,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>438926</v>
+        <v>438950</v>
       </c>
       <c r="R143" t="n">
-        <v>6783632</v>
+        <v>6783777</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -15293,7 +15293,7 @@
         <v>128395878</v>
       </c>
       <c r="B144" t="n">
-        <v>91512</v>
+        <v>91522</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>128395091</v>
       </c>
       <c r="B145" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>128395863</v>
       </c>
       <c r="B146" t="n">
-        <v>75201</v>
+        <v>75202</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>128395650</v>
       </c>
       <c r="B147" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>128395834</v>
       </c>
       <c r="B149" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -13404,10 +13404,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128395880</v>
+        <v>128395197</v>
       </c>
       <c r="B126" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13415,26 +13415,43 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
@@ -13442,10 +13459,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>438950</v>
+        <v>438915</v>
       </c>
       <c r="R126" t="n">
-        <v>6783777</v>
+        <v>6783590</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13480,13 +13497,17 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Hanen har tidigare observerats I reviret respektive den gamla kontinuitetsskogen. Det noterades att det undan för undan har kalavverkats samma kontinuitetsskog även tidigare och vid det angränsande och ca 3 år gamla hygget räknades upp till 230 årsringar på flertalet avverkade tallar. Med tanke på detta är det ytterst viktig att aktuell kontinuitetsskog och reviret ej avverkas för det finns inte mycket kvar av kontinuitetsskog och lämplig revir för spillkråkan i trakten.</t>
+        </is>
+      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13505,10 +13526,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128395197</v>
+        <v>128395880</v>
       </c>
       <c r="B127" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13516,43 +13537,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -13560,10 +13564,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>438915</v>
+        <v>438950</v>
       </c>
       <c r="R127" t="n">
-        <v>6783590</v>
+        <v>6783777</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -13598,17 +13602,13 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>Hanen har tidigare observerats I reviret respektive den gamla kontinuitetsskogen. Det noterades att det undan för undan har kalavverkats samma kontinuitetsskog även tidigare och vid det angränsande och ca 3 år gamla hygget räknades upp till 230 årsringar på flertalet avverkade tallar. Med tanke på detta är det ytterst viktig att aktuell kontinuitetsskog och reviret ej avverkas för det finns inte mycket kvar av kontinuitetsskog och lämplig revir för spillkråkan i trakten.</t>
-        </is>
-      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -13734,32 +13734,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128395275</v>
+        <v>128395870</v>
       </c>
       <c r="B129" t="n">
-        <v>91469</v>
+        <v>91958</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13772,10 +13772,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>438938</v>
+        <v>438950</v>
       </c>
       <c r="R129" t="n">
-        <v>6783582</v>
+        <v>6783777</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -13835,32 +13835,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128395870</v>
+        <v>128395275</v>
       </c>
       <c r="B130" t="n">
-        <v>91958</v>
+        <v>91469</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13873,10 +13873,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>438950</v>
+        <v>438938</v>
       </c>
       <c r="R130" t="n">
-        <v>6783777</v>
+        <v>6783582</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -14138,32 +14138,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128395093</v>
+        <v>128395657</v>
       </c>
       <c r="B133" t="n">
-        <v>79206</v>
+        <v>82979</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14176,10 +14176,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>438902</v>
+        <v>438915</v>
       </c>
       <c r="R133" t="n">
-        <v>6783655</v>
+        <v>6783789</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -14239,32 +14239,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128395657</v>
+        <v>128395093</v>
       </c>
       <c r="B134" t="n">
-        <v>82979</v>
+        <v>79206</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1312</v>
+        <v>6450</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14277,10 +14277,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>438915</v>
+        <v>438902</v>
       </c>
       <c r="R134" t="n">
-        <v>6783789</v>
+        <v>6783655</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -14661,32 +14661,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128395852</v>
+        <v>128395667</v>
       </c>
       <c r="B138" t="n">
-        <v>82979</v>
+        <v>75202</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1312</v>
+        <v>311</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14699,10 +14699,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>438930</v>
+        <v>438913</v>
       </c>
       <c r="R138" t="n">
-        <v>6783803</v>
+        <v>6783798</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -14762,32 +14762,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128395667</v>
+        <v>128395852</v>
       </c>
       <c r="B139" t="n">
-        <v>75202</v>
+        <v>82979</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>311</v>
+        <v>1312</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14800,10 +14800,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>438913</v>
+        <v>438930</v>
       </c>
       <c r="R139" t="n">
-        <v>6783798</v>
+        <v>6783803</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -15088,10 +15088,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128395118</v>
+        <v>128395876</v>
       </c>
       <c r="B142" t="n">
-        <v>79120</v>
+        <v>82979</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15099,21 +15099,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15126,10 +15126,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>438926</v>
+        <v>438950</v>
       </c>
       <c r="R142" t="n">
-        <v>6783632</v>
+        <v>6783777</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15189,10 +15189,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128395876</v>
+        <v>128395118</v>
       </c>
       <c r="B143" t="n">
-        <v>82979</v>
+        <v>79120</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15200,21 +15200,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15227,10 +15227,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>438950</v>
+        <v>438926</v>
       </c>
       <c r="R143" t="n">
-        <v>6783777</v>
+        <v>6783632</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -15391,32 +15391,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128395091</v>
+        <v>128395863</v>
       </c>
       <c r="B145" t="n">
-        <v>79120</v>
+        <v>75202</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>311</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15429,10 +15429,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>438902</v>
+        <v>438948</v>
       </c>
       <c r="R145" t="n">
-        <v>6783655</v>
+        <v>6783801</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -15492,32 +15492,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128395863</v>
+        <v>128395091</v>
       </c>
       <c r="B146" t="n">
-        <v>75202</v>
+        <v>79120</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>311</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15530,10 +15530,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>438948</v>
+        <v>438902</v>
       </c>
       <c r="R146" t="n">
-        <v>6783801</v>
+        <v>6783655</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -13734,32 +13734,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128395870</v>
+        <v>128395275</v>
       </c>
       <c r="B129" t="n">
-        <v>91958</v>
+        <v>91469</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13772,10 +13772,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>438950</v>
+        <v>438938</v>
       </c>
       <c r="R129" t="n">
-        <v>6783777</v>
+        <v>6783582</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -13835,32 +13835,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128395275</v>
+        <v>128395870</v>
       </c>
       <c r="B130" t="n">
-        <v>91469</v>
+        <v>91958</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13873,10 +13873,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>438938</v>
+        <v>438950</v>
       </c>
       <c r="R130" t="n">
-        <v>6783582</v>
+        <v>6783777</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -14661,37 +14661,38 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128395667</v>
+        <v>128395313</v>
       </c>
       <c r="B138" t="n">
-        <v>75202</v>
+        <v>98632</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>311</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
@@ -14699,10 +14700,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>438913</v>
+        <v>438888</v>
       </c>
       <c r="R138" t="n">
-        <v>6783798</v>
+        <v>6783535</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -14735,6 +14736,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>En växtlokal med ett tiotal plantor.</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14762,10 +14768,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128395852</v>
+        <v>128395820</v>
       </c>
       <c r="B139" t="n">
-        <v>82979</v>
+        <v>57716</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14773,26 +14779,39 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
@@ -14800,10 +14819,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>438930</v>
+        <v>438897</v>
       </c>
       <c r="R139" t="n">
-        <v>6783803</v>
+        <v>6783810</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -14838,13 +14857,17 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>En hane som troligen håller på att etablera revir i den gamla kontinuitetsskogen. Förutom själv observationen av fågeln sågs även färska ringhack som indikerar revir respektive revirbildning. Efter trettio år av iakttagelser och egna studier om tretåig hackspett har jag som observatör och erfaren skogsekolog förstod att ringhack är främst ett sätt att markera revir och har inget med att dricka sav att göra. För de allra flesta ringhack sker i gran och tall som knappast har någon sav utan istället kåda och så sker ringhack även utanför trädens savtid. Skulle det vara att dricka sav skulle enstaka hack i en björk räcka för ändamålet.</t>
+        </is>
+      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14863,38 +14886,37 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128395313</v>
+        <v>128395667</v>
       </c>
       <c r="B140" t="n">
-        <v>98632</v>
+        <v>75202</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>311</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -14902,10 +14924,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>438888</v>
+        <v>438913</v>
       </c>
       <c r="R140" t="n">
-        <v>6783535</v>
+        <v>6783798</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -14938,11 +14960,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>En växtlokal med ett tiotal plantor.</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14970,10 +14987,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128395820</v>
+        <v>128395852</v>
       </c>
       <c r="B141" t="n">
-        <v>57716</v>
+        <v>82979</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14981,39 +14998,26 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -15021,10 +15025,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>438897</v>
+        <v>438930</v>
       </c>
       <c r="R141" t="n">
-        <v>6783810</v>
+        <v>6783803</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -15059,17 +15063,13 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>En hane som troligen håller på att etablera revir i den gamla kontinuitetsskogen. Förutom själv observationen av fågeln sågs även färska ringhack som indikerar revir respektive revirbildning. Efter trettio år av iakttagelser och egna studier om tretåig hackspett har jag som observatör och erfaren skogsekolog förstod att ringhack är främst ett sätt att markera revir och har inget med att dricka sav att göra. För de allra flesta ringhack sker i gran och tall som knappast har någon sav utan istället kåda och så sker ringhack även utanför trädens savtid. Skulle det vara att dricka sav skulle enstaka hack i en björk räcka för ändamålet.</t>
-        </is>
-      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -13404,10 +13404,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128395197</v>
+        <v>128395880</v>
       </c>
       <c r="B126" t="n">
-        <v>57713</v>
+        <v>79120</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13415,43 +13415,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
@@ -13459,10 +13442,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>438915</v>
+        <v>438950</v>
       </c>
       <c r="R126" t="n">
-        <v>6783590</v>
+        <v>6783777</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -13497,17 +13480,13 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Hanen har tidigare observerats I reviret respektive den gamla kontinuitetsskogen. Det noterades att det undan för undan har kalavverkats samma kontinuitetsskog även tidigare och vid det angränsande och ca 3 år gamla hygget räknades upp till 230 årsringar på flertalet avverkade tallar. Med tanke på detta är det ytterst viktig att aktuell kontinuitetsskog och reviret ej avverkas för det finns inte mycket kvar av kontinuitetsskog och lämplig revir för spillkråkan i trakten.</t>
-        </is>
-      </c>
       <c r="AD126" t="b">
         <v>0</v>
       </c>
       <c r="AE126" t="b">
         <v>0</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -13526,10 +13505,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128395880</v>
+        <v>128395197</v>
       </c>
       <c r="B127" t="n">
-        <v>79120</v>
+        <v>57713</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13537,26 +13516,43 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
-      <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
@@ -13564,10 +13560,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>438950</v>
+        <v>438915</v>
       </c>
       <c r="R127" t="n">
-        <v>6783777</v>
+        <v>6783590</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -13602,13 +13598,17 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Hanen har tidigare observerats I reviret respektive den gamla kontinuitetsskogen. Det noterades att det undan för undan har kalavverkats samma kontinuitetsskog även tidigare och vid det angränsande och ca 3 år gamla hygget räknades upp till 230 årsringar på flertalet avverkade tallar. Med tanke på detta är det ytterst viktig att aktuell kontinuitetsskog och reviret ej avverkas för det finns inte mycket kvar av kontinuitetsskog och lämplig revir för spillkråkan i trakten.</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
       <c r="AE127" t="b">
         <v>0</v>
       </c>
-      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
@@ -14661,38 +14661,37 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128395313</v>
+        <v>128395667</v>
       </c>
       <c r="B138" t="n">
-        <v>98632</v>
+        <v>75202</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>311</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
@@ -14700,10 +14699,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>438888</v>
+        <v>438913</v>
       </c>
       <c r="R138" t="n">
-        <v>6783535</v>
+        <v>6783798</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -14736,11 +14735,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-09-11</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>En växtlokal med ett tiotal plantor.</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14768,10 +14762,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128395820</v>
+        <v>128395852</v>
       </c>
       <c r="B139" t="n">
-        <v>57716</v>
+        <v>82979</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14779,39 +14773,26 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
@@ -14819,10 +14800,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>438897</v>
+        <v>438930</v>
       </c>
       <c r="R139" t="n">
-        <v>6783810</v>
+        <v>6783803</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -14857,17 +14838,13 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>En hane som troligen håller på att etablera revir i den gamla kontinuitetsskogen. Förutom själv observationen av fågeln sågs även färska ringhack som indikerar revir respektive revirbildning. Efter trettio år av iakttagelser och egna studier om tretåig hackspett har jag som observatör och erfaren skogsekolog förstod att ringhack är främst ett sätt att markera revir och har inget med att dricka sav att göra. För de allra flesta ringhack sker i gran och tall som knappast har någon sav utan istället kåda och så sker ringhack även utanför trädens savtid. Skulle det vara att dricka sav skulle enstaka hack i en björk räcka för ändamålet.</t>
-        </is>
-      </c>
       <c r="AD139" t="b">
         <v>0</v>
       </c>
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
@@ -14886,37 +14863,50 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128395667</v>
+        <v>128395820</v>
       </c>
       <c r="B140" t="n">
-        <v>75202</v>
+        <v>57716</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>311</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -14924,10 +14914,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>438913</v>
+        <v>438897</v>
       </c>
       <c r="R140" t="n">
-        <v>6783798</v>
+        <v>6783810</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -14962,13 +14952,17 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>En hane som troligen håller på att etablera revir i den gamla kontinuitetsskogen. Förutom själv observationen av fågeln sågs även färska ringhack som indikerar revir respektive revirbildning. Efter trettio år av iakttagelser och egna studier om tretåig hackspett har jag som observatör och erfaren skogsekolog förstod att ringhack är främst ett sätt att markera revir och har inget med att dricka sav att göra. För de allra flesta ringhack sker i gran och tall som knappast har någon sav utan istället kåda och så sker ringhack även utanför trädens savtid. Skulle det vara att dricka sav skulle enstaka hack i en björk räcka för ändamålet.</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14987,37 +14981,38 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128395852</v>
+        <v>128395313</v>
       </c>
       <c r="B141" t="n">
-        <v>82979</v>
+        <v>98632</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -15025,10 +15020,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>438930</v>
+        <v>438888</v>
       </c>
       <c r="R141" t="n">
-        <v>6783803</v>
+        <v>6783535</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -15061,6 +15056,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>En växtlokal med ett tiotal plantor.</t>
         </is>
       </c>
       <c r="AD141" t="b">

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -13183,7 +13183,7 @@
         <v>128395406</v>
       </c>
       <c r="B124" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>128395378</v>
       </c>
       <c r="B125" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>128395880</v>
       </c>
       <c r="B126" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>128395197</v>
       </c>
       <c r="B127" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>128395535</v>
       </c>
       <c r="B128" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13734,32 +13734,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128395275</v>
+        <v>128395870</v>
       </c>
       <c r="B129" t="n">
-        <v>91469</v>
+        <v>91962</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13772,10 +13772,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>438938</v>
+        <v>438950</v>
       </c>
       <c r="R129" t="n">
-        <v>6783582</v>
+        <v>6783777</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -13835,32 +13835,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128395870</v>
+        <v>128395275</v>
       </c>
       <c r="B130" t="n">
-        <v>91958</v>
+        <v>91473</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1209</v>
+        <v>5447</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13873,10 +13873,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>438950</v>
+        <v>438938</v>
       </c>
       <c r="R130" t="n">
-        <v>6783777</v>
+        <v>6783582</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -13939,7 +13939,7 @@
         <v>128395068</v>
       </c>
       <c r="B131" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>128395203</v>
       </c>
       <c r="B132" t="n">
-        <v>79206</v>
+        <v>79210</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14138,32 +14138,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128395657</v>
+        <v>128395093</v>
       </c>
       <c r="B133" t="n">
-        <v>82979</v>
+        <v>79210</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1312</v>
+        <v>6450</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14176,10 +14176,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>438915</v>
+        <v>438902</v>
       </c>
       <c r="R133" t="n">
-        <v>6783789</v>
+        <v>6783655</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -14239,32 +14239,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128395093</v>
+        <v>128395657</v>
       </c>
       <c r="B134" t="n">
-        <v>79206</v>
+        <v>82983</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14277,10 +14277,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>438902</v>
+        <v>438915</v>
       </c>
       <c r="R134" t="n">
-        <v>6783655</v>
+        <v>6783789</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -14343,7 +14343,7 @@
         <v>128395497</v>
       </c>
       <c r="B135" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>128395841</v>
       </c>
       <c r="B136" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>128395056</v>
       </c>
       <c r="B137" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>128395667</v>
       </c>
       <c r="B138" t="n">
-        <v>75202</v>
+        <v>75206</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>128395852</v>
       </c>
       <c r="B139" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>128395820</v>
       </c>
       <c r="B140" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>128395313</v>
       </c>
       <c r="B141" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15088,10 +15088,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128395876</v>
+        <v>128395118</v>
       </c>
       <c r="B142" t="n">
-        <v>82979</v>
+        <v>79124</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15099,21 +15099,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15126,10 +15126,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>438950</v>
+        <v>438926</v>
       </c>
       <c r="R142" t="n">
-        <v>6783777</v>
+        <v>6783632</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15189,10 +15189,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128395118</v>
+        <v>128395876</v>
       </c>
       <c r="B143" t="n">
-        <v>79120</v>
+        <v>82983</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15200,21 +15200,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15227,10 +15227,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>438926</v>
+        <v>438950</v>
       </c>
       <c r="R143" t="n">
-        <v>6783632</v>
+        <v>6783777</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -15293,7 +15293,7 @@
         <v>128395878</v>
       </c>
       <c r="B144" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15391,32 +15391,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128395863</v>
+        <v>128395091</v>
       </c>
       <c r="B145" t="n">
-        <v>75202</v>
+        <v>79124</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>311</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15429,10 +15429,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>438948</v>
+        <v>438902</v>
       </c>
       <c r="R145" t="n">
-        <v>6783801</v>
+        <v>6783655</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -15492,32 +15492,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128395091</v>
+        <v>128395863</v>
       </c>
       <c r="B146" t="n">
-        <v>79120</v>
+        <v>75206</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>311</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15530,10 +15530,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>438902</v>
+        <v>438948</v>
       </c>
       <c r="R146" t="n">
-        <v>6783655</v>
+        <v>6783801</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -15596,7 +15596,7 @@
         <v>128395650</v>
       </c>
       <c r="B147" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>128395641</v>
       </c>
       <c r="B148" t="n">
-        <v>56907</v>
+        <v>56910</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>128395834</v>
       </c>
       <c r="B149" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -14138,32 +14138,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128395093</v>
+        <v>128395657</v>
       </c>
       <c r="B133" t="n">
-        <v>79210</v>
+        <v>82983</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6450</v>
+        <v>1312</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14176,10 +14176,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>438902</v>
+        <v>438915</v>
       </c>
       <c r="R133" t="n">
-        <v>6783655</v>
+        <v>6783789</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -14239,32 +14239,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128395657</v>
+        <v>128395093</v>
       </c>
       <c r="B134" t="n">
-        <v>82983</v>
+        <v>79210</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1312</v>
+        <v>6450</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14277,10 +14277,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>438915</v>
+        <v>438902</v>
       </c>
       <c r="R134" t="n">
-        <v>6783789</v>
+        <v>6783655</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -15088,10 +15088,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128395118</v>
+        <v>128395876</v>
       </c>
       <c r="B142" t="n">
-        <v>79124</v>
+        <v>82983</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15099,21 +15099,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15126,10 +15126,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>438926</v>
+        <v>438950</v>
       </c>
       <c r="R142" t="n">
-        <v>6783632</v>
+        <v>6783777</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15189,10 +15189,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128395876</v>
+        <v>128395118</v>
       </c>
       <c r="B143" t="n">
-        <v>82983</v>
+        <v>79124</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15200,21 +15200,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15227,10 +15227,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>438950</v>
+        <v>438926</v>
       </c>
       <c r="R143" t="n">
-        <v>6783777</v>
+        <v>6783632</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -15391,32 +15391,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128395091</v>
+        <v>128395863</v>
       </c>
       <c r="B145" t="n">
-        <v>79124</v>
+        <v>75206</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>311</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15429,10 +15429,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>438902</v>
+        <v>438948</v>
       </c>
       <c r="R145" t="n">
-        <v>6783655</v>
+        <v>6783801</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -15492,32 +15492,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128395863</v>
+        <v>128395091</v>
       </c>
       <c r="B146" t="n">
-        <v>75206</v>
+        <v>79124</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>311</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15530,10 +15530,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>438948</v>
+        <v>438902</v>
       </c>
       <c r="R146" t="n">
-        <v>6783801</v>
+        <v>6783655</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>

--- a/artfynd/A 53355-2024 artfynd.xlsx
+++ b/artfynd/A 53355-2024 artfynd.xlsx
@@ -13183,7 +13183,7 @@
         <v>128395406</v>
       </c>
       <c r="B124" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>128395378</v>
       </c>
       <c r="B125" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>128395880</v>
       </c>
       <c r="B126" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>128395197</v>
       </c>
       <c r="B127" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>128395535</v>
       </c>
       <c r="B128" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>128395870</v>
       </c>
       <c r="B129" t="n">
-        <v>91962</v>
+        <v>91967</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
         <v>128395275</v>
       </c>
       <c r="B130" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>128395068</v>
       </c>
       <c r="B131" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14040,7 +14040,7 @@
         <v>128395203</v>
       </c>
       <c r="B132" t="n">
-        <v>79210</v>
+        <v>79115</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>128395657</v>
       </c>
       <c r="B133" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>128395093</v>
       </c>
       <c r="B134" t="n">
-        <v>79210</v>
+        <v>79115</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>128395497</v>
       </c>
       <c r="B135" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>128395841</v>
       </c>
       <c r="B136" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>128395056</v>
       </c>
       <c r="B137" t="n">
-        <v>56913</v>
+        <v>56916</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14661,37 +14661,50 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128395667</v>
+        <v>128395820</v>
       </c>
       <c r="B138" t="n">
-        <v>75206</v>
+        <v>57723</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>311</v>
+        <v>100109</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Brun nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Chaenotheca phaeocephala</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Turner) Th.Fr.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
@@ -14699,10 +14712,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>438913</v>
+        <v>438897</v>
       </c>
       <c r="R138" t="n">
-        <v>6783798</v>
+        <v>6783810</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -14737,13 +14750,17 @@
           <t>2025-09-11</t>
         </is>
       </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>En hane som troligen håller på att etablera revir i den gamla kontinuitetsskogen. Förutom själv observationen av fågeln sågs även färska ringhack som indikerar revir respektive revirbildning. Efter trettio år av iakttagelser och egna studier om tretåig hackspett har jag som observatör och erfaren skogsekolog förstod att ringhack är främst ett sätt att markera revir och har inget med att dricka sav att göra. För de allra flesta ringhack sker i gran och tall som knappast har någon sav utan istället kåda och så sker ringhack även utanför trädens savtid. Skulle det vara att dricka sav skulle enstaka hack i en björk räcka för ändamålet.</t>
+        </is>
+      </c>
       <c r="AD138" t="b">
         <v>0</v>
       </c>
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
@@ -14762,32 +14779,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128395852</v>
+        <v>128395667</v>
       </c>
       <c r="B139" t="n">
-        <v>82983</v>
+        <v>83002</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1312</v>
+        <v>311</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brun nållav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca phaeocephala</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Turner) Th.Fr.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14800,10 +14817,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>438930</v>
+        <v>438913</v>
       </c>
       <c r="R139" t="n">
-        <v>6783803</v>
+        <v>6783798</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -14863,10 +14880,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128395820</v>
+        <v>128395852</v>
       </c>
       <c r="B140" t="n">
-        <v>57720</v>
+        <v>82892</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14874,39 +14891,26 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -14914,10 +14918,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>438897</v>
+        <v>438930</v>
       </c>
       <c r="R140" t="n">
-        <v>6783810</v>
+        <v>6783803</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -14952,17 +14956,13 @@
           <t>2025-09-11</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>En hane som troligen håller på att etablera revir i den gamla kontinuitetsskogen. Förutom själv observationen av fågeln sågs även färska ringhack som indikerar revir respektive revirbildning. Efter trettio år av iakttagelser och egna studier om tretåig hackspett har jag som observatör och erfaren skogsekolog förstod att ringhack är främst ett sätt att markera revir och har inget med att dricka sav att göra. För de allra flesta ringhack sker i gran och tall som knappast har någon sav utan istället kåda och så sker ringhack även utanför trädens savtid. Skulle det vara att dricka sav skulle enstaka hack i en björk räcka för ändamålet.</t>
-        </is>
-      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -14984,7 +14984,7 @@
         <v>128395313</v>
       </c>
       <c r="B141" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15091,7 +15091,7 @@
         <v>128395876</v>
       </c>
       <c r="B142" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>128395118</v>
       </c>
       <c r="B143" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>128395878</v>
       </c>
       <c r="B144" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>128395863</v>
       </c>
       <c r="B145" t="n">
-        <v>75206</v>
+        <v>83002</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>128395091</v>
       </c>
       <c r="B146" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>128395650</v>
       </c>
       <c r="B147" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>128395641</v>
       </c>
       <c r="B148" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>128395834</v>
       </c>
       <c r="B149" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
